--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="801" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BE2A40B-FD67-4D85-A219-E86693957041}"/>
+  <xr:revisionPtr revIDLastSave="888" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01E68061-4D3E-420B-9472-0F5B5C6967FE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="425">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -398,9 +398,6 @@
     <t>SWINDON</t>
   </si>
   <si>
-    <t>LEYTON ORIENT</t>
-  </si>
-  <si>
     <t>MORGAN ROGERS</t>
   </si>
   <si>
@@ -1127,9 +1124,6 @@
     <t>ELI JUNIOR KROUPI</t>
   </si>
   <si>
-    <t>HUGO EKITIKA</t>
-  </si>
-  <si>
     <t>MACAULEY LANGSTAFF</t>
   </si>
   <si>
@@ -1293,6 +1287,33 @@
   </si>
   <si>
     <t>BRADFORD</t>
+  </si>
+  <si>
+    <t>SAM NOMBE</t>
+  </si>
+  <si>
+    <t>TRANSFER</t>
+  </si>
+  <si>
+    <t>SOLD</t>
+  </si>
+  <si>
+    <t>HUGO EKITIKE</t>
+  </si>
+  <si>
+    <t>SAMMIE SZMODICS</t>
+  </si>
+  <si>
+    <t>JOSH COBURN</t>
+  </si>
+  <si>
+    <t>JOEL PIROE</t>
+  </si>
+  <si>
+    <t>CHRISTOS TZOLIS</t>
+  </si>
+  <si>
+    <t>CYLE LARIN</t>
   </si>
 </sst>
 </file>
@@ -3310,7 +3331,7 @@
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="14">
         <v>1</v>
@@ -3332,11 +3353,11 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
@@ -3402,15 +3423,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3422,10 +3443,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E8" s="29">
         <v>1</v>
@@ -3446,11 +3467,11 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
@@ -3463,7 +3484,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>81</v>
@@ -3488,7 +3509,7 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
@@ -3496,7 +3517,7 @@
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3520,11 +3541,11 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
@@ -3542,7 +3563,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>82</v>
@@ -3567,7 +3588,7 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
@@ -3575,7 +3596,7 @@
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -3583,23 +3604,27 @@
     </row>
     <row r="12" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="79"/>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="D12" s="28" t="s">
+      <c r="C12" s="106" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="106" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="107">
         <v>3</v>
       </c>
-      <c r="F12" s="30">
-        <v>0</v>
-      </c>
-      <c r="G12" s="87"/>
-      <c r="H12" s="84"/>
+      <c r="F12" s="108">
+        <v>0</v>
+      </c>
+      <c r="G12" s="87" t="s">
+        <v>418</v>
+      </c>
+      <c r="H12" s="84">
+        <v>46261</v>
+      </c>
       <c r="I12" s="99"/>
       <c r="J12" s="82"/>
       <c r="K12" s="71" t="str">
@@ -3616,11 +3641,11 @@
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3629,18 +3654,20 @@
         <v>16</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>313</v>
+        <v>423</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="29">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>417</v>
       </c>
       <c r="F13" s="30">
         <v>0</v>
       </c>
-      <c r="G13" s="87"/>
+      <c r="G13" s="87">
+        <v>46261</v>
+      </c>
       <c r="H13" s="84"/>
       <c r="I13" s="99"/>
       <c r="J13" s="82"/>
@@ -3654,11 +3681,11 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
@@ -3672,11 +3699,21 @@
     </row>
     <row r="14" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="79"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
+      <c r="B14" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="29">
+        <v>6</v>
+      </c>
+      <c r="F14" s="30">
+        <v>1</v>
+      </c>
       <c r="G14" s="87"/>
       <c r="H14" s="84"/>
       <c r="I14" s="99"/>
@@ -3691,15 +3728,15 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -3726,15 +3763,15 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3743,10 +3780,10 @@
         <v>17</v>
       </c>
       <c r="C16" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="D16" s="28" t="s">
         <v>348</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>349</v>
       </c>
       <c r="E16" s="29">
         <v>17</v>
@@ -3768,7 +3805,7 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
@@ -3776,7 +3813,7 @@
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3810,7 +3847,7 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
@@ -3818,7 +3855,7 @@
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R17" s="114"/>
       <c r="S17" s="114"/>
@@ -3832,7 +3869,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>90</v>
@@ -3841,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="83"/>
       <c r="H18" s="84"/>
@@ -3857,7 +3894,7 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
@@ -3865,7 +3902,7 @@
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -3877,7 +3914,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>57</v>
@@ -3900,23 +3937,27 @@
     </row>
     <row r="20" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="79"/>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="107">
         <v>8</v>
       </c>
-      <c r="F20" s="30">
-        <v>0</v>
-      </c>
-      <c r="G20" s="87"/>
-      <c r="H20" s="84"/>
+      <c r="F20" s="108">
+        <v>0</v>
+      </c>
+      <c r="G20" s="87" t="s">
+        <v>418</v>
+      </c>
+      <c r="H20" s="84">
+        <v>46261</v>
+      </c>
       <c r="I20" s="99"/>
       <c r="J20" s="76"/>
       <c r="K20" s="1"/>
@@ -3932,12 +3973,24 @@
     </row>
     <row r="21" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79"/>
-      <c r="B21" s="106"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="87"/>
+      <c r="B21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="F21" s="30">
+        <v>0</v>
+      </c>
+      <c r="G21" s="87">
+        <v>46261</v>
+      </c>
       <c r="H21" s="84"/>
       <c r="I21" s="99"/>
       <c r="J21" s="76"/>
@@ -4037,7 +4090,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4092,7 +4145,7 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>21</v>
@@ -4218,10 +4271,10 @@
         <v>14</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E35" s="29">
         <v>1</v>
@@ -4245,7 +4298,7 @@
         <v>14</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>24</v>
@@ -4321,7 +4374,7 @@
         <v>16</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D39" s="28" t="s">
         <v>82</v>
@@ -4436,10 +4489,10 @@
         <v>17</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E44" s="29">
         <v>7</v>
@@ -4463,7 +4516,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D45" s="28" t="s">
         <v>70</v>
@@ -4490,7 +4543,7 @@
         <v>17</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D46" s="28" t="s">
         <v>90</v>
@@ -4517,10 +4570,10 @@
         <v>17</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E47" s="29">
         <v>2</v>
@@ -4684,7 +4737,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4752,13 +4805,13 @@
       </c>
       <c r="C59" s="13"/>
       <c r="D59" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E59" s="14">
         <v>5</v>
       </c>
       <c r="F59" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
@@ -4810,7 +4863,7 @@
         <v>14</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D62" s="28" t="s">
         <v>59</v>
@@ -4846,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="87"/>
       <c r="H63" s="91"/>
@@ -4884,7 +4937,7 @@
         <v>114</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E65" s="29">
         <v>10</v>
@@ -4935,7 +4988,7 @@
         <v>16</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D67" s="28" t="s">
         <v>58</v>
@@ -5023,7 +5076,7 @@
         <v>17</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D71" s="28" t="s">
         <v>59</v>
@@ -5059,7 +5112,7 @@
         <v>4</v>
       </c>
       <c r="F72" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" s="87"/>
       <c r="H72" s="91"/>
@@ -5077,7 +5130,7 @@
         <v>17</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D73" s="28" t="s">
         <v>53</v>
@@ -5104,7 +5157,7 @@
         <v>17</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>52</v>
@@ -5221,7 +5274,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -5397,7 +5450,7 @@
         <v>14</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>22</v>
@@ -5424,7 +5477,7 @@
         <v>14</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D90" s="28" t="s">
         <v>34</v>
@@ -5498,7 +5551,7 @@
         <v>99</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E93" s="29">
         <v>1</v>
@@ -5522,7 +5575,7 @@
         <v>16</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D94" s="28" t="s">
         <v>18</v>
@@ -5531,7 +5584,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="91"/>
       <c r="H94" s="91"/>
@@ -5583,7 +5636,7 @@
         <v>17</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D97" s="28" t="s">
         <v>75</v>
@@ -5610,16 +5663,16 @@
         <v>17</v>
       </c>
       <c r="C98" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="D98" s="28" t="s">
         <v>290</v>
-      </c>
-      <c r="D98" s="28" t="s">
-        <v>291</v>
       </c>
       <c r="E98" s="29">
         <v>7</v>
       </c>
       <c r="F98" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" s="87"/>
       <c r="H98" s="91"/>
@@ -5633,23 +5686,27 @@
     </row>
     <row r="99" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="79"/>
-      <c r="B99" s="28" t="s">
+      <c r="B99" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="D99" s="28" t="s">
+      <c r="C99" s="106" t="s">
+        <v>419</v>
+      </c>
+      <c r="D99" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="E99" s="29">
+      <c r="E99" s="107">
         <v>10</v>
       </c>
-      <c r="F99" s="30">
-        <v>0</v>
-      </c>
-      <c r="G99" s="87"/>
-      <c r="H99" s="91"/>
+      <c r="F99" s="108">
+        <v>0</v>
+      </c>
+      <c r="G99" s="87" t="s">
+        <v>418</v>
+      </c>
+      <c r="H99" s="91">
+        <v>46247</v>
+      </c>
       <c r="I99" s="90"/>
       <c r="J99" s="76"/>
       <c r="K99" s="1"/>
@@ -5664,18 +5721,20 @@
         <v>17</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>361</v>
+        <v>416</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E100" s="29">
-        <v>1</v>
+        <v>98</v>
+      </c>
+      <c r="E100" s="29" t="s">
+        <v>417</v>
       </c>
       <c r="F100" s="30">
         <v>0</v>
       </c>
-      <c r="G100" s="87"/>
+      <c r="G100" s="87">
+        <v>46247</v>
+      </c>
       <c r="H100" s="91"/>
       <c r="I100" s="90"/>
       <c r="J100" s="76"/>
@@ -5687,23 +5746,27 @@
     </row>
     <row r="101" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="79"/>
-      <c r="B101" s="28" t="s">
+      <c r="B101" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="28" t="s">
-        <v>363</v>
-      </c>
-      <c r="D101" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="E101" s="29">
-        <v>48</v>
-      </c>
-      <c r="F101" s="30">
-        <v>0</v>
-      </c>
-      <c r="G101" s="87"/>
-      <c r="H101" s="91"/>
+      <c r="C101" s="106" t="s">
+        <v>360</v>
+      </c>
+      <c r="D101" s="106" t="s">
+        <v>116</v>
+      </c>
+      <c r="E101" s="107">
+        <v>1</v>
+      </c>
+      <c r="F101" s="108">
+        <v>0</v>
+      </c>
+      <c r="G101" s="87" t="s">
+        <v>418</v>
+      </c>
+      <c r="H101" s="91">
+        <v>46254</v>
+      </c>
       <c r="I101" s="90"/>
       <c r="J101" s="76"/>
       <c r="K101" s="1"/>
@@ -5714,12 +5777,24 @@
     </row>
     <row r="102" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="79"/>
-      <c r="B102" s="106"/>
-      <c r="C102" s="106"/>
-      <c r="D102" s="106"/>
-      <c r="E102" s="107"/>
-      <c r="F102" s="108"/>
-      <c r="G102" s="87"/>
+      <c r="B102" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="28" t="s">
+        <v>422</v>
+      </c>
+      <c r="D102" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E102" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="F102" s="30">
+        <v>1</v>
+      </c>
+      <c r="G102" s="87">
+        <v>46254</v>
+      </c>
       <c r="H102" s="91"/>
       <c r="I102" s="90"/>
       <c r="J102" s="76"/>
@@ -5731,11 +5806,21 @@
     </row>
     <row r="103" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="79"/>
-      <c r="B103" s="28"/>
-      <c r="C103" s="28"/>
-      <c r="D103" s="28"/>
-      <c r="E103" s="29"/>
-      <c r="F103" s="30"/>
+      <c r="B103" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="D103" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E103" s="29">
+        <v>48</v>
+      </c>
+      <c r="F103" s="30">
+        <v>0</v>
+      </c>
       <c r="G103" s="87"/>
       <c r="H103" s="91"/>
       <c r="I103" s="90"/>
@@ -5808,7 +5893,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -5858,7 +5943,7 @@
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>49</v>
@@ -5932,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -5984,10 +6069,10 @@
         <v>14</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D116" s="28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E116" s="29">
         <v>1</v>
@@ -6011,10 +6096,10 @@
         <v>14</v>
       </c>
       <c r="C117" s="28" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D117" s="28" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E117" s="29">
         <v>1</v>
@@ -6082,10 +6167,10 @@
         <v>16</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E120" s="29">
         <v>1</v>
@@ -6112,7 +6197,7 @@
         <v>117</v>
       </c>
       <c r="D121" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E121" s="29">
         <v>1</v>
@@ -6170,7 +6255,7 @@
         <v>17</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D124" s="28" t="s">
         <v>70</v>
@@ -6224,7 +6309,7 @@
         <v>17</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D126" s="28" t="s">
         <v>98</v>
@@ -6254,7 +6339,7 @@
         <v>112</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E127" s="29">
         <v>1</v>
@@ -6278,10 +6363,10 @@
         <v>17</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D128" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E128" s="29">
         <v>1</v>
@@ -6395,7 +6480,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -6571,7 +6656,7 @@
         <v>14</v>
       </c>
       <c r="C143" s="28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D143" s="28" t="s">
         <v>109</v>
@@ -6598,7 +6683,7 @@
         <v>14</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D144" s="28" t="s">
         <v>59</v>
@@ -6642,10 +6727,10 @@
         <v>16</v>
       </c>
       <c r="C146" s="28" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D146" s="28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E146" s="29">
         <v>1</v>
@@ -6672,7 +6757,7 @@
         <v>105</v>
       </c>
       <c r="D147" s="28" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E147" s="29">
         <v>6</v>
@@ -6696,7 +6781,7 @@
         <v>16</v>
       </c>
       <c r="C148" s="28" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D148" s="28" t="s">
         <v>81</v>
@@ -6705,7 +6790,7 @@
         <v>2</v>
       </c>
       <c r="F148" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G148" s="87"/>
       <c r="H148" s="91"/>
@@ -6757,7 +6842,7 @@
         <v>17</v>
       </c>
       <c r="C151" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D151" s="28" t="s">
         <v>71</v>
@@ -6784,7 +6869,7 @@
         <v>17</v>
       </c>
       <c r="C152" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D152" s="28" t="s">
         <v>59</v>
@@ -6811,7 +6896,7 @@
         <v>17</v>
       </c>
       <c r="C153" s="28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D153" s="28" t="s">
         <v>20</v>
@@ -6838,7 +6923,7 @@
         <v>17</v>
       </c>
       <c r="C154" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D154" s="28" t="s">
         <v>81</v>
@@ -6865,10 +6950,10 @@
         <v>17</v>
       </c>
       <c r="C155" s="28" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D155" s="28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E155" s="29">
         <v>10</v>
@@ -6982,7 +7067,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -7106,7 +7191,7 @@
         <v>4</v>
       </c>
       <c r="F167" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G167" s="80"/>
       <c r="H167" s="94"/>
@@ -7158,10 +7243,10 @@
         <v>14</v>
       </c>
       <c r="C170" s="28" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D170" s="28" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E170" s="29">
         <v>3</v>
@@ -7185,7 +7270,7 @@
         <v>14</v>
       </c>
       <c r="C171" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D171" s="28" t="s">
         <v>70</v>
@@ -7229,10 +7314,10 @@
         <v>16</v>
       </c>
       <c r="C173" s="28" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D173" s="28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E173" s="29">
         <v>6</v>
@@ -7256,7 +7341,7 @@
         <v>16</v>
       </c>
       <c r="C174" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D174" s="28" t="s">
         <v>19</v>
@@ -7283,7 +7368,7 @@
         <v>16</v>
       </c>
       <c r="C175" s="28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D175" s="28" t="s">
         <v>22</v>
@@ -7344,7 +7429,7 @@
         <v>17</v>
       </c>
       <c r="C178" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D178" s="28" t="s">
         <v>102</v>
@@ -7371,10 +7456,10 @@
         <v>17</v>
       </c>
       <c r="C179" s="28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D179" s="28" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E179" s="29">
         <v>24</v>
@@ -7398,10 +7483,10 @@
         <v>17</v>
       </c>
       <c r="C180" s="28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D180" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E180" s="29">
         <v>7</v>
@@ -7425,7 +7510,7 @@
         <v>17</v>
       </c>
       <c r="C181" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D181" s="28" t="s">
         <v>116</v>
@@ -7452,10 +7537,10 @@
         <v>17</v>
       </c>
       <c r="C182" s="28" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D182" s="28" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E182" s="29">
         <v>1</v>
@@ -7569,7 +7654,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -7619,10 +7704,10 @@
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="1"/>
@@ -7687,13 +7772,13 @@
       </c>
       <c r="C194" s="13"/>
       <c r="D194" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E194" s="14">
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -7745,16 +7830,16 @@
         <v>14</v>
       </c>
       <c r="C197" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D197" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E197" s="29">
         <v>3</v>
       </c>
       <c r="F197" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197" s="83"/>
       <c r="H197" s="91"/>
@@ -7772,7 +7857,7 @@
         <v>14</v>
       </c>
       <c r="C198" s="28" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D198" s="28" t="s">
         <v>31</v>
@@ -7816,7 +7901,7 @@
         <v>16</v>
       </c>
       <c r="C200" s="28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D200" s="28" t="s">
         <v>113</v>
@@ -7843,7 +7928,7 @@
         <v>16</v>
       </c>
       <c r="C201" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D201" s="28" t="s">
         <v>34</v>
@@ -7870,7 +7955,7 @@
         <v>16</v>
       </c>
       <c r="C202" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D202" s="28" t="s">
         <v>31</v>
@@ -7927,23 +8012,27 @@
     </row>
     <row r="205" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="79"/>
-      <c r="B205" s="28" t="s">
+      <c r="B205" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C205" s="28" t="s">
+      <c r="C205" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="D205" s="28" t="s">
+      <c r="D205" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="E205" s="29">
+      <c r="E205" s="107">
         <v>3</v>
       </c>
-      <c r="F205" s="30">
-        <v>0</v>
-      </c>
-      <c r="G205" s="83"/>
-      <c r="H205" s="91"/>
+      <c r="F205" s="108">
+        <v>0</v>
+      </c>
+      <c r="G205" s="83" t="s">
+        <v>418</v>
+      </c>
+      <c r="H205" s="91">
+        <v>46254</v>
+      </c>
       <c r="I205" s="90"/>
       <c r="J205" s="76"/>
       <c r="K205" s="1"/>
@@ -7958,18 +8047,20 @@
         <v>17</v>
       </c>
       <c r="C206" s="28" t="s">
-        <v>146</v>
+        <v>420</v>
       </c>
       <c r="D206" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="E206" s="29">
-        <v>10</v>
+        <v>62</v>
+      </c>
+      <c r="E206" s="29" t="s">
+        <v>417</v>
       </c>
       <c r="F206" s="30">
         <v>0</v>
       </c>
-      <c r="G206" s="87"/>
+      <c r="G206" s="87">
+        <v>46254</v>
+      </c>
       <c r="H206" s="90"/>
       <c r="I206" s="90"/>
       <c r="J206" s="76"/>
@@ -7985,13 +8076,13 @@
         <v>17</v>
       </c>
       <c r="C207" s="28" t="s">
-        <v>289</v>
+        <v>145</v>
       </c>
       <c r="D207" s="28" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E207" s="29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F207" s="30">
         <v>0</v>
@@ -8012,13 +8103,13 @@
         <v>17</v>
       </c>
       <c r="C208" s="28" t="s">
-        <v>78</v>
+        <v>288</v>
       </c>
       <c r="D208" s="28" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="E208" s="29">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="F208" s="30">
         <v>0</v>
@@ -8039,13 +8130,13 @@
         <v>17</v>
       </c>
       <c r="C209" s="28" t="s">
-        <v>314</v>
+        <v>78</v>
       </c>
       <c r="D209" s="28" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E209" s="29">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="F209" s="30">
         <v>0</v>
@@ -8062,11 +8153,21 @@
     </row>
     <row r="210" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="79"/>
-      <c r="B210" s="106"/>
-      <c r="C210" s="106"/>
-      <c r="D210" s="106"/>
-      <c r="E210" s="107"/>
-      <c r="F210" s="108"/>
+      <c r="B210" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C210" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="D210" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E210" s="29">
+        <v>1</v>
+      </c>
+      <c r="F210" s="30">
+        <v>0</v>
+      </c>
       <c r="G210" s="87"/>
       <c r="H210" s="90"/>
       <c r="I210" s="90"/>
@@ -8206,7 +8307,7 @@
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>50</v>
@@ -8332,10 +8433,10 @@
         <v>14</v>
       </c>
       <c r="C224" s="28" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D224" s="28" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E224" s="29">
         <v>1</v>
@@ -8359,10 +8460,10 @@
         <v>14</v>
       </c>
       <c r="C225" s="28" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D225" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E225" s="29">
         <v>1</v>
@@ -8403,7 +8504,7 @@
         <v>16</v>
       </c>
       <c r="C227" s="28" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D227" s="28" t="s">
         <v>101</v>
@@ -8412,7 +8513,7 @@
         <v>1</v>
       </c>
       <c r="F227" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G227" s="83"/>
       <c r="H227" s="91"/>
@@ -8430,7 +8531,7 @@
         <v>16</v>
       </c>
       <c r="C228" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D228" s="28" t="s">
         <v>69</v>
@@ -8457,7 +8558,7 @@
         <v>16</v>
       </c>
       <c r="C229" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D229" s="28" t="s">
         <v>57</v>
@@ -8518,7 +8619,7 @@
         <v>17</v>
       </c>
       <c r="C232" s="28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D232" s="28" t="s">
         <v>23</v>
@@ -8545,10 +8646,10 @@
         <v>17</v>
       </c>
       <c r="C233" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D233" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E233" s="29">
         <v>19</v>
@@ -8572,7 +8673,7 @@
         <v>17</v>
       </c>
       <c r="C234" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D234" s="28" t="s">
         <v>18</v>
@@ -8599,10 +8700,10 @@
         <v>17</v>
       </c>
       <c r="C235" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="D235" s="28" t="s">
         <v>277</v>
-      </c>
-      <c r="D235" s="28" t="s">
-        <v>278</v>
       </c>
       <c r="E235" s="29">
         <v>5</v>
@@ -8626,10 +8727,10 @@
         <v>17</v>
       </c>
       <c r="C236" s="28" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D236" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E236" s="29">
         <v>13</v>
@@ -8743,7 +8844,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -8793,7 +8894,7 @@
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>51</v>
@@ -8867,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G248" s="80"/>
       <c r="H248" s="94"/>
@@ -8919,7 +9020,7 @@
         <v>14</v>
       </c>
       <c r="C251" s="28" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D251" s="28" t="s">
         <v>22</v>
@@ -8928,7 +9029,7 @@
         <v>2</v>
       </c>
       <c r="F251" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G251" s="83"/>
       <c r="H251" s="91"/>
@@ -8990,10 +9091,10 @@
         <v>16</v>
       </c>
       <c r="C254" s="28" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D254" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E254" s="29">
         <v>16</v>
@@ -9017,7 +9118,7 @@
         <v>16</v>
       </c>
       <c r="C255" s="28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D255" s="28" t="s">
         <v>73</v>
@@ -9044,10 +9145,10 @@
         <v>16</v>
       </c>
       <c r="C256" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D256" s="28" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E256" s="29">
         <v>1</v>
@@ -9105,7 +9206,7 @@
         <v>17</v>
       </c>
       <c r="C259" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D259" s="28" t="s">
         <v>118</v>
@@ -9114,7 +9215,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G259" s="87"/>
       <c r="H259" s="91"/>
@@ -9132,16 +9233,16 @@
         <v>17</v>
       </c>
       <c r="C260" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D260" s="28" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="E260" s="29">
         <v>22</v>
       </c>
       <c r="F260" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
@@ -9168,7 +9269,7 @@
         <v>33</v>
       </c>
       <c r="F261" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G261" s="87"/>
       <c r="H261" s="91"/>
@@ -9186,7 +9287,7 @@
         <v>17</v>
       </c>
       <c r="C262" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D262" s="28" t="s">
         <v>62</v>
@@ -9195,7 +9296,7 @@
         <v>3</v>
       </c>
       <c r="F262" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G262" s="87"/>
       <c r="H262" s="91"/>
@@ -9330,7 +9431,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -9448,13 +9549,13 @@
       </c>
       <c r="C275" s="13"/>
       <c r="D275" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E275" s="14">
         <v>1</v>
       </c>
       <c r="F275" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G275" s="80"/>
       <c r="H275" s="94"/>
@@ -9506,10 +9607,10 @@
         <v>14</v>
       </c>
       <c r="C278" s="28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D278" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E278" s="29">
         <v>1</v>
@@ -9533,7 +9634,7 @@
         <v>14</v>
       </c>
       <c r="C279" s="28" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D279" s="28" t="s">
         <v>104</v>
@@ -9577,7 +9678,7 @@
         <v>16</v>
       </c>
       <c r="C281" s="28" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D281" s="28" t="s">
         <v>19</v>
@@ -9604,10 +9705,10 @@
         <v>16</v>
       </c>
       <c r="C282" s="28" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D282" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E282" s="29">
         <v>1</v>
@@ -9631,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C283" s="28" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D283" s="28" t="s">
         <v>52</v>
@@ -9701,7 +9802,7 @@
         <v>1</v>
       </c>
       <c r="F286" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G286" s="83"/>
       <c r="H286" s="91"/>
@@ -9719,7 +9820,7 @@
         <v>17</v>
       </c>
       <c r="C287" s="28" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D287" s="28" t="s">
         <v>102</v>
@@ -9746,7 +9847,7 @@
         <v>17</v>
       </c>
       <c r="C288" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D288" s="28" t="s">
         <v>72</v>
@@ -9773,7 +9874,7 @@
         <v>17</v>
       </c>
       <c r="C289" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D289" s="28" t="s">
         <v>113</v>
@@ -9917,7 +10018,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -9967,7 +10068,7 @@
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>80</v>
@@ -10041,7 +10142,7 @@
         <v>1</v>
       </c>
       <c r="F302" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G302" s="80"/>
       <c r="H302" s="91"/>
@@ -10120,10 +10221,10 @@
         <v>14</v>
       </c>
       <c r="C306" s="28" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D306" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E306" s="29">
         <v>1</v>
@@ -10164,7 +10265,7 @@
         <v>16</v>
       </c>
       <c r="C308" s="28" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D308" s="28" t="s">
         <v>95</v>
@@ -10191,10 +10292,10 @@
         <v>16</v>
       </c>
       <c r="C309" s="28" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D309" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E309" s="29">
         <v>1</v>
@@ -10218,10 +10319,10 @@
         <v>16</v>
       </c>
       <c r="C310" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D310" s="77" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E310" s="29">
         <v>1</v>
@@ -10306,10 +10407,10 @@
         <v>17</v>
       </c>
       <c r="C314" s="28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D314" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E314" s="29">
         <v>1</v>
@@ -10333,7 +10434,7 @@
         <v>17</v>
       </c>
       <c r="C315" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D315" s="28" t="s">
         <v>20</v>
@@ -10360,10 +10461,10 @@
         <v>17</v>
       </c>
       <c r="C316" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D316" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E316" s="29">
         <v>1</v>
@@ -10387,10 +10488,10 @@
         <v>17</v>
       </c>
       <c r="C317" s="28" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D317" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E317" s="29">
         <v>1</v>
@@ -10504,7 +10605,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -10554,10 +10655,10 @@
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E326" s="2"/>
       <c r="F326" s="1"/>
@@ -10628,7 +10729,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -10680,10 +10781,10 @@
         <v>14</v>
       </c>
       <c r="C332" s="28" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D332" s="28" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E332" s="29">
         <v>2</v>
@@ -10707,7 +10808,7 @@
         <v>14</v>
       </c>
       <c r="C333" s="28" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D333" s="28" t="s">
         <v>18</v>
@@ -10751,10 +10852,10 @@
         <v>16</v>
       </c>
       <c r="C335" s="28" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D335" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E335" s="29">
         <v>10</v>
@@ -10778,10 +10879,10 @@
         <v>16</v>
       </c>
       <c r="C336" s="28" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D336" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E336" s="29">
         <v>1</v>
@@ -10805,10 +10906,10 @@
         <v>16</v>
       </c>
       <c r="C337" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D337" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E337" s="29">
         <v>1</v>
@@ -10863,7 +10964,7 @@
         <v>17</v>
       </c>
       <c r="C340" s="28" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D340" s="28" t="s">
         <v>58</v>
@@ -10887,10 +10988,10 @@
         <v>17</v>
       </c>
       <c r="C341" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D341" s="28" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E341" s="29">
         <v>5</v>
@@ -10911,10 +11012,10 @@
         <v>17</v>
       </c>
       <c r="C342" s="28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D342" s="28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E342" s="29">
         <v>12</v>
@@ -10935,7 +11036,7 @@
         <v>17</v>
       </c>
       <c r="C343" s="28" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D343" s="28" t="s">
         <v>23</v>
@@ -10959,10 +11060,10 @@
         <v>17</v>
       </c>
       <c r="C344" s="28" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D344" s="28" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E344" s="29">
         <v>40</v>
@@ -11058,7 +11159,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -11084,10 +11185,10 @@
     <row r="353" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="1"/>
       <c r="C353" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E353" s="2"/>
       <c r="F353" s="1"/>
@@ -11140,7 +11241,7 @@
         <v>3</v>
       </c>
       <c r="F356" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -11174,7 +11275,7 @@
         <v>14</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D359" s="28" t="s">
         <v>24</v>
@@ -11195,7 +11296,7 @@
         <v>14</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D360" s="28" t="s">
         <v>18</v>
@@ -11269,7 +11370,7 @@
         <v>16</v>
       </c>
       <c r="C364" s="28" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D364" s="28" t="s">
         <v>22</v>
@@ -11312,10 +11413,10 @@
         <v>17</v>
       </c>
       <c r="C367" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D367" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E367" s="29">
         <v>25</v>
@@ -11333,7 +11434,7 @@
         <v>17</v>
       </c>
       <c r="C368" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D368" s="28" t="s">
         <v>70</v>
@@ -11354,10 +11455,10 @@
         <v>17</v>
       </c>
       <c r="C369" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D369" s="28" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E369" s="29">
         <v>1</v>
@@ -11371,23 +11472,27 @@
       <c r="J369" s="1"/>
     </row>
     <row r="370" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B370" s="28" t="s">
+      <c r="B370" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C370" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="D370" s="28" t="s">
-        <v>403</v>
-      </c>
-      <c r="E370" s="29">
+      <c r="C370" s="106" t="s">
+        <v>400</v>
+      </c>
+      <c r="D370" s="106" t="s">
+        <v>401</v>
+      </c>
+      <c r="E370" s="107">
         <v>1</v>
       </c>
-      <c r="F370" s="30">
-        <v>0</v>
-      </c>
-      <c r="G370" s="103"/>
-      <c r="H370" s="1"/>
+      <c r="F370" s="108">
+        <v>0</v>
+      </c>
+      <c r="G370" s="103" t="s">
+        <v>418</v>
+      </c>
+      <c r="H370" s="103">
+        <v>46254</v>
+      </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
     </row>
@@ -11396,28 +11501,40 @@
         <v>17</v>
       </c>
       <c r="C371" s="28" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="D371" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="E371" s="29">
-        <v>20</v>
+        <v>73</v>
+      </c>
+      <c r="E371" s="29" t="s">
+        <v>417</v>
       </c>
       <c r="F371" s="30">
         <v>0</v>
       </c>
-      <c r="G371" s="1"/>
+      <c r="G371" s="103">
+        <v>46254</v>
+      </c>
       <c r="H371" s="103"/>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
     </row>
     <row r="372" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B372" s="106"/>
-      <c r="C372" s="106"/>
-      <c r="D372" s="106"/>
-      <c r="E372" s="107"/>
-      <c r="F372" s="108"/>
+      <c r="B372" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C372" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="D372" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="E372" s="29">
+        <v>20</v>
+      </c>
+      <c r="F372" s="30">
+        <v>0</v>
+      </c>
       <c r="G372" s="103"/>
       <c r="H372" s="103"/>
       <c r="I372" s="1"/>
@@ -11477,7 +11594,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -11770,7 +11887,7 @@
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
       <c r="D4" s="43" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="41"/>
@@ -11826,14 +11943,14 @@
       <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="24" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" s="26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" s="27">
         <v>0</v>
@@ -11849,19 +11966,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>326</v>
+        <v>51</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>345</v>
+        <v>135</v>
       </c>
       <c r="E8" s="25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8" s="26">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G8" s="27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -11874,19 +11991,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>136</v>
+        <v>2</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>1</v>
       </c>
       <c r="E9" s="25">
-        <v>3</v>
-      </c>
-      <c r="F9" s="26">
-        <v>4</v>
-      </c>
-      <c r="G9" s="27">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F9" s="56">
+        <v>5</v>
+      </c>
+      <c r="G9" s="57">
+        <v>0</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -11899,16 +12016,16 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E10" s="25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="27">
         <v>0</v>
@@ -11924,19 +12041,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>267</v>
+        <v>344</v>
       </c>
       <c r="E11" s="25">
         <v>2</v>
       </c>
       <c r="F11" s="26">
+        <v>4</v>
+      </c>
+      <c r="G11" s="27">
         <v>2</v>
-      </c>
-      <c r="G11" s="27">
-        <v>0</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="41"/>
@@ -11949,19 +12066,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="E12" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -11971,22 +12088,22 @@
     <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47"/>
       <c r="B13" s="54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="E13" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="26">
         <v>2</v>
       </c>
       <c r="G13" s="27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="41"/>
@@ -11999,19 +12116,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>126</v>
       </c>
       <c r="E14" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G14" s="27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="41"/>
@@ -12021,22 +12138,22 @@
     <row r="15" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47"/>
       <c r="B15" s="54">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="55" t="s">
-        <v>159</v>
+        <v>93</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="25">
-        <v>1</v>
-      </c>
-      <c r="F15" s="56">
-        <v>1</v>
-      </c>
-      <c r="G15" s="57">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F15" s="26">
+        <v>3</v>
+      </c>
+      <c r="G15" s="27">
+        <v>3</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="41"/>
@@ -12046,22 +12163,22 @@
     <row r="16" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47"/>
       <c r="B16" s="54">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="55" t="s">
-        <v>144</v>
-      </c>
       <c r="E16" s="25">
+        <v>0</v>
+      </c>
+      <c r="F16" s="26">
         <v>1</v>
       </c>
-      <c r="F16" s="56">
+      <c r="G16" s="27">
         <v>1</v>
-      </c>
-      <c r="G16" s="57">
-        <v>0</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -12076,17 +12193,17 @@
       <c r="C17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="55" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="25">
-        <v>0</v>
-      </c>
-      <c r="F17" s="26">
+        <v>-1</v>
+      </c>
+      <c r="F17" s="56">
         <v>3</v>
       </c>
-      <c r="G17" s="27">
-        <v>3</v>
+      <c r="G17" s="57">
+        <v>4</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -12099,19 +12216,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E18" s="25">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F18" s="26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -12124,19 +12241,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="55" t="s">
-        <v>141</v>
+        <v>343</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>403</v>
       </c>
       <c r="E19" s="25">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="F19" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -12149,10 +12266,10 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>405</v>
+        <v>49</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>127</v>
       </c>
       <c r="E20" s="25">
         <v>-3</v>
@@ -12227,7 +12344,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -12264,10 +12381,10 @@
       <c r="F4" s="100"/>
       <c r="G4" s="100"/>
       <c r="I4" s="38" t="s">
+        <v>296</v>
+      </c>
+      <c r="J4" s="38" t="s">
         <v>297</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12281,10 +12398,10 @@
       <c r="F5" s="64"/>
       <c r="G5" s="64"/>
       <c r="I5" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="J5" s="38" t="s">
         <v>299</v>
-      </c>
-      <c r="J5" s="38" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12298,10 +12415,10 @@
       <c r="F6" s="64"/>
       <c r="G6" s="64"/>
       <c r="I6" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="J6" s="38" t="s">
         <v>301</v>
-      </c>
-      <c r="J6" s="38" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12318,7 +12435,7 @@
         <v>38</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12343,7 +12460,7 @@
       <c r="F9" s="100"/>
       <c r="G9" s="100"/>
       <c r="I9" s="38" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12358,7 +12475,7 @@
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="67"/>
       <c r="B11" s="63" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C11" s="68"/>
       <c r="D11" s="64"/>
@@ -12452,7 +12569,7 @@
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="67"/>
       <c r="B20" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C20" s="68"/>
       <c r="D20" s="64"/>
@@ -12523,7 +12640,7 @@
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="67"/>
       <c r="B27" s="63" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C27" s="68"/>
       <c r="D27" s="64"/>
@@ -12533,7 +12650,7 @@
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B28" s="68"/>
       <c r="C28" s="64"/>
@@ -12562,7 +12679,7 @@
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B31" s="65"/>
       <c r="C31" s="64"/>
@@ -12622,7 +12739,7 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -12712,7 +12829,7 @@
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
       <c r="J4" s="98" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K4" s="38"/>
       <c r="L4" s="38"/>
@@ -12742,7 +12859,7 @@
       <c r="H5" s="38"/>
       <c r="I5" s="38"/>
       <c r="J5" s="98" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K5" s="38"/>
       <c r="L5" s="38"/>
@@ -12772,7 +12889,7 @@
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
       <c r="J6" s="98" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K6" s="38"/>
       <c r="L6" s="38"/>
@@ -12802,7 +12919,7 @@
       <c r="H7" s="38"/>
       <c r="I7" s="38"/>
       <c r="J7" s="98" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K7" s="38"/>
       <c r="L7" s="38"/>
@@ -13016,7 +13133,7 @@
     <row r="15" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A15" s="67"/>
       <c r="B15" s="63" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C15" s="64"/>
       <c r="D15" s="64"/>
@@ -13098,7 +13215,7 @@
     <row r="18" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A18" s="67"/>
       <c r="B18" s="63" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="68"/>
       <c r="D18" s="64"/>
@@ -13209,7 +13326,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" s="70"/>
       <c r="C22" s="100"/>
@@ -13237,7 +13354,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B23" s="65"/>
       <c r="C23" s="64"/>
@@ -13265,7 +13382,7 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24" s="65"/>
       <c r="C24" s="64"/>
@@ -13293,7 +13410,7 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B25" s="65"/>
       <c r="C25" s="64"/>
@@ -13321,7 +13438,7 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B26" s="65"/>
       <c r="C26" s="64"/>
@@ -13403,7 +13520,7 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="67" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B29" s="70"/>
       <c r="C29" s="100"/>
@@ -13431,7 +13548,7 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B30" s="70"/>
       <c r="C30" s="100"/>
@@ -13459,7 +13576,7 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B31" s="70"/>
       <c r="C31" s="100"/>
@@ -13487,7 +13604,7 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="67" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B32" s="70"/>
       <c r="C32" s="100"/>
@@ -13567,7 +13684,7 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B35" s="70"/>
       <c r="C35" s="100"/>
@@ -13595,7 +13712,7 @@
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="67" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B36" s="70"/>
       <c r="C36" s="100"/>
@@ -13675,7 +13792,7 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="67" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B39" s="65"/>
       <c r="C39" s="64"/>
@@ -14351,47 +14468,47 @@
   <sheetData>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J5" s="67" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N5" s="67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C6">
         <f>COUNTIF(Stats!D:D,'Player Count'!B6)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G6">
         <f>COUNTIF(Stats!D:D,'Player Count'!F6)</f>
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K6">
         <f>COUNTIF(Stats!D:D,'Player Count'!J6)</f>
@@ -14399,7 +14516,7 @@
       </c>
       <c r="M6" s="109"/>
       <c r="N6" s="67" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O6">
         <f>COUNTIF(Stats!D:D,'Player Count'!N6)</f>
@@ -14409,21 +14526,21 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7">
         <f>COUNTIF(Stats!D:D,'Player Count'!B7)</f>
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G7">
         <f>COUNTIF(Stats!D:D,'Player Count'!F7)</f>
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K7">
         <f>COUNTIF(Stats!D:D,'Player Count'!J7)</f>
@@ -14431,7 +14548,7 @@
       </c>
       <c r="M7" s="109"/>
       <c r="N7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O7">
         <f>COUNTIF(Stats!D:D,'Player Count'!N7)</f>
@@ -14441,21 +14558,21 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C8">
         <f>COUNTIF(Stats!D:D,'Player Count'!B8)</f>
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G8">
         <f>COUNTIF(Stats!D:D,'Player Count'!F8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K8">
         <f>COUNTIF(Stats!D:D,'Player Count'!J8)</f>
@@ -14463,7 +14580,7 @@
       </c>
       <c r="M8" s="109"/>
       <c r="N8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O8">
         <f>COUNTIF(Stats!D:D,'Player Count'!N8)</f>
@@ -14473,21 +14590,21 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C9">
         <f>COUNTIF(Stats!D:D,'Player Count'!B9)</f>
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G9">
         <f>COUNTIF(Stats!D:D,'Player Count'!F9)</f>
         <v>1</v>
       </c>
       <c r="J9" s="67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K9">
         <f>COUNTIF(Stats!D:D,'Player Count'!J9)</f>
@@ -14495,7 +14612,7 @@
       </c>
       <c r="M9" s="109"/>
       <c r="N9" s="67" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O9">
         <f>COUNTIF(Stats!D:D,'Player Count'!N9)</f>
@@ -14505,21 +14622,21 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C10">
         <f>COUNTIF(Stats!D:D,'Player Count'!B10)</f>
         <v>3</v>
       </c>
       <c r="F10" s="67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G10">
         <f>COUNTIF(Stats!D:D,'Player Count'!F10)</f>
         <v>1</v>
       </c>
       <c r="J10" s="67" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K10">
         <f>COUNTIF(Stats!D:D,'Player Count'!J10)</f>
@@ -14527,7 +14644,7 @@
       </c>
       <c r="M10" s="109"/>
       <c r="N10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O10">
         <f>COUNTIF(Stats!D:D,'Player Count'!N10)</f>
@@ -14537,21 +14654,21 @@
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="67" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11">
         <f>COUNTIF(Stats!D:D,'Player Count'!B11)</f>
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G11">
         <f>COUNTIF(Stats!D:D,'Player Count'!F11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="67" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K11">
         <f>COUNTIF(Stats!D:D,'Player Count'!J11)</f>
@@ -14559,7 +14676,7 @@
       </c>
       <c r="M11" s="109"/>
       <c r="N11" s="67" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O11">
         <f>COUNTIF(Stats!D:D,'Player Count'!N11)</f>
@@ -14569,21 +14686,21 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C12">
         <f>COUNTIF(Stats!D:D,'Player Count'!B12)</f>
         <v>6</v>
       </c>
       <c r="F12" s="67" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G12">
         <f>COUNTIF(Stats!D:D,'Player Count'!F12)</f>
         <v>1</v>
       </c>
       <c r="J12" s="67" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K12">
         <f>COUNTIF(Stats!D:D,'Player Count'!J12)</f>
@@ -14591,7 +14708,7 @@
       </c>
       <c r="M12" s="109"/>
       <c r="N12" s="67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O12">
         <f>COUNTIF(Stats!D:D,'Player Count'!N12)</f>
@@ -14601,21 +14718,21 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C13">
         <f>COUNTIF(Stats!D:D,'Player Count'!B13)</f>
         <v>4</v>
       </c>
       <c r="F13" s="67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G13">
         <f>COUNTIF(Stats!D:D,'Player Count'!F13)</f>
         <v>0</v>
       </c>
       <c r="J13" s="67" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K13">
         <f>COUNTIF(Stats!D:D,'Player Count'!J13)</f>
@@ -14623,7 +14740,7 @@
       </c>
       <c r="M13" s="109"/>
       <c r="N13" s="67" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O13">
         <f>COUNTIF(Stats!D:D,'Player Count'!N13)</f>
@@ -14633,21 +14750,21 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C14">
         <f>COUNTIF(Stats!D:D,'Player Count'!B14)</f>
         <v>1</v>
       </c>
       <c r="F14" s="67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G14">
         <f>COUNTIF(Stats!D:D,'Player Count'!F14)</f>
         <v>0</v>
       </c>
       <c r="J14" s="67" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K14">
         <f>COUNTIF(Stats!D:D,'Player Count'!J14)</f>
@@ -14655,7 +14772,7 @@
       </c>
       <c r="M14" s="109"/>
       <c r="N14" s="67" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O14">
         <f>COUNTIF(Stats!D:D,'Player Count'!N14)</f>
@@ -14665,29 +14782,29 @@
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15">
         <f>COUNTIF(Stats!D:D,'Player Count'!B15)</f>
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G15">
         <f>COUNTIF(Stats!D:D,'Player Count'!F15)</f>
         <v>3</v>
       </c>
       <c r="J15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K15">
         <f>COUNTIF(Stats!D:D,'Player Count'!J15)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="109"/>
       <c r="N15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O15">
         <f>COUNTIF(Stats!D:D,'Player Count'!N15)</f>
@@ -14697,21 +14814,21 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C16">
         <f>COUNTIF(Stats!D:D,'Player Count'!B16)</f>
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G16">
         <f>COUNTIF(Stats!D:D,'Player Count'!F16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="67" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K16">
         <f>COUNTIF(Stats!D:D,'Player Count'!J16)</f>
@@ -14719,7 +14836,7 @@
       </c>
       <c r="M16" s="109"/>
       <c r="N16" s="67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O16">
         <f>COUNTIF(Stats!D:D,'Player Count'!N16)</f>
@@ -14729,21 +14846,21 @@
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C17">
         <f>COUNTIF(Stats!D:D,'Player Count'!B17)</f>
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G17">
         <f>COUNTIF(Stats!D:D,'Player Count'!F17)</f>
         <v>2</v>
       </c>
       <c r="J17" s="67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K17">
         <f>COUNTIF(Stats!D:D,'Player Count'!J17)</f>
@@ -14751,7 +14868,7 @@
       </c>
       <c r="M17" s="109"/>
       <c r="N17" s="67" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O17">
         <f>COUNTIF(Stats!D:D,'Player Count'!N17)</f>
@@ -14761,21 +14878,21 @@
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18">
         <f>COUNTIF(Stats!D:D,'Player Count'!B18)</f>
         <v>9</v>
       </c>
       <c r="F18" s="67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G18">
         <f>COUNTIF(Stats!D:D,'Player Count'!F18)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K18">
         <f>COUNTIF(Stats!D:D,'Player Count'!J18)</f>
@@ -14783,7 +14900,7 @@
       </c>
       <c r="M18" s="109"/>
       <c r="N18" s="67" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O18">
         <f>COUNTIF(Stats!D:D,'Player Count'!N18)</f>
@@ -14793,21 +14910,21 @@
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19">
         <f>COUNTIF(Stats!D:D,'Player Count'!B19)</f>
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G19">
         <f>COUNTIF(Stats!D:D,'Player Count'!F19)</f>
         <v>1</v>
       </c>
       <c r="J19" s="67" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K19">
         <f>COUNTIF(Stats!D:D,'Player Count'!J19)</f>
@@ -14815,7 +14932,7 @@
       </c>
       <c r="M19" s="109"/>
       <c r="N19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O19">
         <f>COUNTIF(Stats!D:D,'Player Count'!N19)</f>
@@ -14825,21 +14942,21 @@
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C20">
         <f>COUNTIF(Stats!D:D,'Player Count'!B20)</f>
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G20">
         <f>COUNTIF(Stats!D:D,'Player Count'!F20)</f>
         <v>0</v>
       </c>
       <c r="J20" s="67" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K20">
         <f>COUNTIF(Stats!D:D,'Player Count'!J20)</f>
@@ -14847,7 +14964,7 @@
       </c>
       <c r="M20" s="109"/>
       <c r="N20" s="67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O20">
         <f>COUNTIF(Stats!D:D,'Player Count'!N20)</f>
@@ -14857,21 +14974,21 @@
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C21">
         <f>COUNTIF(Stats!D:D,'Player Count'!B21)</f>
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G21">
         <f>COUNTIF(Stats!D:D,'Player Count'!F21)</f>
         <v>2</v>
       </c>
       <c r="J21" s="67" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K21">
         <f>COUNTIF(Stats!D:D,'Player Count'!J21)</f>
@@ -14879,7 +14996,7 @@
       </c>
       <c r="M21" s="109"/>
       <c r="N21" s="67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O21">
         <f>COUNTIF(Stats!D:D,'Player Count'!N21)</f>
@@ -14889,21 +15006,21 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C22">
         <f>COUNTIF(Stats!D:D,'Player Count'!B22)</f>
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G22">
         <f>COUNTIF(Stats!D:D,'Player Count'!F22)</f>
         <v>2</v>
       </c>
       <c r="J22" s="67" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K22">
         <f>COUNTIF(Stats!D:D,'Player Count'!J22)</f>
@@ -14911,7 +15028,7 @@
       </c>
       <c r="M22" s="109"/>
       <c r="N22" s="67" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O22">
         <f>COUNTIF(Stats!D:D,'Player Count'!N22)</f>
@@ -14921,21 +15038,21 @@
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C23">
         <f>COUNTIF(Stats!D:D,'Player Count'!B23)</f>
         <v>4</v>
       </c>
       <c r="F23" s="67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G23">
         <f>COUNTIF(Stats!D:D,'Player Count'!F23)</f>
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K23">
         <f>COUNTIF(Stats!D:D,'Player Count'!J23)</f>
@@ -14943,31 +15060,31 @@
       </c>
       <c r="M23" s="109"/>
       <c r="N23" s="67" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O23">
         <f>COUNTIF(Stats!D:D,'Player Count'!N23)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="109"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" s="67" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C24">
         <f>COUNTIF(Stats!D:D,'Player Count'!B24)</f>
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G24">
         <f>COUNTIF(Stats!D:D,'Player Count'!F24)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" s="67" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K24">
         <f>COUNTIF(Stats!D:D,'Player Count'!J24)</f>
@@ -14975,7 +15092,7 @@
       </c>
       <c r="M24" s="109"/>
       <c r="N24" s="67" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O24">
         <f>COUNTIF(Stats!D:D,'Player Count'!N24)</f>
@@ -14985,21 +15102,21 @@
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="67" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25">
         <f>COUNTIF(Stats!D:D,'Player Count'!B25)</f>
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G25">
         <f>COUNTIF(Stats!D:D,'Player Count'!F25)</f>
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K25">
         <f>COUNTIF(Stats!D:D,'Player Count'!J25)</f>
@@ -15007,7 +15124,7 @@
       </c>
       <c r="M25" s="109"/>
       <c r="N25" s="67" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O25">
         <f>COUNTIF(Stats!D:D,'Player Count'!N25)</f>
@@ -15017,21 +15134,21 @@
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" s="78" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G26">
         <f>COUNTIF(Stats!D:D,'Player Count'!F26)</f>
         <v>2</v>
       </c>
       <c r="J26" s="67" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K26">
         <f>COUNTIF(Stats!D:D,'Player Count'!J26)</f>
@@ -15039,7 +15156,7 @@
       </c>
       <c r="M26" s="109"/>
       <c r="N26" s="67" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O26">
         <f>COUNTIF(Stats!D:D,'Player Count'!N26)</f>
@@ -15049,14 +15166,14 @@
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G27">
         <f>COUNTIF(Stats!D:D,'Player Count'!F27)</f>
         <v>0</v>
       </c>
       <c r="J27" s="67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K27">
         <f>COUNTIF(Stats!D:D,'Player Count'!J27)</f>
@@ -15064,7 +15181,7 @@
       </c>
       <c r="M27" s="109"/>
       <c r="N27" s="67" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O27">
         <f>COUNTIF(Stats!D:D,'Player Count'!N27)</f>
@@ -15074,14 +15191,14 @@
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G28">
         <f>COUNTIF(Stats!D:D,'Player Count'!F28)</f>
         <v>0</v>
       </c>
       <c r="J28" s="67" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K28">
         <f>COUNTIF(Stats!D:D,'Player Count'!J28)</f>
@@ -15089,7 +15206,7 @@
       </c>
       <c r="M28" s="109"/>
       <c r="N28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O28">
         <f>COUNTIF(Stats!D:D,'Player Count'!N28)</f>
@@ -15099,21 +15216,21 @@
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G29">
         <f>COUNTIF(Stats!D:D,'Player Count'!F29)</f>
         <v>2</v>
       </c>
       <c r="J29" s="67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K29">
         <f>COUNTIF(Stats!D:D,'Player Count'!J29)</f>
         <v>0</v>
       </c>
       <c r="N29" s="67" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O29">
         <f>COUNTIF(Stats!D:D,'Player Count'!N29)</f>
@@ -15123,25 +15240,25 @@
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" s="67"/>
       <c r="F30" s="78" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G30" s="78">
         <f>SUM(G6:G29)</f>
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J30" s="78" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N30" s="78" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
@@ -15161,32 +15278,32 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="67" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.44</v>
+        <v>0.42948717948717946</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.22</v>
+        <v>0.24358974358974358</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20666666666666667</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.13333333333333333</v>
+        <v>0.13461538461538461</v>
       </c>
     </row>
   </sheetData>
@@ -15209,55 +15326,55 @@
   <sheetData>
     <row r="5" spans="6:24" x14ac:dyDescent="0.3">
       <c r="G5" s="67" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H5" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="I5" s="67" t="s">
         <v>328</v>
       </c>
-      <c r="I5" s="67" t="s">
+      <c r="J5" s="67" t="s">
         <v>329</v>
       </c>
-      <c r="J5" s="67" t="s">
+      <c r="K5" s="67" t="s">
         <v>330</v>
       </c>
-      <c r="K5" s="67" t="s">
+      <c r="L5" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="L5" s="67" t="s">
+      <c r="M5" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="M5" s="67" t="s">
+      <c r="N5" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="N5" s="67" t="s">
+      <c r="O5" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="O5" s="67" t="s">
+      <c r="P5" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="P5" s="67" t="s">
+      <c r="Q5" s="67" t="s">
         <v>336</v>
       </c>
-      <c r="Q5" s="67" t="s">
+      <c r="R5" s="67" t="s">
         <v>337</v>
       </c>
-      <c r="R5" s="67" t="s">
+      <c r="S5" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="T5" s="67" t="s">
         <v>338</v>
       </c>
-      <c r="S5" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="T5" s="67" t="s">
+      <c r="U5" s="67" t="s">
         <v>339</v>
       </c>
-      <c r="U5" s="67" t="s">
+      <c r="V5" s="67" t="s">
         <v>340</v>
       </c>
-      <c r="V5" s="67" t="s">
-        <v>341</v>
-      </c>
       <c r="W5" s="67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="6:24" x14ac:dyDescent="0.3">
@@ -15303,7 +15420,7 @@
         <v>280</v>
       </c>
       <c r="X6" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="6:24" x14ac:dyDescent="0.3">
@@ -15345,7 +15462,7 @@
         <v>210</v>
       </c>
       <c r="X7" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="6:24" x14ac:dyDescent="0.3">
@@ -15469,7 +15586,7 @@
         <v>-65</v>
       </c>
       <c r="X10" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="6:24" x14ac:dyDescent="0.3">
@@ -15509,7 +15626,7 @@
         <v>-45</v>
       </c>
       <c r="X11" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="6:24" x14ac:dyDescent="0.3">
@@ -15553,7 +15670,7 @@
         <v>5</v>
       </c>
       <c r="X12" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" spans="6:24" x14ac:dyDescent="0.3">
@@ -15587,7 +15704,7 @@
         <v>-35</v>
       </c>
       <c r="X13" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" spans="6:24" x14ac:dyDescent="0.3">
@@ -15629,12 +15746,12 @@
         <v>-45</v>
       </c>
       <c r="X14" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G15" s="113">
         <v>-20</v>
@@ -15714,7 +15831,7 @@
         <v>-60</v>
       </c>
       <c r="X16" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="6:24" x14ac:dyDescent="0.3">
@@ -15754,7 +15871,7 @@
     </row>
     <row r="18" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F18" s="67" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G18" s="113">
         <v>-20</v>
@@ -15783,12 +15900,12 @@
         <v>-35</v>
       </c>
       <c r="X18" s="67" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F19" s="67" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G19" s="113">
         <v>-20</v>

--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="888" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01E68061-4D3E-420B-9472-0F5B5C6967FE}"/>
+  <xr:revisionPtr revIDLastSave="1061" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2D71B1-8827-4AE0-8AB7-3C525667647C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="436">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1184,9 +1185,6 @@
     <t>ZIAN FLEMMING</t>
   </si>
   <si>
-    <t>RENNES</t>
-  </si>
-  <si>
     <t>KASEY PALMER</t>
   </si>
   <si>
@@ -1314,6 +1312,42 @@
   </si>
   <si>
     <t>CYLE LARIN</t>
+  </si>
+  <si>
+    <t>LEE BONIS</t>
+  </si>
+  <si>
+    <t>CHESTERFIELD</t>
+  </si>
+  <si>
+    <t>JULIAN ALVAREZ</t>
+  </si>
+  <si>
+    <t>ATLETICO MADRID</t>
+  </si>
+  <si>
+    <t>KEANE LEWIS-POTTER</t>
+  </si>
+  <si>
+    <t>NICHOLAS JACKSON</t>
+  </si>
+  <si>
+    <t>BRADLEY BARCOLA</t>
+  </si>
+  <si>
+    <t>LEO SCIENZA</t>
+  </si>
+  <si>
+    <t>OMAR MARMOUSH</t>
+  </si>
+  <si>
+    <t>BLACKPOOL</t>
+  </si>
+  <si>
+    <t>CHARLIE LAKIN</t>
+  </si>
+  <si>
+    <t>YOANNE WISSA</t>
   </si>
 </sst>
 </file>
@@ -1734,7 +1768,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2025,6 +2059,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3318,11 +3364,11 @@
       <c r="O4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
     </row>
     <row r="5" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
@@ -3337,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="83"/>
       <c r="H5" s="84"/>
@@ -3353,15 +3399,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3392,11 +3438,11 @@
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3423,15 +3469,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3467,15 +3513,15 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3509,15 +3555,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3545,17 +3591,17 @@
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>0</v>
-      </c>
-      <c r="R10" s="114"/>
-      <c r="S10" s="114"/>
-      <c r="T10" s="114"/>
-      <c r="U10" s="114"/>
-      <c r="V10" s="114"/>
+        <v>5</v>
+      </c>
+      <c r="R10" s="118"/>
+      <c r="S10" s="118"/>
+      <c r="T10" s="118"/>
+      <c r="U10" s="118"/>
+      <c r="V10" s="118"/>
     </row>
     <row r="11" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="79"/>
@@ -3572,7 +3618,7 @@
         <v>8</v>
       </c>
       <c r="F11" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="87"/>
       <c r="H11" s="84"/>
@@ -3588,15 +3634,15 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -3620,7 +3666,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="87" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H12" s="84">
         <v>46261</v>
@@ -3637,15 +3683,15 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3654,13 +3700,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F13" s="30">
         <v>0</v>
@@ -3681,21 +3727,21 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
         <v>0</v>
       </c>
-      <c r="R13" s="114"/>
-      <c r="S13" s="114"/>
-      <c r="T13" s="114"/>
-      <c r="U13" s="114"/>
-      <c r="V13" s="114"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="118"/>
+      <c r="T13" s="118"/>
+      <c r="U13" s="118"/>
+      <c r="V13" s="118"/>
     </row>
     <row r="14" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="79"/>
@@ -3728,15 +3774,15 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -3763,7 +3809,7 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
@@ -3771,7 +3817,7 @@
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3809,11 +3855,11 @@
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3831,7 +3877,7 @@
         <v>28</v>
       </c>
       <c r="F17" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="84"/>
       <c r="H17" s="84"/>
@@ -3847,21 +3893,21 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>2</v>
-      </c>
-      <c r="R17" s="114"/>
-      <c r="S17" s="114"/>
-      <c r="T17" s="114"/>
-      <c r="U17" s="114"/>
-      <c r="V17" s="114"/>
+        <v>4</v>
+      </c>
+      <c r="R17" s="118"/>
+      <c r="S17" s="118"/>
+      <c r="T17" s="118"/>
+      <c r="U17" s="118"/>
+      <c r="V17" s="118"/>
     </row>
     <row r="18" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="79"/>
@@ -3878,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="83"/>
       <c r="H18" s="84"/>
@@ -3894,15 +3940,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -3923,7 +3969,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G19" s="87"/>
       <c r="H19" s="84"/>
@@ -3953,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="87" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H20" s="84">
         <v>46261</v>
@@ -3965,11 +4011,11 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="114"/>
-      <c r="U20" s="114"/>
-      <c r="V20" s="114"/>
+      <c r="R20" s="118"/>
+      <c r="S20" s="118"/>
+      <c r="T20" s="118"/>
+      <c r="U20" s="118"/>
+      <c r="V20" s="118"/>
     </row>
     <row r="21" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79"/>
@@ -3977,16 +4023,16 @@
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F21" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="87">
         <v>46261</v>
@@ -4053,11 +4099,11 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-      <c r="R24" s="114"/>
-      <c r="S24" s="114"/>
-      <c r="T24" s="114"/>
-      <c r="U24" s="114"/>
-      <c r="V24" s="114"/>
+      <c r="R24" s="118"/>
+      <c r="S24" s="118"/>
+      <c r="T24" s="118"/>
+      <c r="U24" s="118"/>
+      <c r="V24" s="118"/>
     </row>
     <row r="25" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="79"/>
@@ -4090,7 +4136,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4135,11 +4181,11 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-      <c r="R28" s="114"/>
-      <c r="S28" s="114"/>
-      <c r="T28" s="114"/>
-      <c r="U28" s="114"/>
-      <c r="V28" s="114"/>
+      <c r="R28" s="118"/>
+      <c r="S28" s="118"/>
+      <c r="T28" s="118"/>
+      <c r="U28" s="118"/>
+      <c r="V28" s="118"/>
     </row>
     <row r="29" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -4219,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32" s="80"/>
       <c r="H32" s="94"/>
@@ -4362,11 +4408,11 @@
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
-      <c r="R38" s="114"/>
-      <c r="S38" s="114"/>
-      <c r="T38" s="114"/>
-      <c r="U38" s="114"/>
-      <c r="V38" s="114"/>
+      <c r="R38" s="118"/>
+      <c r="S38" s="118"/>
+      <c r="T38" s="118"/>
+      <c r="U38" s="118"/>
+      <c r="V38" s="118"/>
     </row>
     <row r="39" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="79"/>
@@ -4383,7 +4429,7 @@
         <v>11</v>
       </c>
       <c r="F39" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -4410,7 +4456,7 @@
         <v>43</v>
       </c>
       <c r="F40" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="87"/>
       <c r="H40" s="91"/>
@@ -4498,7 +4544,7 @@
         <v>7</v>
       </c>
       <c r="F44" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="87"/>
       <c r="H44" s="91"/>
@@ -4512,23 +4558,27 @@
     </row>
     <row r="45" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="79"/>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="106" t="s">
         <v>134</v>
       </c>
-      <c r="D45" s="28" t="s">
+      <c r="D45" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="107">
         <v>1</v>
       </c>
-      <c r="F45" s="30">
+      <c r="F45" s="108">
         <v>0</v>
       </c>
-      <c r="G45" s="87"/>
-      <c r="H45" s="91"/>
+      <c r="G45" s="87" t="s">
+        <v>417</v>
+      </c>
+      <c r="H45" s="91">
+        <v>46261</v>
+      </c>
       <c r="I45" s="89"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -4543,18 +4593,20 @@
         <v>17</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>287</v>
+        <v>429</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E46" s="29">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="E46" s="29" t="s">
+        <v>416</v>
       </c>
       <c r="F46" s="30">
         <v>0</v>
       </c>
-      <c r="G46" s="91"/>
+      <c r="G46" s="91">
+        <v>46261</v>
+      </c>
       <c r="H46" s="91"/>
       <c r="I46" s="89"/>
       <c r="J46" s="76"/>
@@ -4570,13 +4622,13 @@
         <v>17</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>160</v>
+        <v>287</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>355</v>
+        <v>90</v>
       </c>
       <c r="E47" s="29">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F47" s="30">
         <v>0</v>
@@ -4593,11 +4645,21 @@
     </row>
     <row r="48" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="79"/>
-      <c r="B48" s="106"/>
-      <c r="C48" s="106"/>
-      <c r="D48" s="106"/>
-      <c r="E48" s="107"/>
-      <c r="F48" s="108"/>
+      <c r="B48" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E48" s="29">
+        <v>2</v>
+      </c>
+      <c r="F48" s="30">
+        <v>1</v>
+      </c>
       <c r="G48" s="91"/>
       <c r="H48" s="91"/>
       <c r="I48" s="89"/>
@@ -4800,21 +4862,25 @@
     </row>
     <row r="59" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="79"/>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="C59" s="13"/>
-      <c r="D59" s="12" t="s">
+      <c r="C59" s="115"/>
+      <c r="D59" s="114" t="s">
         <v>164</v>
       </c>
-      <c r="E59" s="14">
+      <c r="E59" s="116">
         <v>5</v>
       </c>
-      <c r="F59" s="15">
-        <v>5</v>
-      </c>
-      <c r="G59" s="80"/>
-      <c r="H59" s="92"/>
+      <c r="F59" s="117">
+        <v>10</v>
+      </c>
+      <c r="G59" s="80" t="s">
+        <v>417</v>
+      </c>
+      <c r="H59" s="94">
+        <v>46268</v>
+      </c>
       <c r="I59" s="92"/>
       <c r="J59" s="76"/>
       <c r="K59" s="1"/>
@@ -4825,12 +4891,22 @@
     </row>
     <row r="60" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="79"/>
-      <c r="B60" s="21"/>
+      <c r="B60" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="80"/>
+      <c r="D60" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="F60" s="21">
+        <v>0</v>
+      </c>
+      <c r="G60" s="86">
+        <v>46268</v>
+      </c>
       <c r="H60" s="92"/>
       <c r="I60" s="92"/>
       <c r="J60" s="90"/>
@@ -4930,23 +5006,27 @@
     </row>
     <row r="65" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="79"/>
-      <c r="B65" s="28" t="s">
+      <c r="B65" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="C65" s="106" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D65" s="106" t="s">
         <v>132</v>
       </c>
-      <c r="E65" s="29">
+      <c r="E65" s="107">
         <v>10</v>
       </c>
-      <c r="F65" s="30">
+      <c r="F65" s="108">
         <v>0</v>
       </c>
-      <c r="G65" s="83"/>
-      <c r="H65" s="90"/>
+      <c r="G65" s="83" t="s">
+        <v>417</v>
+      </c>
+      <c r="H65" s="91">
+        <v>46261</v>
+      </c>
       <c r="I65" s="90"/>
       <c r="J65" s="76"/>
       <c r="K65" s="1"/>
@@ -4961,18 +5041,20 @@
         <v>16</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>28</v>
+        <v>432</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="E66" s="29">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="E66" s="29" t="s">
+        <v>416</v>
       </c>
       <c r="F66" s="30">
         <v>0</v>
       </c>
-      <c r="G66" s="83"/>
+      <c r="G66" s="87">
+        <v>46261</v>
+      </c>
       <c r="H66" s="91"/>
       <c r="I66" s="90"/>
       <c r="J66" s="76"/>
@@ -4988,18 +5070,18 @@
         <v>16</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>356</v>
+        <v>28</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E67" s="29">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F67" s="30">
-        <v>0</v>
-      </c>
-      <c r="G67" s="87"/>
+        <v>3</v>
+      </c>
+      <c r="G67" s="83"/>
       <c r="H67" s="91"/>
       <c r="I67" s="90"/>
       <c r="J67" s="76"/>
@@ -5011,13 +5093,27 @@
     </row>
     <row r="68" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="79"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="91"/>
-      <c r="H68" s="91"/>
+      <c r="B68" s="106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="106" t="s">
+        <v>356</v>
+      </c>
+      <c r="D68" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="E68" s="107">
+        <v>1</v>
+      </c>
+      <c r="F68" s="108">
+        <v>0</v>
+      </c>
+      <c r="G68" s="87" t="s">
+        <v>417</v>
+      </c>
+      <c r="H68" s="91">
+        <v>46261</v>
+      </c>
       <c r="I68" s="90"/>
       <c r="J68" s="76"/>
       <c r="K68" s="1"/>
@@ -5028,12 +5124,24 @@
     </row>
     <row r="69" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="79"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="87"/>
+      <c r="B69" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>431</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E69" s="29" t="s">
+        <v>416</v>
+      </c>
+      <c r="F69" s="30">
+        <v>1</v>
+      </c>
+      <c r="G69" s="91">
+        <v>46261</v>
+      </c>
       <c r="H69" s="91"/>
       <c r="I69" s="90"/>
       <c r="J69" s="76"/>
@@ -5058,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="F70" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" s="87"/>
       <c r="H70" s="91"/>
@@ -5085,7 +5193,7 @@
         <v>23</v>
       </c>
       <c r="F71" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="83"/>
       <c r="H71" s="91"/>
@@ -5139,7 +5247,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" s="87"/>
       <c r="H73" s="91"/>
@@ -5274,7 +5382,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -5398,7 +5506,7 @@
         <v>4</v>
       </c>
       <c r="F86" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
@@ -5584,7 +5692,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94" s="91"/>
       <c r="H94" s="91"/>
@@ -5672,7 +5780,7 @@
         <v>7</v>
       </c>
       <c r="F98" s="30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G98" s="87"/>
       <c r="H98" s="91"/>
@@ -5690,7 +5798,7 @@
         <v>17</v>
       </c>
       <c r="C99" s="106" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D99" s="106" t="s">
         <v>31</v>
@@ -5702,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="87" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H99" s="91">
         <v>46247</v>
@@ -5721,13 +5829,13 @@
         <v>17</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D100" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E100" s="29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F100" s="30">
         <v>0</v>
@@ -5762,7 +5870,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="87" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H101" s="91">
         <v>46254</v>
@@ -5781,13 +5889,13 @@
         <v>17</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D102" s="28" t="s">
         <v>53</v>
       </c>
       <c r="E102" s="29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F102" s="30">
         <v>1</v>
@@ -5893,7 +6001,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6017,7 +6125,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -6190,23 +6298,27 @@
     </row>
     <row r="121" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="79"/>
-      <c r="B121" s="28" t="s">
+      <c r="B121" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C121" s="28" t="s">
+      <c r="C121" s="106" t="s">
         <v>117</v>
       </c>
-      <c r="D121" s="28" t="s">
+      <c r="D121" s="106" t="s">
         <v>294</v>
       </c>
-      <c r="E121" s="29">
+      <c r="E121" s="107">
         <v>1</v>
       </c>
-      <c r="F121" s="30">
+      <c r="F121" s="108">
         <v>0</v>
       </c>
-      <c r="G121" s="86"/>
-      <c r="H121" s="94"/>
+      <c r="G121" s="86" t="s">
+        <v>417</v>
+      </c>
+      <c r="H121" s="94">
+        <v>46261</v>
+      </c>
       <c r="I121" s="90"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
@@ -6217,12 +6329,24 @@
     </row>
     <row r="122" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="79"/>
-      <c r="B122" s="28"/>
-      <c r="C122" s="28"/>
-      <c r="D122" s="28"/>
-      <c r="E122" s="29"/>
-      <c r="F122" s="30"/>
-      <c r="G122" s="87"/>
+      <c r="B122" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" s="28" t="s">
+        <v>430</v>
+      </c>
+      <c r="D122" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E122" s="29" t="s">
+        <v>416</v>
+      </c>
+      <c r="F122" s="30">
+        <v>0</v>
+      </c>
+      <c r="G122" s="87">
+        <v>46261</v>
+      </c>
       <c r="H122" s="91"/>
       <c r="I122" s="90"/>
       <c r="J122" s="76"/>
@@ -6278,23 +6402,27 @@
     </row>
     <row r="125" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="79"/>
-      <c r="B125" s="28" t="s">
+      <c r="B125" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C125" s="28" t="s">
+      <c r="C125" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="D125" s="28" t="s">
+      <c r="D125" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="E125" s="29">
+      <c r="E125" s="107">
         <v>38</v>
       </c>
-      <c r="F125" s="30">
+      <c r="F125" s="108">
         <v>0</v>
       </c>
-      <c r="G125" s="87"/>
-      <c r="H125" s="91"/>
+      <c r="G125" s="87" t="s">
+        <v>417</v>
+      </c>
+      <c r="H125" s="91">
+        <v>46261</v>
+      </c>
       <c r="I125" s="90"/>
       <c r="J125" s="76"/>
       <c r="K125" s="1"/>
@@ -6309,18 +6437,20 @@
         <v>17</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>270</v>
+        <v>424</v>
       </c>
       <c r="D126" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E126" s="29">
-        <v>20</v>
+        <v>425</v>
+      </c>
+      <c r="E126" s="29" t="s">
+        <v>416</v>
       </c>
       <c r="F126" s="30">
         <v>0</v>
       </c>
-      <c r="G126" s="87"/>
+      <c r="G126" s="87">
+        <v>46261</v>
+      </c>
       <c r="H126" s="91"/>
       <c r="I126" s="90"/>
       <c r="J126" s="76"/>
@@ -6336,16 +6466,16 @@
         <v>17</v>
       </c>
       <c r="C127" s="28" t="s">
-        <v>112</v>
+        <v>270</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>204</v>
+        <v>98</v>
       </c>
       <c r="E127" s="29">
+        <v>20</v>
+      </c>
+      <c r="F127" s="30">
         <v>1</v>
-      </c>
-      <c r="F127" s="30">
-        <v>0</v>
       </c>
       <c r="G127" s="87"/>
       <c r="H127" s="91"/>
@@ -6363,10 +6493,10 @@
         <v>17</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="D128" s="28" t="s">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="E128" s="29">
         <v>1</v>
@@ -6386,11 +6516,21 @@
     </row>
     <row r="129" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="79"/>
-      <c r="B129" s="106"/>
-      <c r="C129" s="106"/>
-      <c r="D129" s="106"/>
-      <c r="E129" s="107"/>
-      <c r="F129" s="108"/>
+      <c r="B129" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="D129" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="E129" s="29">
+        <v>1</v>
+      </c>
+      <c r="F129" s="30">
+        <v>0</v>
+      </c>
       <c r="G129" s="87"/>
       <c r="H129" s="91"/>
       <c r="I129" s="90"/>
@@ -6480,7 +6620,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -6604,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="F140" s="15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G140" s="80"/>
       <c r="H140" s="94"/>
@@ -6730,7 +6870,7 @@
         <v>369</v>
       </c>
       <c r="D146" s="28" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E146" s="29">
         <v>1</v>
@@ -6763,7 +6903,7 @@
         <v>6</v>
       </c>
       <c r="F147" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G147" s="87"/>
       <c r="H147" s="91"/>
@@ -6905,7 +7045,7 @@
         <v>13</v>
       </c>
       <c r="F153" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G153" s="87"/>
       <c r="H153" s="91"/>
@@ -6932,7 +7072,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G154" s="87"/>
       <c r="H154" s="91"/>
@@ -6946,23 +7086,27 @@
     </row>
     <row r="155" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="79"/>
-      <c r="B155" s="28" t="s">
+      <c r="B155" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C155" s="28" t="s">
+      <c r="C155" s="106" t="s">
         <v>371</v>
       </c>
-      <c r="D155" s="28" t="s">
+      <c r="D155" s="106" t="s">
         <v>204</v>
       </c>
-      <c r="E155" s="29">
+      <c r="E155" s="107">
         <v>10</v>
       </c>
-      <c r="F155" s="30">
+      <c r="F155" s="108">
         <v>0</v>
       </c>
-      <c r="G155" s="87"/>
-      <c r="H155" s="91"/>
+      <c r="G155" s="87" t="s">
+        <v>417</v>
+      </c>
+      <c r="H155" s="91">
+        <v>46261</v>
+      </c>
       <c r="I155" s="90"/>
       <c r="J155" s="76"/>
       <c r="K155" s="1"/>
@@ -6973,12 +7117,24 @@
     </row>
     <row r="156" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="79"/>
-      <c r="B156" s="106"/>
-      <c r="C156" s="106"/>
-      <c r="D156" s="106"/>
-      <c r="E156" s="107"/>
-      <c r="F156" s="108"/>
-      <c r="G156" s="87"/>
+      <c r="B156" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" s="28" t="s">
+        <v>426</v>
+      </c>
+      <c r="D156" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="E156" s="29" t="s">
+        <v>416</v>
+      </c>
+      <c r="F156" s="30">
+        <v>0</v>
+      </c>
+      <c r="G156" s="87">
+        <v>46261</v>
+      </c>
       <c r="H156" s="91"/>
       <c r="I156" s="90"/>
       <c r="J156" s="76"/>
@@ -7191,7 +7347,7 @@
         <v>4</v>
       </c>
       <c r="F167" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G167" s="80"/>
       <c r="H167" s="94"/>
@@ -7273,7 +7429,7 @@
         <v>122</v>
       </c>
       <c r="D171" s="28" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="E171" s="29">
         <v>4</v>
@@ -7350,7 +7506,7 @@
         <v>12</v>
       </c>
       <c r="F174" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" s="91"/>
       <c r="H174" s="91"/>
@@ -7377,7 +7533,7 @@
         <v>8</v>
       </c>
       <c r="F175" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G175" s="87"/>
       <c r="H175" s="91"/>
@@ -7654,7 +7810,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -7704,7 +7860,7 @@
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>343</v>
@@ -7778,7 +7934,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -7910,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="F200" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" s="83"/>
       <c r="H200" s="90"/>
@@ -7937,7 +8093,7 @@
         <v>4</v>
       </c>
       <c r="F201" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G201" s="83"/>
       <c r="H201" s="90"/>
@@ -8028,7 +8184,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="83" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H205" s="91">
         <v>46254</v>
@@ -8047,13 +8203,13 @@
         <v>17</v>
       </c>
       <c r="C206" s="28" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D206" s="28" t="s">
         <v>62</v>
       </c>
       <c r="E206" s="29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F206" s="30">
         <v>0</v>
@@ -8085,7 +8241,7 @@
         <v>10</v>
       </c>
       <c r="F207" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" s="83"/>
       <c r="H207" s="90"/>
@@ -8112,7 +8268,7 @@
         <v>5</v>
       </c>
       <c r="F208" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" s="83"/>
       <c r="H208" s="91"/>
@@ -8139,7 +8295,7 @@
         <v>49</v>
       </c>
       <c r="F209" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G209" s="87"/>
       <c r="H209" s="91"/>
@@ -8257,7 +8413,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -8436,7 +8592,7 @@
         <v>376</v>
       </c>
       <c r="D224" s="28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E224" s="29">
         <v>1</v>
@@ -8628,7 +8784,7 @@
         <v>11</v>
       </c>
       <c r="F232" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" s="87"/>
       <c r="H232" s="91"/>
@@ -8736,7 +8892,7 @@
         <v>13</v>
       </c>
       <c r="F236" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G236" s="83"/>
       <c r="H236" s="91"/>
@@ -8844,7 +9000,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -8968,7 +9124,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G248" s="80"/>
       <c r="H248" s="94"/>
@@ -9148,13 +9304,13 @@
         <v>293</v>
       </c>
       <c r="D256" s="28" t="s">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="E256" s="29">
         <v>1</v>
       </c>
       <c r="F256" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G256" s="87"/>
       <c r="H256" s="91"/>
@@ -9431,7 +9587,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -9555,7 +9711,7 @@
         <v>1</v>
       </c>
       <c r="F275" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G275" s="80"/>
       <c r="H275" s="94"/>
@@ -9607,7 +9763,7 @@
         <v>14</v>
       </c>
       <c r="C278" s="28" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D278" s="28" t="s">
         <v>294</v>
@@ -9634,7 +9790,7 @@
         <v>14</v>
       </c>
       <c r="C279" s="28" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D279" s="28" t="s">
         <v>104</v>
@@ -9678,7 +9834,7 @@
         <v>16</v>
       </c>
       <c r="C281" s="28" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D281" s="28" t="s">
         <v>19</v>
@@ -9705,7 +9861,7 @@
         <v>16</v>
       </c>
       <c r="C282" s="28" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D282" s="28" t="s">
         <v>294</v>
@@ -9732,7 +9888,7 @@
         <v>16</v>
       </c>
       <c r="C283" s="28" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D283" s="28" t="s">
         <v>52</v>
@@ -9820,7 +9976,7 @@
         <v>17</v>
       </c>
       <c r="C287" s="28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D287" s="28" t="s">
         <v>102</v>
@@ -10018,7 +10174,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -10129,23 +10285,27 @@
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
     </row>
-    <row r="302" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A302" s="79"/>
-      <c r="B302" s="12" t="s">
+      <c r="B302" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="C302" s="13"/>
-      <c r="D302" s="12" t="s">
+      <c r="C302" s="115"/>
+      <c r="D302" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="E302" s="14">
+      <c r="E302" s="116">
         <v>1</v>
       </c>
-      <c r="F302" s="15">
-        <v>5</v>
-      </c>
-      <c r="G302" s="80"/>
-      <c r="H302" s="91"/>
+      <c r="F302" s="117">
+        <v>6</v>
+      </c>
+      <c r="G302" s="80" t="s">
+        <v>417</v>
+      </c>
+      <c r="H302" s="91">
+        <v>46261</v>
+      </c>
       <c r="I302" s="92"/>
       <c r="J302" s="1"/>
       <c r="K302" s="1"/>
@@ -10156,12 +10316,22 @@
     </row>
     <row r="303" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="79"/>
-      <c r="B303" s="21"/>
+      <c r="B303" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="C303" s="21"/>
-      <c r="D303" s="21"/>
-      <c r="E303" s="22"/>
-      <c r="F303" s="21"/>
-      <c r="G303" s="87"/>
+      <c r="D303" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E303" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="F303" s="21">
+        <v>1</v>
+      </c>
+      <c r="G303" s="87">
+        <v>46261</v>
+      </c>
       <c r="H303" s="91"/>
       <c r="I303" s="92"/>
       <c r="J303" s="1"/>
@@ -10221,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="C306" s="28" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D306" s="28" t="s">
         <v>162</v>
@@ -10265,7 +10435,7 @@
         <v>16</v>
       </c>
       <c r="C308" s="28" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D308" s="28" t="s">
         <v>95</v>
@@ -10292,7 +10462,7 @@
         <v>16</v>
       </c>
       <c r="C309" s="28" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D309" s="28" t="s">
         <v>132</v>
@@ -10319,7 +10489,7 @@
         <v>16</v>
       </c>
       <c r="C310" s="28" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D310" s="77" t="s">
         <v>268</v>
@@ -10389,7 +10559,7 @@
         <v>78</v>
       </c>
       <c r="F313" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -10407,7 +10577,7 @@
         <v>17</v>
       </c>
       <c r="C314" s="28" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D314" s="28" t="s">
         <v>294</v>
@@ -10488,7 +10658,7 @@
         <v>17</v>
       </c>
       <c r="C317" s="28" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D317" s="28" t="s">
         <v>280</v>
@@ -10729,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -10777,23 +10947,27 @@
     </row>
     <row r="332" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="79"/>
-      <c r="B332" s="28" t="s">
+      <c r="B332" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="C332" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="D332" s="28" t="s">
-        <v>410</v>
-      </c>
-      <c r="E332" s="29">
+      <c r="C332" s="106" t="s">
+        <v>387</v>
+      </c>
+      <c r="D332" s="106" t="s">
+        <v>409</v>
+      </c>
+      <c r="E332" s="107">
         <v>2</v>
       </c>
-      <c r="F332" s="30">
+      <c r="F332" s="108">
         <v>0</v>
       </c>
-      <c r="G332" s="83"/>
-      <c r="H332" s="90"/>
+      <c r="G332" s="83" t="s">
+        <v>417</v>
+      </c>
+      <c r="H332" s="91">
+        <v>46261</v>
+      </c>
       <c r="I332" s="90"/>
       <c r="J332" s="1"/>
       <c r="K332" s="1"/>
@@ -10808,18 +10982,20 @@
         <v>14</v>
       </c>
       <c r="C333" s="28" t="s">
-        <v>387</v>
+        <v>428</v>
       </c>
       <c r="D333" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E333" s="29">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="E333" s="29" t="s">
+        <v>416</v>
       </c>
       <c r="F333" s="30">
         <v>0</v>
       </c>
-      <c r="G333" s="83"/>
+      <c r="G333" s="87">
+        <v>46261</v>
+      </c>
       <c r="H333" s="90"/>
       <c r="I333" s="90"/>
       <c r="J333" s="1"/>
@@ -10831,11 +11007,21 @@
     </row>
     <row r="334" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="79"/>
-      <c r="B334" s="28"/>
-      <c r="C334" s="28"/>
-      <c r="D334" s="28"/>
-      <c r="E334" s="29"/>
-      <c r="F334" s="30"/>
+      <c r="B334" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C334" s="28" t="s">
+        <v>386</v>
+      </c>
+      <c r="D334" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E334" s="29">
+        <v>1</v>
+      </c>
+      <c r="F334" s="30">
+        <v>0</v>
+      </c>
       <c r="G334" s="87"/>
       <c r="H334" s="91"/>
       <c r="I334" s="90"/>
@@ -10852,7 +11038,7 @@
         <v>16</v>
       </c>
       <c r="C335" s="28" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D335" s="28" t="s">
         <v>162</v>
@@ -10879,7 +11065,7 @@
         <v>16</v>
       </c>
       <c r="C336" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D336" s="28" t="s">
         <v>124</v>
@@ -10909,7 +11095,7 @@
         <v>317</v>
       </c>
       <c r="D337" s="28" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E337" s="29">
         <v>1</v>
@@ -10973,7 +11159,7 @@
         <v>9</v>
       </c>
       <c r="F340" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G340" s="87"/>
       <c r="H340" s="90"/>
@@ -10988,7 +11174,7 @@
         <v>17</v>
       </c>
       <c r="C341" s="28" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D341" s="28" t="s">
         <v>348</v>
@@ -11012,7 +11198,7 @@
         <v>17</v>
       </c>
       <c r="C342" s="28" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D342" s="28" t="s">
         <v>141</v>
@@ -11021,7 +11207,7 @@
         <v>12</v>
       </c>
       <c r="F342" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G342" s="87"/>
       <c r="H342" s="91"/>
@@ -11036,7 +11222,7 @@
         <v>17</v>
       </c>
       <c r="C343" s="28" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D343" s="28" t="s">
         <v>23</v>
@@ -11045,7 +11231,7 @@
         <v>1</v>
       </c>
       <c r="F343" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G343" s="87"/>
       <c r="H343" s="91"/>
@@ -11060,10 +11246,10 @@
         <v>17</v>
       </c>
       <c r="C344" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="D344" s="28" t="s">
         <v>395</v>
-      </c>
-      <c r="D344" s="28" t="s">
-        <v>396</v>
       </c>
       <c r="E344" s="29">
         <v>40</v>
@@ -11159,7 +11345,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -11241,7 +11427,7 @@
         <v>3</v>
       </c>
       <c r="F356" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -11275,7 +11461,7 @@
         <v>14</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D359" s="28" t="s">
         <v>24</v>
@@ -11296,7 +11482,7 @@
         <v>14</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D360" s="28" t="s">
         <v>18</v>
@@ -11337,7 +11523,7 @@
         <v>15</v>
       </c>
       <c r="F362" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G362" s="1"/>
       <c r="H362" s="103"/>
@@ -11366,33 +11552,49 @@
       <c r="J363" s="1"/>
     </row>
     <row r="364" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B364" s="28" t="s">
+      <c r="B364" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C364" s="28" t="s">
-        <v>399</v>
-      </c>
-      <c r="D364" s="28" t="s">
+      <c r="C364" s="106" t="s">
+        <v>398</v>
+      </c>
+      <c r="D364" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="E364" s="29">
+      <c r="E364" s="107">
         <v>1</v>
       </c>
-      <c r="F364" s="30">
+      <c r="F364" s="108">
         <v>0</v>
       </c>
-      <c r="G364" s="103"/>
-      <c r="H364" s="103"/>
+      <c r="G364" s="103" t="s">
+        <v>417</v>
+      </c>
+      <c r="H364" s="103">
+        <v>46268</v>
+      </c>
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
     </row>
     <row r="365" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B365" s="28"/>
-      <c r="C365" s="28"/>
-      <c r="D365" s="28"/>
-      <c r="E365" s="29"/>
-      <c r="F365" s="30"/>
-      <c r="G365" s="103"/>
+      <c r="B365" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C365" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="D365" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E365" s="29" t="s">
+        <v>416</v>
+      </c>
+      <c r="F365" s="30">
+        <v>0</v>
+      </c>
+      <c r="G365" s="103">
+        <v>46268</v>
+      </c>
       <c r="H365" s="103"/>
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
@@ -11430,23 +11632,27 @@
       <c r="J367" s="1"/>
     </row>
     <row r="368" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B368" s="28" t="s">
+      <c r="B368" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C368" s="28" t="s">
+      <c r="C368" s="106" t="s">
         <v>131</v>
       </c>
-      <c r="D368" s="28" t="s">
+      <c r="D368" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="E368" s="29">
+      <c r="E368" s="107">
         <v>10</v>
       </c>
-      <c r="F368" s="30">
+      <c r="F368" s="108">
         <v>0</v>
       </c>
-      <c r="G368" s="103"/>
-      <c r="H368" s="103"/>
+      <c r="G368" s="103" t="s">
+        <v>417</v>
+      </c>
+      <c r="H368" s="103">
+        <v>46268</v>
+      </c>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
     </row>
@@ -11455,67 +11661,67 @@
         <v>17</v>
       </c>
       <c r="C369" s="28" t="s">
-        <v>278</v>
+        <v>435</v>
       </c>
       <c r="D369" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="E369" s="29">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="E369" s="29" t="s">
+        <v>416</v>
       </c>
       <c r="F369" s="30">
         <v>0</v>
       </c>
-      <c r="G369" s="103"/>
+      <c r="G369" s="103">
+        <v>46268</v>
+      </c>
       <c r="H369" s="103"/>
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
     </row>
     <row r="370" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B370" s="106" t="s">
+      <c r="B370" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C370" s="106" t="s">
-        <v>400</v>
-      </c>
-      <c r="D370" s="106" t="s">
-        <v>401</v>
-      </c>
-      <c r="E370" s="107">
+      <c r="C370" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="D370" s="28" t="s">
+        <v>355</v>
+      </c>
+      <c r="E370" s="29">
         <v>1</v>
       </c>
-      <c r="F370" s="108">
-        <v>0</v>
-      </c>
-      <c r="G370" s="103" t="s">
-        <v>418</v>
-      </c>
-      <c r="H370" s="103">
-        <v>46254</v>
-      </c>
+      <c r="F370" s="30">
+        <v>1</v>
+      </c>
+      <c r="G370" s="103"/>
+      <c r="H370" s="103"/>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
     </row>
     <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B371" s="28" t="s">
+      <c r="B371" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C371" s="28" t="s">
-        <v>421</v>
-      </c>
-      <c r="D371" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E371" s="29" t="s">
+      <c r="C371" s="106" t="s">
+        <v>399</v>
+      </c>
+      <c r="D371" s="106" t="s">
+        <v>400</v>
+      </c>
+      <c r="E371" s="107">
+        <v>1</v>
+      </c>
+      <c r="F371" s="108">
+        <v>0</v>
+      </c>
+      <c r="G371" s="103" t="s">
         <v>417</v>
       </c>
-      <c r="F371" s="30">
-        <v>0</v>
-      </c>
-      <c r="G371" s="103">
+      <c r="H371" s="103">
         <v>46254</v>
       </c>
-      <c r="H371" s="103"/>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
     </row>
@@ -11524,28 +11730,40 @@
         <v>17</v>
       </c>
       <c r="C372" s="28" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="D372" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="E372" s="29">
-        <v>20</v>
+        <v>73</v>
+      </c>
+      <c r="E372" s="29" t="s">
+        <v>416</v>
       </c>
       <c r="F372" s="30">
         <v>0</v>
       </c>
-      <c r="G372" s="103"/>
+      <c r="G372" s="103">
+        <v>46254</v>
+      </c>
       <c r="H372" s="103"/>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
     </row>
     <row r="373" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B373" s="28"/>
-      <c r="C373" s="28"/>
-      <c r="D373" s="28"/>
-      <c r="E373" s="29"/>
-      <c r="F373" s="30"/>
+      <c r="B373" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C373" s="28" t="s">
+        <v>401</v>
+      </c>
+      <c r="D373" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="E373" s="29">
+        <v>20</v>
+      </c>
+      <c r="F373" s="30">
+        <v>0</v>
+      </c>
       <c r="G373" s="103"/>
       <c r="H373" s="103"/>
       <c r="I373" s="1"/>
@@ -11594,7 +11812,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -11887,7 +12105,7 @@
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
       <c r="D4" s="43" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="41"/>
@@ -11941,19 +12159,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E7" s="25">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F7" s="26">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G7" s="27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="111"/>
       <c r="I7" s="41"/>
@@ -11966,19 +12184,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>135</v>
+        <v>30</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>29</v>
       </c>
       <c r="E8" s="25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="26">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8" s="27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -11991,19 +12209,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="25">
+        <v>6</v>
+      </c>
+      <c r="F9" s="26">
+        <v>7</v>
+      </c>
+      <c r="G9" s="27">
         <v>1</v>
-      </c>
-      <c r="E9" s="25">
-        <v>5</v>
-      </c>
-      <c r="F9" s="56">
-        <v>5</v>
-      </c>
-      <c r="G9" s="57">
-        <v>0</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -12016,19 +12234,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>15</v>
+        <v>51</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>135</v>
       </c>
       <c r="E10" s="25">
-        <v>4</v>
-      </c>
-      <c r="F10" s="26">
-        <v>4</v>
-      </c>
-      <c r="G10" s="27">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F10" s="56">
+        <v>10</v>
+      </c>
+      <c r="G10" s="57">
+        <v>5</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="41"/>
@@ -12041,19 +12259,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>344</v>
+        <v>158</v>
       </c>
       <c r="E11" s="25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="41"/>
@@ -12066,19 +12284,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>266</v>
+        <v>344</v>
       </c>
       <c r="E12" s="25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="56">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G12" s="57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -12088,22 +12306,22 @@
     <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47"/>
       <c r="B13" s="54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="E13" s="25">
         <v>2</v>
       </c>
       <c r="F13" s="26">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G13" s="27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="41"/>
@@ -12116,19 +12334,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="55" t="s">
-        <v>126</v>
+        <v>21</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>266</v>
       </c>
       <c r="E14" s="25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="41"/>
@@ -12141,19 +12359,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>93</v>
+        <v>343</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>106</v>
+        <v>402</v>
       </c>
       <c r="E15" s="25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="26">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15" s="27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="41"/>
@@ -12166,19 +12384,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>143</v>
+        <v>32</v>
       </c>
       <c r="E16" s="25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G16" s="27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -12191,19 +12409,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="E17" s="25">
-        <v>-1</v>
-      </c>
-      <c r="F17" s="56">
+        <v>1</v>
+      </c>
+      <c r="F17" s="26">
+        <v>4</v>
+      </c>
+      <c r="G17" s="27">
         <v>3</v>
-      </c>
-      <c r="G17" s="57">
-        <v>4</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -12224,11 +12442,11 @@
       <c r="E18" s="25">
         <v>-3</v>
       </c>
-      <c r="F18" s="26">
-        <v>2</v>
-      </c>
-      <c r="G18" s="27">
-        <v>5</v>
+      <c r="F18" s="56">
+        <v>4</v>
+      </c>
+      <c r="G18" s="57">
+        <v>7</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -12241,19 +12459,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>343</v>
+        <v>93</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>403</v>
+        <v>106</v>
       </c>
       <c r="E19" s="25">
         <v>-3</v>
       </c>
       <c r="F19" s="26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" s="27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -12272,13 +12490,13 @@
         <v>127</v>
       </c>
       <c r="E20" s="25">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="F20" s="26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="41"/>
@@ -14530,7 +14748,7 @@
       </c>
       <c r="C7">
         <f>COUNTIF(Stats!D:D,'Player Count'!B7)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
         <v>190</v>
@@ -14544,7 +14762,7 @@
       </c>
       <c r="K7">
         <f>COUNTIF(Stats!D:D,'Player Count'!J7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="109"/>
       <c r="N7" t="s">
@@ -14552,7 +14770,7 @@
       </c>
       <c r="O7">
         <f>COUNTIF(Stats!D:D,'Player Count'!N7)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="109"/>
     </row>
@@ -14594,7 +14812,7 @@
       </c>
       <c r="C9">
         <f>COUNTIF(Stats!D:D,'Player Count'!B9)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="s">
         <v>192</v>
@@ -14648,7 +14866,7 @@
       </c>
       <c r="O10">
         <f>COUNTIF(Stats!D:D,'Player Count'!N10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="109"/>
     </row>
@@ -14722,7 +14940,7 @@
       </c>
       <c r="C13">
         <f>COUNTIF(Stats!D:D,'Player Count'!B13)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="67" t="s">
         <v>217</v>
@@ -14818,7 +15036,7 @@
       </c>
       <c r="C16">
         <f>COUNTIF(Stats!D:D,'Player Count'!B16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
         <v>199</v>
@@ -14850,7 +15068,7 @@
       </c>
       <c r="C17">
         <f>COUNTIF(Stats!D:D,'Player Count'!B17)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>200</v>
@@ -14946,7 +15164,7 @@
       </c>
       <c r="C20">
         <f>COUNTIF(Stats!D:D,'Player Count'!B20)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="s">
         <v>203</v>
@@ -14978,7 +15196,7 @@
       </c>
       <c r="C21">
         <f>COUNTIF(Stats!D:D,'Player Count'!B21)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="s">
         <v>204</v>
@@ -15042,14 +15260,14 @@
       </c>
       <c r="C23">
         <f>COUNTIF(Stats!D:D,'Player Count'!B23)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="67" t="s">
         <v>185</v>
       </c>
       <c r="G23">
         <f>COUNTIF(Stats!D:D,'Player Count'!F23)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" t="s">
         <v>228</v>
@@ -15081,14 +15299,14 @@
       </c>
       <c r="G24">
         <f>COUNTIF(Stats!D:D,'Player Count'!F24)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" s="67" t="s">
         <v>206</v>
       </c>
       <c r="K24">
         <f>COUNTIF(Stats!D:D,'Player Count'!J24)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M24" s="109"/>
       <c r="N24" s="67" t="s">
@@ -15138,7 +15356,7 @@
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
         <v>209</v>
@@ -15244,7 +15462,7 @@
       </c>
       <c r="G30" s="78">
         <f>SUM(G6:G29)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J30" s="78" t="s">
         <v>187</v>
@@ -15258,7 +15476,7 @@
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
@@ -15282,28 +15500,28 @@
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.42948717948717946</v>
+        <v>0.44311377245508982</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.24358974358974358</v>
+        <v>0.23952095808383234</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.19230769230769232</v>
+        <v>0.17964071856287425</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.13461538461538461</v>
+        <v>0.1377245508982036</v>
       </c>
     </row>
   </sheetData>
@@ -15420,7 +15638,7 @@
         <v>280</v>
       </c>
       <c r="X6" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="6:24" x14ac:dyDescent="0.3">
@@ -15462,7 +15680,7 @@
         <v>210</v>
       </c>
       <c r="X7" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="6:24" x14ac:dyDescent="0.3">
@@ -15586,7 +15804,7 @@
         <v>-65</v>
       </c>
       <c r="X10" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="6:24" x14ac:dyDescent="0.3">
@@ -15626,7 +15844,7 @@
         <v>-45</v>
       </c>
       <c r="X11" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="6:24" x14ac:dyDescent="0.3">
@@ -15670,7 +15888,7 @@
         <v>5</v>
       </c>
       <c r="X12" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="6:24" x14ac:dyDescent="0.3">
@@ -15704,7 +15922,7 @@
         <v>-35</v>
       </c>
       <c r="X13" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="6:24" x14ac:dyDescent="0.3">
@@ -15746,7 +15964,7 @@
         <v>-45</v>
       </c>
       <c r="X14" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="6:24" x14ac:dyDescent="0.3">
@@ -15831,7 +16049,7 @@
         <v>-60</v>
       </c>
       <c r="X16" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" spans="6:24" x14ac:dyDescent="0.3">
@@ -15900,7 +16118,7 @@
         <v>-35</v>
       </c>
       <c r="X18" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="6:24" x14ac:dyDescent="0.3">

--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1061" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2D71B1-8827-4AE0-8AB7-3C525667647C}"/>
+  <xr:revisionPtr revIDLastSave="1240" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA0DF0CC-B9A5-4491-BE58-A8EF076EE83D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -23,8 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="450">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -267,9 +266,6 @@
     <t>BRISTOL CITY</t>
   </si>
   <si>
-    <t>CHARLTON</t>
-  </si>
-  <si>
     <t>PHIL FODEN</t>
   </si>
   <si>
@@ -888,9 +884,6 @@
     <t>DOM BALLARD</t>
   </si>
   <si>
-    <t>BURNLEY</t>
-  </si>
-  <si>
     <t>IGOR THIAGO</t>
   </si>
   <si>
@@ -957,9 +950,6 @@
     <t>FEMI AZEEZ</t>
   </si>
   <si>
-    <t>EXETER</t>
-  </si>
-  <si>
     <t>JACK CLARKE</t>
   </si>
   <si>
@@ -1348,6 +1338,57 @@
   </si>
   <si>
     <t>YOANNE WISSA</t>
+  </si>
+  <si>
+    <t>COLORADO RAPIDS</t>
+  </si>
+  <si>
+    <t>SHAQUILLE GWENGE</t>
+  </si>
+  <si>
+    <t>NEWPORT</t>
+  </si>
+  <si>
+    <t>JAMAL LOWE</t>
+  </si>
+  <si>
+    <t>EMIL RIIS</t>
+  </si>
+  <si>
+    <t>YUSUF AKHAMRICH</t>
+  </si>
+  <si>
+    <t>LEYTON ORIENT</t>
+  </si>
+  <si>
+    <t>DANE SCARLETT</t>
+  </si>
+  <si>
+    <t>AARON PRESSLEY</t>
+  </si>
+  <si>
+    <t>WALSALL</t>
+  </si>
+  <si>
+    <t>WEST BROM</t>
+  </si>
+  <si>
+    <t>JIMMY-JAY MORGAN</t>
+  </si>
+  <si>
+    <t>CALUM KAVANAGH</t>
+  </si>
+  <si>
+    <t>NOTTS COUNTY</t>
+  </si>
+  <si>
+    <t>WYCOMBE</t>
+  </si>
+  <si>
+    <t>KIERNAN DEWSBURY-HALL</t>
+  </si>
+  <si>
+    <t>DAVIS KEILLOR DUNN</t>
   </si>
 </sst>
 </file>
@@ -3372,21 +3413,25 @@
     </row>
     <row r="5" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="C5" s="115"/>
+      <c r="D5" s="114" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="116">
         <v>1</v>
       </c>
-      <c r="F5" s="15">
-        <v>4</v>
-      </c>
-      <c r="G5" s="83"/>
-      <c r="H5" s="84"/>
+      <c r="F5" s="117">
+        <v>7</v>
+      </c>
+      <c r="G5" s="83" t="s">
+        <v>414</v>
+      </c>
+      <c r="H5" s="84">
+        <v>46275</v>
+      </c>
       <c r="I5" s="85"/>
       <c r="J5" s="82"/>
       <c r="K5" s="16" t="str">
@@ -3399,15 +3444,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3415,12 +3460,22 @@
     </row>
     <row r="6" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
-      <c r="B6" s="21"/>
+      <c r="B6" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="86"/>
+      <c r="D6" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="F6" s="21">
+        <v>0</v>
+      </c>
+      <c r="G6" s="86">
+        <v>46275</v>
+      </c>
       <c r="H6" s="84"/>
       <c r="I6" s="81"/>
       <c r="J6" s="79"/>
@@ -3434,15 +3489,15 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3469,15 +3524,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3489,10 +3544,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E8" s="29">
         <v>1</v>
@@ -3513,15 +3568,15 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3530,10 +3585,10 @@
         <v>14</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" s="29">
         <v>2</v>
@@ -3555,11 +3610,11 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
@@ -3587,15 +3642,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R10" s="118"/>
       <c r="S10" s="118"/>
@@ -3609,10 +3664,10 @@
         <v>16</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" s="29">
         <v>8</v>
@@ -3634,11 +3689,11 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
@@ -3654,10 +3709,10 @@
         <v>16</v>
       </c>
       <c r="C12" s="106" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D12" s="106" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" s="107">
         <v>3</v>
@@ -3666,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H12" s="84">
         <v>46261</v>
@@ -3687,11 +3742,11 @@
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3700,13 +3755,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F13" s="30">
         <v>0</v>
@@ -3727,15 +3782,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="118"/>
       <c r="S13" s="118"/>
@@ -3749,7 +3804,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D14" s="28" t="s">
         <v>31</v>
@@ -3774,15 +3829,15 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -3809,11 +3864,11 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
@@ -3826,16 +3881,16 @@
         <v>17</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E16" s="29">
         <v>17</v>
       </c>
       <c r="F16" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="84"/>
       <c r="H16" s="84"/>
@@ -3851,15 +3906,15 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3868,7 +3923,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>19</v>
@@ -3893,15 +3948,15 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R17" s="118"/>
       <c r="S17" s="118"/>
@@ -3915,16 +3970,16 @@
         <v>17</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18" s="29">
         <v>1</v>
       </c>
       <c r="F18" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="83"/>
       <c r="H18" s="84"/>
@@ -3940,11 +3995,11 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
@@ -3960,7 +4015,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>57</v>
@@ -3969,7 +4024,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" s="87"/>
       <c r="H19" s="84"/>
@@ -3987,10 +4042,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="106" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" s="106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="107">
         <v>8</v>
@@ -3999,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H20" s="84">
         <v>46261</v>
@@ -4023,13 +4078,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F21" s="30">
         <v>2</v>
@@ -4136,7 +4191,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4191,7 +4246,7 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>21</v>
@@ -4265,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" s="80"/>
       <c r="H32" s="94"/>
@@ -4317,10 +4372,10 @@
         <v>14</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="E35" s="29">
         <v>1</v>
@@ -4344,7 +4399,7 @@
         <v>14</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>24</v>
@@ -4388,7 +4443,7 @@
         <v>16</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D38" s="28" t="s">
         <v>22</v>
@@ -4420,16 +4475,16 @@
         <v>16</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E39" s="29">
         <v>11</v>
       </c>
       <c r="F39" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -4456,7 +4511,7 @@
         <v>43</v>
       </c>
       <c r="F40" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="87"/>
       <c r="H40" s="91"/>
@@ -4508,16 +4563,16 @@
         <v>17</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E43" s="29">
         <v>1</v>
       </c>
       <c r="F43" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="87"/>
       <c r="H43" s="91"/>
@@ -4535,16 +4590,16 @@
         <v>17</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E44" s="29">
         <v>7</v>
       </c>
       <c r="F44" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="87"/>
       <c r="H44" s="91"/>
@@ -4562,7 +4617,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="106" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D45" s="106" t="s">
         <v>70</v>
@@ -4574,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H45" s="91">
         <v>46261</v>
@@ -4593,13 +4648,13 @@
         <v>17</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D46" s="28" t="s">
         <v>26</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F46" s="30">
         <v>0</v>
@@ -4622,10 +4677,10 @@
         <v>17</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E47" s="29">
         <v>13</v>
@@ -4649,10 +4704,10 @@
         <v>17</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E48" s="29">
         <v>2</v>
@@ -4749,7 +4804,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -4799,7 +4854,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4867,7 +4922,7 @@
       </c>
       <c r="C59" s="115"/>
       <c r="D59" s="114" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E59" s="116">
         <v>5</v>
@@ -4876,7 +4931,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="80" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H59" s="94">
         <v>46268</v>
@@ -4899,10 +4954,10 @@
         <v>23</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F60" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" s="86">
         <v>46268</v>
@@ -4939,7 +4994,7 @@
         <v>14</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D62" s="28" t="s">
         <v>59</v>
@@ -4966,7 +5021,7 @@
         <v>14</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D63" s="28" t="s">
         <v>22</v>
@@ -5010,10 +5065,10 @@
         <v>16</v>
       </c>
       <c r="C65" s="106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D65" s="106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E65" s="107">
         <v>10</v>
@@ -5022,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="83" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H65" s="91">
         <v>46261</v>
@@ -5041,13 +5096,13 @@
         <v>16</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D66" s="28" t="s">
         <v>24</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F66" s="30">
         <v>0</v>
@@ -5097,7 +5152,7 @@
         <v>16</v>
       </c>
       <c r="C68" s="106" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D68" s="106" t="s">
         <v>58</v>
@@ -5109,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H68" s="91">
         <v>46261</v>
@@ -5128,13 +5183,13 @@
         <v>16</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F69" s="30">
         <v>1</v>
@@ -5157,7 +5212,7 @@
         <v>17</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D70" s="28" t="s">
         <v>19</v>
@@ -5184,7 +5239,7 @@
         <v>17</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D71" s="28" t="s">
         <v>59</v>
@@ -5193,7 +5248,7 @@
         <v>23</v>
       </c>
       <c r="F71" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" s="83"/>
       <c r="H71" s="91"/>
@@ -5220,7 +5275,7 @@
         <v>4</v>
       </c>
       <c r="F72" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="87"/>
       <c r="H72" s="91"/>
@@ -5238,7 +5293,7 @@
         <v>17</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D73" s="28" t="s">
         <v>53</v>
@@ -5265,7 +5320,7 @@
         <v>17</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>52</v>
@@ -5382,7 +5437,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -5500,13 +5555,13 @@
       </c>
       <c r="C86" s="13"/>
       <c r="D86" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E86" s="14">
         <v>4</v>
       </c>
       <c r="F86" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
@@ -5558,7 +5613,7 @@
         <v>14</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>22</v>
@@ -5585,7 +5640,7 @@
         <v>14</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D90" s="28" t="s">
         <v>34</v>
@@ -5629,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D92" s="28" t="s">
         <v>69</v>
@@ -5656,10 +5711,10 @@
         <v>16</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E93" s="29">
         <v>1</v>
@@ -5683,7 +5738,7 @@
         <v>16</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D94" s="28" t="s">
         <v>18</v>
@@ -5744,10 +5799,10 @@
         <v>17</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>75</v>
+        <v>446</v>
       </c>
       <c r="E97" s="29">
         <v>4</v>
@@ -5771,10 +5826,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E98" s="29">
         <v>7</v>
@@ -5798,7 +5853,7 @@
         <v>17</v>
       </c>
       <c r="C99" s="106" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D99" s="106" t="s">
         <v>31</v>
@@ -5810,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H99" s="91">
         <v>46247</v>
@@ -5829,13 +5884,13 @@
         <v>17</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E100" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F100" s="30">
         <v>0</v>
@@ -5858,10 +5913,10 @@
         <v>17</v>
       </c>
       <c r="C101" s="106" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D101" s="106" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E101" s="107">
         <v>1</v>
@@ -5870,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H101" s="91">
         <v>46254</v>
@@ -5889,16 +5944,16 @@
         <v>17</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D102" s="28" t="s">
         <v>53</v>
       </c>
       <c r="E102" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F102" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G102" s="87">
         <v>46254</v>
@@ -5918,10 +5973,10 @@
         <v>17</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D103" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E103" s="29">
         <v>48</v>
@@ -6001,7 +6056,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6051,7 +6106,7 @@
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>49</v>
@@ -6177,10 +6232,10 @@
         <v>14</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D116" s="28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E116" s="29">
         <v>1</v>
@@ -6204,10 +6259,10 @@
         <v>14</v>
       </c>
       <c r="C117" s="28" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D117" s="28" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E117" s="29">
         <v>1</v>
@@ -6248,10 +6303,10 @@
         <v>16</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E119" s="29">
         <v>1</v>
@@ -6275,10 +6330,10 @@
         <v>16</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E120" s="29">
         <v>1</v>
@@ -6302,10 +6357,10 @@
         <v>16</v>
       </c>
       <c r="C121" s="106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D121" s="106" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E121" s="107">
         <v>1</v>
@@ -6314,7 +6369,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="86" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H121" s="94">
         <v>46261</v>
@@ -6333,13 +6388,13 @@
         <v>16</v>
       </c>
       <c r="C122" s="28" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D122" s="28" t="s">
         <v>31</v>
       </c>
       <c r="E122" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F122" s="30">
         <v>0</v>
@@ -6379,7 +6434,7 @@
         <v>17</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D124" s="28" t="s">
         <v>70</v>
@@ -6418,7 +6473,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H125" s="91">
         <v>46261</v>
@@ -6437,13 +6492,13 @@
         <v>17</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D126" s="28" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E126" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F126" s="30">
         <v>0</v>
@@ -6462,23 +6517,27 @@
     </row>
     <row r="127" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="79"/>
-      <c r="B127" s="28" t="s">
+      <c r="B127" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="D127" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E127" s="29">
+      <c r="C127" s="106" t="s">
+        <v>269</v>
+      </c>
+      <c r="D127" s="106" t="s">
+        <v>97</v>
+      </c>
+      <c r="E127" s="107">
         <v>20</v>
       </c>
-      <c r="F127" s="30">
+      <c r="F127" s="108">
         <v>1</v>
       </c>
-      <c r="G127" s="87"/>
-      <c r="H127" s="91"/>
+      <c r="G127" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H127" s="91">
+        <v>46275</v>
+      </c>
       <c r="I127" s="90"/>
       <c r="J127" s="76"/>
       <c r="K127" s="1"/>
@@ -6493,18 +6552,20 @@
         <v>17</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>112</v>
+        <v>449</v>
       </c>
       <c r="D128" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="E128" s="29">
-        <v>1</v>
+        <v>352</v>
+      </c>
+      <c r="E128" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F128" s="30">
         <v>0</v>
       </c>
-      <c r="G128" s="87"/>
+      <c r="G128" s="87">
+        <v>46275</v>
+      </c>
       <c r="H128" s="91"/>
       <c r="I128" s="90"/>
       <c r="J128" s="76"/>
@@ -6520,10 +6581,10 @@
         <v>17</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>367</v>
+        <v>111</v>
       </c>
       <c r="D129" s="28" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="E129" s="29">
         <v>1</v>
@@ -6543,13 +6604,27 @@
     </row>
     <row r="130" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="79"/>
-      <c r="B130" s="28"/>
-      <c r="C130" s="28"/>
-      <c r="D130" s="28"/>
-      <c r="E130" s="29"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="87"/>
-      <c r="H130" s="91"/>
+      <c r="B130" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" s="106" t="s">
+        <v>364</v>
+      </c>
+      <c r="D130" s="106" t="s">
+        <v>267</v>
+      </c>
+      <c r="E130" s="107">
+        <v>1</v>
+      </c>
+      <c r="F130" s="108">
+        <v>0</v>
+      </c>
+      <c r="G130" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H130" s="91">
+        <v>46268</v>
+      </c>
       <c r="I130" s="90"/>
       <c r="J130" s="76"/>
       <c r="K130" s="1"/>
@@ -6560,12 +6635,24 @@
     </row>
     <row r="131" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="79"/>
-      <c r="B131" s="106"/>
-      <c r="C131" s="106"/>
-      <c r="D131" s="106"/>
-      <c r="E131" s="107"/>
-      <c r="F131" s="108"/>
-      <c r="G131" s="87"/>
+      <c r="B131" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="D131" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="E131" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F131" s="30">
+        <v>1</v>
+      </c>
+      <c r="G131" s="87">
+        <v>46268</v>
+      </c>
       <c r="H131" s="91"/>
       <c r="I131" s="90"/>
       <c r="J131" s="76"/>
@@ -6620,7 +6707,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -6744,7 +6831,7 @@
         <v>1</v>
       </c>
       <c r="F140" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G140" s="80"/>
       <c r="H140" s="94"/>
@@ -6796,10 +6883,10 @@
         <v>14</v>
       </c>
       <c r="C143" s="28" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D143" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E143" s="29">
         <v>2</v>
@@ -6823,7 +6910,7 @@
         <v>14</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D144" s="28" t="s">
         <v>59</v>
@@ -6863,23 +6950,27 @@
     </row>
     <row r="146" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="79"/>
-      <c r="B146" s="28" t="s">
+      <c r="B146" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C146" s="28" t="s">
-        <v>369</v>
-      </c>
-      <c r="D146" s="28" t="s">
+      <c r="C146" s="106" t="s">
+        <v>366</v>
+      </c>
+      <c r="D146" s="106" t="s">
+        <v>411</v>
+      </c>
+      <c r="E146" s="107">
+        <v>1</v>
+      </c>
+      <c r="F146" s="108">
+        <v>0</v>
+      </c>
+      <c r="G146" s="87" t="s">
         <v>414</v>
       </c>
-      <c r="E146" s="29">
-        <v>1</v>
-      </c>
-      <c r="F146" s="30">
-        <v>0</v>
-      </c>
-      <c r="G146" s="87"/>
-      <c r="H146" s="91"/>
+      <c r="H146" s="91">
+        <v>46268</v>
+      </c>
       <c r="I146" s="90"/>
       <c r="J146" s="76"/>
       <c r="K146" s="1"/>
@@ -6894,18 +6985,20 @@
         <v>16</v>
       </c>
       <c r="C147" s="28" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D147" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="E147" s="29">
-        <v>6</v>
+        <v>93</v>
+      </c>
+      <c r="E147" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F147" s="30">
-        <v>2</v>
-      </c>
-      <c r="G147" s="87"/>
+        <v>1</v>
+      </c>
+      <c r="G147" s="87">
+        <v>46268</v>
+      </c>
       <c r="H147" s="91"/>
       <c r="I147" s="90"/>
       <c r="J147" s="96"/>
@@ -6921,13 +7014,13 @@
         <v>16</v>
       </c>
       <c r="C148" s="28" t="s">
-        <v>370</v>
+        <v>104</v>
       </c>
       <c r="D148" s="28" t="s">
-        <v>81</v>
+        <v>352</v>
       </c>
       <c r="E148" s="29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F148" s="30">
         <v>3</v>
@@ -6944,11 +7037,21 @@
     </row>
     <row r="149" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="79"/>
-      <c r="B149" s="28"/>
-      <c r="C149" s="28"/>
-      <c r="D149" s="28"/>
-      <c r="E149" s="29"/>
-      <c r="F149" s="30"/>
+      <c r="B149" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="D149" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E149" s="29">
+        <v>2</v>
+      </c>
+      <c r="F149" s="30">
+        <v>4</v>
+      </c>
       <c r="G149" s="87"/>
       <c r="H149" s="91"/>
       <c r="I149" s="90"/>
@@ -6982,7 +7085,7 @@
         <v>17</v>
       </c>
       <c r="C151" s="28" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D151" s="28" t="s">
         <v>71</v>
@@ -6991,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="F151" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G151" s="83"/>
       <c r="H151" s="91"/>
@@ -7009,7 +7112,7 @@
         <v>17</v>
       </c>
       <c r="C152" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D152" s="28" t="s">
         <v>59</v>
@@ -7018,7 +7121,7 @@
         <v>33</v>
       </c>
       <c r="F152" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" s="87"/>
       <c r="H152" s="91"/>
@@ -7036,7 +7139,7 @@
         <v>17</v>
       </c>
       <c r="C153" s="28" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D153" s="28" t="s">
         <v>20</v>
@@ -7045,7 +7148,7 @@
         <v>13</v>
       </c>
       <c r="F153" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G153" s="87"/>
       <c r="H153" s="91"/>
@@ -7063,10 +7166,10 @@
         <v>17</v>
       </c>
       <c r="C154" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D154" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E154" s="29">
         <v>25</v>
@@ -7090,10 +7193,10 @@
         <v>17</v>
       </c>
       <c r="C155" s="106" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D155" s="106" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E155" s="107">
         <v>10</v>
@@ -7102,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="G155" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H155" s="91">
         <v>46261</v>
@@ -7117,25 +7220,27 @@
     </row>
     <row r="156" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="79"/>
-      <c r="B156" s="28" t="s">
+      <c r="B156" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C156" s="28" t="s">
-        <v>426</v>
-      </c>
-      <c r="D156" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="E156" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="F156" s="30">
+      <c r="C156" s="106" t="s">
+        <v>423</v>
+      </c>
+      <c r="D156" s="106" t="s">
+        <v>424</v>
+      </c>
+      <c r="E156" s="107" t="s">
+        <v>413</v>
+      </c>
+      <c r="F156" s="108">
         <v>0</v>
       </c>
       <c r="G156" s="87">
         <v>46261</v>
       </c>
-      <c r="H156" s="91"/>
+      <c r="H156" s="91">
+        <v>46268</v>
+      </c>
       <c r="I156" s="90"/>
       <c r="J156" s="76"/>
       <c r="K156" s="1"/>
@@ -7146,12 +7251,24 @@
     </row>
     <row r="157" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="79"/>
-      <c r="B157" s="28"/>
-      <c r="C157" s="28"/>
-      <c r="D157" s="28"/>
-      <c r="E157" s="29"/>
-      <c r="F157" s="30"/>
-      <c r="G157" s="87"/>
+      <c r="B157" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="D157" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="E157" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F157" s="30">
+        <v>0</v>
+      </c>
+      <c r="G157" s="87">
+        <v>46268</v>
+      </c>
       <c r="H157" s="91"/>
       <c r="I157" s="90"/>
       <c r="J157" s="76"/>
@@ -7223,7 +7340,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -7399,10 +7516,10 @@
         <v>14</v>
       </c>
       <c r="C170" s="28" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D170" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E170" s="29">
         <v>3</v>
@@ -7426,10 +7543,10 @@
         <v>14</v>
       </c>
       <c r="C171" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D171" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E171" s="29">
         <v>4</v>
@@ -7470,10 +7587,10 @@
         <v>16</v>
       </c>
       <c r="C173" s="28" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D173" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E173" s="29">
         <v>6</v>
@@ -7497,7 +7614,7 @@
         <v>16</v>
       </c>
       <c r="C174" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D174" s="28" t="s">
         <v>19</v>
@@ -7506,7 +7623,7 @@
         <v>12</v>
       </c>
       <c r="F174" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G174" s="91"/>
       <c r="H174" s="91"/>
@@ -7524,7 +7641,7 @@
         <v>16</v>
       </c>
       <c r="C175" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D175" s="28" t="s">
         <v>22</v>
@@ -7585,10 +7702,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D178" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E178" s="29">
         <v>23</v>
@@ -7612,16 +7729,16 @@
         <v>17</v>
       </c>
       <c r="C179" s="28" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D179" s="28" t="s">
-        <v>305</v>
+        <v>447</v>
       </c>
       <c r="E179" s="29">
         <v>24</v>
       </c>
       <c r="F179" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" s="83"/>
       <c r="H179" s="91"/>
@@ -7639,16 +7756,16 @@
         <v>17</v>
       </c>
       <c r="C180" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D180" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E180" s="29">
         <v>7</v>
       </c>
       <c r="F180" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G180" s="91"/>
       <c r="H180" s="91"/>
@@ -7666,10 +7783,10 @@
         <v>17</v>
       </c>
       <c r="C181" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D181" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E181" s="29">
         <v>3</v>
@@ -7693,10 +7810,10 @@
         <v>17</v>
       </c>
       <c r="C182" s="28" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D182" s="28" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E182" s="29">
         <v>1</v>
@@ -7810,7 +7927,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -7860,10 +7977,10 @@
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="1"/>
@@ -7928,13 +8045,13 @@
       </c>
       <c r="C194" s="13"/>
       <c r="D194" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E194" s="14">
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -7986,10 +8103,10 @@
         <v>14</v>
       </c>
       <c r="C197" s="28" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D197" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E197" s="29">
         <v>3</v>
@@ -8013,7 +8130,7 @@
         <v>14</v>
       </c>
       <c r="C198" s="28" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D198" s="28" t="s">
         <v>31</v>
@@ -8057,10 +8174,10 @@
         <v>16</v>
       </c>
       <c r="C200" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D200" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E200" s="29">
         <v>10</v>
@@ -8084,7 +8201,7 @@
         <v>16</v>
       </c>
       <c r="C201" s="28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D201" s="28" t="s">
         <v>34</v>
@@ -8093,7 +8210,7 @@
         <v>4</v>
       </c>
       <c r="F201" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G201" s="83"/>
       <c r="H201" s="90"/>
@@ -8111,7 +8228,7 @@
         <v>16</v>
       </c>
       <c r="C202" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D202" s="28" t="s">
         <v>31</v>
@@ -8172,10 +8289,10 @@
         <v>17</v>
       </c>
       <c r="C205" s="106" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D205" s="106" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E205" s="107">
         <v>3</v>
@@ -8184,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="83" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H205" s="91">
         <v>46254</v>
@@ -8203,16 +8320,16 @@
         <v>17</v>
       </c>
       <c r="C206" s="28" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D206" s="28" t="s">
         <v>62</v>
       </c>
       <c r="E206" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F206" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" s="87">
         <v>46254</v>
@@ -8232,7 +8349,7 @@
         <v>17</v>
       </c>
       <c r="C207" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D207" s="28" t="s">
         <v>74</v>
@@ -8259,7 +8376,7 @@
         <v>17</v>
       </c>
       <c r="C208" s="28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D208" s="28" t="s">
         <v>63</v>
@@ -8286,7 +8403,7 @@
         <v>17</v>
       </c>
       <c r="C209" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D209" s="28" t="s">
         <v>31</v>
@@ -8295,7 +8412,7 @@
         <v>49</v>
       </c>
       <c r="F209" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G209" s="87"/>
       <c r="H209" s="91"/>
@@ -8313,7 +8430,7 @@
         <v>17</v>
       </c>
       <c r="C210" s="28" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D210" s="28" t="s">
         <v>58</v>
@@ -8463,7 +8580,7 @@
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>50</v>
@@ -8537,7 +8654,7 @@
         <v>8</v>
       </c>
       <c r="F221" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G221" s="80"/>
       <c r="H221" s="94"/>
@@ -8589,10 +8706,10 @@
         <v>14</v>
       </c>
       <c r="C224" s="28" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D224" s="28" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E224" s="29">
         <v>1</v>
@@ -8616,10 +8733,10 @@
         <v>14</v>
       </c>
       <c r="C225" s="28" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D225" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E225" s="29">
         <v>1</v>
@@ -8660,10 +8777,10 @@
         <v>16</v>
       </c>
       <c r="C227" s="28" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D227" s="28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E227" s="29">
         <v>1</v>
@@ -8683,23 +8800,27 @@
     </row>
     <row r="228" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="79"/>
-      <c r="B228" s="28" t="s">
+      <c r="B228" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C228" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="D228" s="28" t="s">
+      <c r="C228" s="106" t="s">
+        <v>129</v>
+      </c>
+      <c r="D228" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="E228" s="29">
+      <c r="E228" s="107">
         <v>1</v>
       </c>
-      <c r="F228" s="30">
+      <c r="F228" s="108">
         <v>0</v>
       </c>
-      <c r="G228" s="87"/>
-      <c r="H228" s="91"/>
+      <c r="G228" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H228" s="91">
+        <v>46268</v>
+      </c>
       <c r="I228" s="89"/>
       <c r="J228" s="1"/>
       <c r="K228" s="1"/>
@@ -8714,18 +8835,20 @@
         <v>16</v>
       </c>
       <c r="C229" s="28" t="s">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="D229" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E229" s="29">
-        <v>6</v>
+        <v>128</v>
+      </c>
+      <c r="E229" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F229" s="30">
         <v>0</v>
       </c>
-      <c r="G229" s="87"/>
+      <c r="G229" s="87">
+        <v>46268</v>
+      </c>
       <c r="H229" s="91"/>
       <c r="I229" s="89"/>
       <c r="J229" s="76"/>
@@ -8737,11 +8860,21 @@
     </row>
     <row r="230" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="79"/>
-      <c r="B230" s="28"/>
-      <c r="C230" s="28"/>
-      <c r="D230" s="28"/>
-      <c r="E230" s="29"/>
-      <c r="F230" s="30"/>
+      <c r="B230" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C230" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="D230" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E230" s="29">
+        <v>6</v>
+      </c>
+      <c r="F230" s="30">
+        <v>0</v>
+      </c>
       <c r="G230" s="87"/>
       <c r="H230" s="91"/>
       <c r="I230" s="89"/>
@@ -8775,7 +8908,7 @@
         <v>17</v>
       </c>
       <c r="C232" s="28" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D232" s="28" t="s">
         <v>23</v>
@@ -8802,16 +8935,16 @@
         <v>17</v>
       </c>
       <c r="C233" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D233" s="28" t="s">
-        <v>162</v>
+        <v>439</v>
       </c>
       <c r="E233" s="29">
         <v>19</v>
       </c>
       <c r="F233" s="30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G233" s="87"/>
       <c r="H233" s="91"/>
@@ -8825,23 +8958,27 @@
     </row>
     <row r="234" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="79"/>
-      <c r="B234" s="28" t="s">
+      <c r="B234" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C234" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D234" s="28" t="s">
+      <c r="C234" s="106" t="s">
+        <v>132</v>
+      </c>
+      <c r="D234" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="E234" s="29">
+      <c r="E234" s="107">
         <v>34</v>
       </c>
-      <c r="F234" s="30">
+      <c r="F234" s="108">
         <v>0</v>
       </c>
-      <c r="G234" s="87"/>
-      <c r="H234" s="91"/>
+      <c r="G234" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H234" s="91">
+        <v>46268</v>
+      </c>
       <c r="I234" s="89"/>
       <c r="J234" s="1"/>
       <c r="K234" s="1"/>
@@ -8856,18 +8993,20 @@
         <v>17</v>
       </c>
       <c r="C235" s="28" t="s">
-        <v>276</v>
+        <v>441</v>
       </c>
       <c r="D235" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="E235" s="29">
-        <v>5</v>
+        <v>442</v>
+      </c>
+      <c r="E235" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F235" s="30">
         <v>0</v>
       </c>
-      <c r="G235" s="87"/>
+      <c r="G235" s="87">
+        <v>46268</v>
+      </c>
       <c r="H235" s="91"/>
       <c r="I235" s="89"/>
       <c r="J235" s="76"/>
@@ -8883,16 +9022,16 @@
         <v>17</v>
       </c>
       <c r="C236" s="28" t="s">
-        <v>378</v>
+        <v>275</v>
       </c>
       <c r="D236" s="28" t="s">
-        <v>124</v>
+        <v>276</v>
       </c>
       <c r="E236" s="29">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F236" s="30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G236" s="83"/>
       <c r="H236" s="91"/>
@@ -8906,11 +9045,21 @@
     </row>
     <row r="237" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="79"/>
-      <c r="B237" s="106"/>
-      <c r="C237" s="106"/>
-      <c r="D237" s="106"/>
-      <c r="E237" s="107"/>
-      <c r="F237" s="108"/>
+      <c r="B237" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237" s="28" t="s">
+        <v>375</v>
+      </c>
+      <c r="D237" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E237" s="29">
+        <v>13</v>
+      </c>
+      <c r="F237" s="30">
+        <v>2</v>
+      </c>
       <c r="G237" s="87"/>
       <c r="H237" s="91"/>
       <c r="I237" s="89"/>
@@ -9000,7 +9149,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -9050,7 +9199,7 @@
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>51</v>
@@ -9124,7 +9273,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G248" s="80"/>
       <c r="H248" s="94"/>
@@ -9176,7 +9325,7 @@
         <v>14</v>
       </c>
       <c r="C251" s="28" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D251" s="28" t="s">
         <v>22</v>
@@ -9247,10 +9396,10 @@
         <v>16</v>
       </c>
       <c r="C254" s="28" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D254" s="28" t="s">
-        <v>282</v>
+        <v>100</v>
       </c>
       <c r="E254" s="29">
         <v>16</v>
@@ -9274,10 +9423,10 @@
         <v>16</v>
       </c>
       <c r="C255" s="28" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D255" s="28" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="E255" s="29">
         <v>2</v>
@@ -9301,10 +9450,10 @@
         <v>16</v>
       </c>
       <c r="C256" s="28" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D256" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E256" s="29">
         <v>1</v>
@@ -9362,16 +9511,16 @@
         <v>17</v>
       </c>
       <c r="C259" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D259" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E259" s="29">
         <v>14</v>
       </c>
       <c r="F259" s="30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G259" s="87"/>
       <c r="H259" s="91"/>
@@ -9389,7 +9538,7 @@
         <v>17</v>
       </c>
       <c r="C260" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D260" s="28" t="s">
         <v>74</v>
@@ -9398,7 +9547,7 @@
         <v>22</v>
       </c>
       <c r="F260" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
@@ -9416,10 +9565,10 @@
         <v>17</v>
       </c>
       <c r="C261" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D261" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E261" s="29">
         <v>33</v>
@@ -9443,7 +9592,7 @@
         <v>17</v>
       </c>
       <c r="C262" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D262" s="28" t="s">
         <v>62</v>
@@ -9470,7 +9619,7 @@
         <v>17</v>
       </c>
       <c r="C263" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D263" s="28" t="s">
         <v>59</v>
@@ -9587,7 +9736,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -9637,10 +9786,10 @@
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" s="1"/>
@@ -9705,7 +9854,7 @@
       </c>
       <c r="C275" s="13"/>
       <c r="D275" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E275" s="14">
         <v>1</v>
@@ -9763,10 +9912,10 @@
         <v>14</v>
       </c>
       <c r="C278" s="28" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D278" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E278" s="29">
         <v>1</v>
@@ -9790,10 +9939,10 @@
         <v>14</v>
       </c>
       <c r="C279" s="28" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D279" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E279" s="29">
         <v>1</v>
@@ -9834,10 +9983,10 @@
         <v>16</v>
       </c>
       <c r="C281" s="28" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D281" s="28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E281" s="29">
         <v>1</v>
@@ -9861,10 +10010,10 @@
         <v>16</v>
       </c>
       <c r="C282" s="28" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D282" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E282" s="29">
         <v>1</v>
@@ -9888,7 +10037,7 @@
         <v>16</v>
       </c>
       <c r="C283" s="28" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D283" s="28" t="s">
         <v>52</v>
@@ -9949,7 +10098,7 @@
         <v>17</v>
       </c>
       <c r="C286" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D286" s="28" t="s">
         <v>31</v>
@@ -9976,10 +10125,10 @@
         <v>17</v>
       </c>
       <c r="C287" s="28" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D287" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E287" s="29">
         <v>1</v>
@@ -10003,7 +10152,7 @@
         <v>17</v>
       </c>
       <c r="C288" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D288" s="28" t="s">
         <v>72</v>
@@ -10012,7 +10161,7 @@
         <v>1</v>
       </c>
       <c r="F288" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G288" s="87"/>
       <c r="H288" s="91"/>
@@ -10030,10 +10179,10 @@
         <v>17</v>
       </c>
       <c r="C289" s="28" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D289" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E289" s="29">
         <v>1</v>
@@ -10057,10 +10206,10 @@
         <v>17</v>
       </c>
       <c r="C290" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D290" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E290" s="29">
         <v>1</v>
@@ -10174,7 +10323,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -10224,10 +10373,10 @@
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E299" s="2"/>
       <c r="F299" s="1"/>
@@ -10301,7 +10450,7 @@
         <v>6</v>
       </c>
       <c r="G302" s="80" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H302" s="91">
         <v>46261</v>
@@ -10324,10 +10473,10 @@
         <v>63</v>
       </c>
       <c r="E303" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F303" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G303" s="87">
         <v>46261</v>
@@ -10364,7 +10513,7 @@
         <v>14</v>
       </c>
       <c r="C305" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D305" s="28" t="s">
         <v>71</v>
@@ -10391,10 +10540,10 @@
         <v>14</v>
       </c>
       <c r="C306" s="28" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D306" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E306" s="29">
         <v>1</v>
@@ -10435,10 +10584,10 @@
         <v>16</v>
       </c>
       <c r="C308" s="28" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D308" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E308" s="29">
         <v>1</v>
@@ -10458,23 +10607,27 @@
     </row>
     <row r="309" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="79"/>
-      <c r="B309" s="28" t="s">
+      <c r="B309" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C309" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="D309" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E309" s="29">
+      <c r="C309" s="106" t="s">
+        <v>379</v>
+      </c>
+      <c r="D309" s="106" t="s">
+        <v>131</v>
+      </c>
+      <c r="E309" s="107">
         <v>1</v>
       </c>
-      <c r="F309" s="30">
+      <c r="F309" s="108">
         <v>0</v>
       </c>
-      <c r="G309" s="87"/>
-      <c r="H309" s="91"/>
+      <c r="G309" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H309" s="91">
+        <v>46268</v>
+      </c>
       <c r="I309" s="90"/>
       <c r="J309" s="1"/>
       <c r="K309" s="1"/>
@@ -10489,18 +10642,20 @@
         <v>16</v>
       </c>
       <c r="C310" s="28" t="s">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="D310" s="77" t="s">
-        <v>268</v>
-      </c>
-      <c r="E310" s="29">
-        <v>1</v>
+        <v>352</v>
+      </c>
+      <c r="E310" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F310" s="30">
         <v>0</v>
       </c>
-      <c r="G310" s="87"/>
+      <c r="G310" s="87">
+        <v>46268</v>
+      </c>
       <c r="H310" s="91"/>
       <c r="I310" s="90"/>
       <c r="J310" s="1"/>
@@ -10512,11 +10667,21 @@
     </row>
     <row r="311" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="79"/>
-      <c r="B311" s="28"/>
-      <c r="C311" s="28"/>
-      <c r="D311" s="28"/>
-      <c r="E311" s="29"/>
-      <c r="F311" s="30"/>
+      <c r="B311" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C311" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="D311" s="77" t="s">
+        <v>267</v>
+      </c>
+      <c r="E311" s="29">
+        <v>1</v>
+      </c>
+      <c r="F311" s="30">
+        <v>1</v>
+      </c>
       <c r="G311" s="83"/>
       <c r="H311" s="91"/>
       <c r="I311" s="90"/>
@@ -10559,7 +10724,7 @@
         <v>78</v>
       </c>
       <c r="F313" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -10573,23 +10738,27 @@
     </row>
     <row r="314" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="79"/>
-      <c r="B314" s="28" t="s">
+      <c r="B314" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C314" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="D314" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="E314" s="29">
+      <c r="C314" s="106" t="s">
+        <v>381</v>
+      </c>
+      <c r="D314" s="106" t="s">
+        <v>292</v>
+      </c>
+      <c r="E314" s="107">
         <v>1</v>
       </c>
-      <c r="F314" s="30">
+      <c r="F314" s="108">
         <v>0</v>
       </c>
-      <c r="G314" s="87"/>
-      <c r="H314" s="91"/>
+      <c r="G314" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H314" s="91">
+        <v>46268</v>
+      </c>
       <c r="I314" s="90"/>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
@@ -10604,18 +10773,20 @@
         <v>17</v>
       </c>
       <c r="C315" s="28" t="s">
-        <v>291</v>
+        <v>437</v>
       </c>
       <c r="D315" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E315" s="29">
-        <v>1</v>
+        <v>292</v>
+      </c>
+      <c r="E315" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F315" s="30">
         <v>0</v>
       </c>
-      <c r="G315" s="87"/>
+      <c r="G315" s="87">
+        <v>46268</v>
+      </c>
       <c r="H315" s="91"/>
       <c r="I315" s="90"/>
       <c r="J315" s="1"/>
@@ -10631,10 +10802,10 @@
         <v>17</v>
       </c>
       <c r="C316" s="28" t="s">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="D316" s="28" t="s">
-        <v>162</v>
+        <v>20</v>
       </c>
       <c r="E316" s="29">
         <v>1</v>
@@ -10658,10 +10829,10 @@
         <v>17</v>
       </c>
       <c r="C317" s="28" t="s">
-        <v>385</v>
+        <v>320</v>
       </c>
       <c r="D317" s="28" t="s">
-        <v>280</v>
+        <v>161</v>
       </c>
       <c r="E317" s="29">
         <v>1</v>
@@ -10681,13 +10852,27 @@
     </row>
     <row r="318" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="79"/>
-      <c r="B318" s="106"/>
-      <c r="C318" s="106"/>
-      <c r="D318" s="106"/>
-      <c r="E318" s="107"/>
-      <c r="F318" s="108"/>
-      <c r="G318" s="83"/>
-      <c r="H318" s="91"/>
+      <c r="B318" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C318" s="106" t="s">
+        <v>382</v>
+      </c>
+      <c r="D318" s="106" t="s">
+        <v>279</v>
+      </c>
+      <c r="E318" s="107">
+        <v>1</v>
+      </c>
+      <c r="F318" s="108">
+        <v>0</v>
+      </c>
+      <c r="G318" s="83" t="s">
+        <v>414</v>
+      </c>
+      <c r="H318" s="91">
+        <v>46268</v>
+      </c>
       <c r="I318" s="90"/>
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
@@ -10698,12 +10883,24 @@
     </row>
     <row r="319" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="79"/>
-      <c r="B319" s="28"/>
-      <c r="C319" s="28"/>
-      <c r="D319" s="28"/>
-      <c r="E319" s="29"/>
-      <c r="F319" s="30"/>
-      <c r="G319" s="87"/>
+      <c r="B319" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C319" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="D319" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="E319" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F319" s="30">
+        <v>0</v>
+      </c>
+      <c r="G319" s="87">
+        <v>46268</v>
+      </c>
       <c r="H319" s="91"/>
       <c r="I319" s="90"/>
       <c r="J319" s="1"/>
@@ -10775,7 +10972,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -10825,10 +11022,10 @@
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E326" s="2"/>
       <c r="F326" s="1"/>
@@ -10899,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -10951,10 +11148,10 @@
         <v>14</v>
       </c>
       <c r="C332" s="106" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D332" s="106" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E332" s="107">
         <v>2</v>
@@ -10963,7 +11160,7 @@
         <v>0</v>
       </c>
       <c r="G332" s="83" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H332" s="91">
         <v>46261</v>
@@ -10982,13 +11179,13 @@
         <v>14</v>
       </c>
       <c r="C333" s="28" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D333" s="28" t="s">
         <v>23</v>
       </c>
       <c r="E333" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F333" s="30">
         <v>0</v>
@@ -11011,7 +11208,7 @@
         <v>14</v>
       </c>
       <c r="C334" s="28" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D334" s="28" t="s">
         <v>18</v>
@@ -11038,16 +11235,16 @@
         <v>16</v>
       </c>
       <c r="C335" s="28" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D335" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E335" s="29">
         <v>10</v>
       </c>
       <c r="F335" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G335" s="87"/>
       <c r="H335" s="91"/>
@@ -11065,10 +11262,10 @@
         <v>16</v>
       </c>
       <c r="C336" s="28" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D336" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E336" s="29">
         <v>1</v>
@@ -11088,23 +11285,27 @@
     </row>
     <row r="337" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="79"/>
-      <c r="B337" s="28" t="s">
+      <c r="B337" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C337" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="D337" s="28" t="s">
-        <v>390</v>
-      </c>
-      <c r="E337" s="29">
+      <c r="C337" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="D337" s="106" t="s">
+        <v>387</v>
+      </c>
+      <c r="E337" s="107">
         <v>1</v>
       </c>
-      <c r="F337" s="30">
+      <c r="F337" s="108">
         <v>0</v>
       </c>
-      <c r="G337" s="87"/>
-      <c r="H337" s="91"/>
+      <c r="G337" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H337" s="91">
+        <v>46268</v>
+      </c>
       <c r="I337" s="90"/>
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
@@ -11115,12 +11316,24 @@
     </row>
     <row r="338" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="79"/>
-      <c r="B338" s="28"/>
-      <c r="C338" s="28"/>
-      <c r="D338" s="28"/>
-      <c r="E338" s="29"/>
-      <c r="F338" s="30"/>
-      <c r="G338" s="87"/>
+      <c r="B338" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C338" s="28" t="s">
+        <v>448</v>
+      </c>
+      <c r="D338" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E338" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F338" s="30">
+        <v>0</v>
+      </c>
+      <c r="G338" s="87">
+        <v>46268</v>
+      </c>
       <c r="H338" s="91"/>
       <c r="I338" s="90"/>
       <c r="J338" s="1"/>
@@ -11150,7 +11363,7 @@
         <v>17</v>
       </c>
       <c r="C340" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D340" s="28" t="s">
         <v>58</v>
@@ -11159,7 +11372,7 @@
         <v>9</v>
       </c>
       <c r="F340" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G340" s="87"/>
       <c r="H340" s="90"/>
@@ -11174,10 +11387,10 @@
         <v>17</v>
       </c>
       <c r="C341" s="28" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D341" s="28" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E341" s="29">
         <v>5</v>
@@ -11198,16 +11411,16 @@
         <v>17</v>
       </c>
       <c r="C342" s="28" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D342" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E342" s="29">
         <v>12</v>
       </c>
       <c r="F342" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G342" s="87"/>
       <c r="H342" s="91"/>
@@ -11222,7 +11435,7 @@
         <v>17</v>
       </c>
       <c r="C343" s="28" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D343" s="28" t="s">
         <v>23</v>
@@ -11246,10 +11459,10 @@
         <v>17</v>
       </c>
       <c r="C344" s="28" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D344" s="28" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E344" s="29">
         <v>40</v>
@@ -11345,7 +11558,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -11371,10 +11584,10 @@
     <row r="353" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="1"/>
       <c r="C353" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E353" s="2"/>
       <c r="F353" s="1"/>
@@ -11421,7 +11634,7 @@
       </c>
       <c r="C356" s="13"/>
       <c r="D356" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E356" s="14">
         <v>3</v>
@@ -11461,7 +11674,7 @@
         <v>14</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D359" s="28" t="s">
         <v>24</v>
@@ -11482,7 +11695,7 @@
         <v>14</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D360" s="28" t="s">
         <v>18</v>
@@ -11514,7 +11727,7 @@
         <v>16</v>
       </c>
       <c r="C362" s="28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D362" s="28" t="s">
         <v>19</v>
@@ -11535,7 +11748,7 @@
         <v>16</v>
       </c>
       <c r="C363" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D363" s="28" t="s">
         <v>22</v>
@@ -11556,7 +11769,7 @@
         <v>16</v>
       </c>
       <c r="C364" s="106" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D364" s="106" t="s">
         <v>22</v>
@@ -11568,7 +11781,7 @@
         <v>0</v>
       </c>
       <c r="G364" s="103" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H364" s="103">
         <v>46268</v>
@@ -11581,13 +11794,13 @@
         <v>16</v>
       </c>
       <c r="C365" s="28" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D365" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E365" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F365" s="30">
         <v>0</v>
@@ -11615,16 +11828,16 @@
         <v>17</v>
       </c>
       <c r="C367" s="28" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D367" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E367" s="29">
         <v>25</v>
       </c>
       <c r="F367" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="103"/>
@@ -11636,7 +11849,7 @@
         <v>17</v>
       </c>
       <c r="C368" s="106" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D368" s="106" t="s">
         <v>70</v>
@@ -11648,7 +11861,7 @@
         <v>0</v>
       </c>
       <c r="G368" s="103" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H368" s="103">
         <v>46268</v>
@@ -11661,13 +11874,13 @@
         <v>17</v>
       </c>
       <c r="C369" s="28" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D369" s="28" t="s">
         <v>34</v>
       </c>
       <c r="E369" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F369" s="30">
         <v>0</v>
@@ -11680,71 +11893,75 @@
       <c r="J369" s="1"/>
     </row>
     <row r="370" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B370" s="28" t="s">
+      <c r="B370" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C370" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="D370" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="E370" s="29">
+      <c r="C370" s="106" t="s">
+        <v>277</v>
+      </c>
+      <c r="D370" s="106" t="s">
+        <v>352</v>
+      </c>
+      <c r="E370" s="107">
         <v>1</v>
       </c>
-      <c r="F370" s="30">
+      <c r="F370" s="108">
         <v>1</v>
       </c>
-      <c r="G370" s="103"/>
-      <c r="H370" s="103"/>
+      <c r="G370" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="H370" s="103">
+        <v>46268</v>
+      </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
     </row>
     <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B371" s="106" t="s">
+      <c r="B371" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C371" s="106" t="s">
-        <v>399</v>
-      </c>
-      <c r="D371" s="106" t="s">
-        <v>400</v>
-      </c>
-      <c r="E371" s="107">
-        <v>1</v>
-      </c>
-      <c r="F371" s="108">
+      <c r="C371" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="D371" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="E371" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F371" s="30">
         <v>0</v>
       </c>
-      <c r="G371" s="103" t="s">
-        <v>417</v>
-      </c>
-      <c r="H371" s="103">
-        <v>46254</v>
-      </c>
+      <c r="G371" s="103">
+        <v>46268</v>
+      </c>
+      <c r="H371" s="103"/>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
     </row>
     <row r="372" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B372" s="28" t="s">
+      <c r="B372" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C372" s="28" t="s">
-        <v>420</v>
-      </c>
-      <c r="D372" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E372" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="F372" s="30">
+      <c r="C372" s="106" t="s">
+        <v>396</v>
+      </c>
+      <c r="D372" s="106" t="s">
+        <v>397</v>
+      </c>
+      <c r="E372" s="107">
+        <v>1</v>
+      </c>
+      <c r="F372" s="108">
         <v>0</v>
       </c>
-      <c r="G372" s="103">
+      <c r="G372" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="H372" s="103">
         <v>46254</v>
       </c>
-      <c r="H372" s="103"/>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
     </row>
@@ -11753,28 +11970,40 @@
         <v>17</v>
       </c>
       <c r="C373" s="28" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="D373" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="E373" s="29">
-        <v>20</v>
+        <v>73</v>
+      </c>
+      <c r="E373" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F373" s="30">
         <v>0</v>
       </c>
-      <c r="G373" s="103"/>
+      <c r="G373" s="103">
+        <v>46254</v>
+      </c>
       <c r="H373" s="103"/>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
     </row>
     <row r="374" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B374" s="106"/>
-      <c r="C374" s="106"/>
-      <c r="D374" s="106"/>
-      <c r="E374" s="107"/>
-      <c r="F374" s="108"/>
+      <c r="B374" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C374" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="D374" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="E374" s="29">
+        <v>20</v>
+      </c>
+      <c r="F374" s="30">
+        <v>0</v>
+      </c>
       <c r="G374" s="103"/>
       <c r="H374" s="103"/>
       <c r="I374" s="1"/>
@@ -11812,7 +12041,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -11822,10 +12051,10 @@
     <row r="380" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="1"/>
       <c r="C380" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D380" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="D380" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="E380" s="2"/>
       <c r="F380" s="1"/>
@@ -12105,7 +12334,7 @@
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
       <c r="D4" s="43" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="41"/>
@@ -12165,13 +12394,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="25">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="26">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G7" s="27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H7" s="111"/>
       <c r="I7" s="41"/>
@@ -12190,13 +12419,13 @@
         <v>29</v>
       </c>
       <c r="E8" s="25">
+        <v>11</v>
+      </c>
+      <c r="F8" s="56">
+        <v>18</v>
+      </c>
+      <c r="G8" s="57">
         <v>7</v>
-      </c>
-      <c r="F8" s="26">
-        <v>12</v>
-      </c>
-      <c r="G8" s="27">
-        <v>5</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -12209,19 +12438,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D9" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="25">
+        <v>9</v>
+      </c>
+      <c r="F9" s="26">
         <v>15</v>
       </c>
-      <c r="E9" s="25">
+      <c r="G9" s="27">
         <v>6</v>
-      </c>
-      <c r="F9" s="26">
-        <v>7</v>
-      </c>
-      <c r="G9" s="27">
-        <v>1</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -12234,19 +12463,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>135</v>
+        <v>50</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>157</v>
       </c>
       <c r="E10" s="25">
-        <v>5</v>
-      </c>
-      <c r="F10" s="56">
-        <v>10</v>
-      </c>
-      <c r="G10" s="57">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="F10" s="26">
+        <v>8</v>
+      </c>
+      <c r="G10" s="27">
+        <v>1</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="41"/>
@@ -12259,19 +12488,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>158</v>
+        <v>21</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>265</v>
       </c>
       <c r="E11" s="25">
         <v>5</v>
       </c>
       <c r="F11" s="26">
+        <v>10</v>
+      </c>
+      <c r="G11" s="27">
         <v>5</v>
-      </c>
-      <c r="G11" s="27">
-        <v>0</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="41"/>
@@ -12281,22 +12510,22 @@
     <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47"/>
       <c r="B12" s="54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>344</v>
+        <v>33</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="E12" s="25">
-        <v>3</v>
-      </c>
-      <c r="F12" s="56">
-        <v>7</v>
-      </c>
-      <c r="G12" s="57">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="F12" s="26">
+        <v>10</v>
+      </c>
+      <c r="G12" s="27">
+        <v>5</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -12309,19 +12538,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="E13" s="25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13" s="26">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" s="27">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="41"/>
@@ -12334,19 +12563,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>266</v>
+        <v>322</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>341</v>
       </c>
       <c r="E14" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" s="26">
+        <v>10</v>
+      </c>
+      <c r="G14" s="27">
         <v>6</v>
-      </c>
-      <c r="G14" s="27">
-        <v>4</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="41"/>
@@ -12359,19 +12588,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>343</v>
+        <v>25</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>402</v>
+        <v>125</v>
       </c>
       <c r="E15" s="25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="26">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G15" s="27">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="41"/>
@@ -12384,19 +12613,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>32</v>
+        <v>141</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>142</v>
       </c>
       <c r="E16" s="25">
-        <v>1</v>
-      </c>
-      <c r="F16" s="26">
-        <v>6</v>
-      </c>
-      <c r="G16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="56">
         <v>5</v>
+      </c>
+      <c r="G16" s="57">
+        <v>3</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -12409,19 +12638,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>142</v>
+        <v>340</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>143</v>
+        <v>399</v>
       </c>
       <c r="E17" s="25">
         <v>1</v>
       </c>
-      <c r="F17" s="26">
-        <v>4</v>
-      </c>
-      <c r="G17" s="27">
-        <v>3</v>
+      <c r="F17" s="56">
+        <v>11</v>
+      </c>
+      <c r="G17" s="57">
+        <v>10</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -12434,19 +12663,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E18" s="25">
-        <v>-3</v>
-      </c>
-      <c r="F18" s="56">
-        <v>4</v>
-      </c>
-      <c r="G18" s="57">
-        <v>7</v>
+        <v>-2</v>
+      </c>
+      <c r="F18" s="26">
+        <v>6</v>
+      </c>
+      <c r="G18" s="27">
+        <v>8</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -12459,16 +12688,16 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E19" s="25">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F19" s="26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="27">
         <v>6</v>
@@ -12486,14 +12715,14 @@
       <c r="C20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="55" t="s">
-        <v>127</v>
+      <c r="D20" s="24" t="s">
+        <v>126</v>
       </c>
       <c r="E20" s="25">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="F20" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="27">
         <v>6</v>
@@ -12562,7 +12791,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -12599,10 +12828,10 @@
       <c r="F4" s="100"/>
       <c r="G4" s="100"/>
       <c r="I4" s="38" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12616,10 +12845,10 @@
       <c r="F5" s="64"/>
       <c r="G5" s="64"/>
       <c r="I5" s="38" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12633,10 +12862,10 @@
       <c r="F6" s="64"/>
       <c r="G6" s="64"/>
       <c r="I6" s="38" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12653,7 +12882,7 @@
         <v>38</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12678,7 +12907,7 @@
       <c r="F9" s="100"/>
       <c r="G9" s="100"/>
       <c r="I9" s="38" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12693,7 +12922,7 @@
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="67"/>
       <c r="B11" s="63" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C11" s="68"/>
       <c r="D11" s="64"/>
@@ -12787,7 +13016,7 @@
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="67"/>
       <c r="B20" s="63" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C20" s="68"/>
       <c r="D20" s="64"/>
@@ -12837,7 +13066,7 @@
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" s="65"/>
       <c r="C25" s="64"/>
@@ -12858,7 +13087,7 @@
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="67"/>
       <c r="B27" s="63" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C27" s="68"/>
       <c r="D27" s="64"/>
@@ -12868,7 +13097,7 @@
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B28" s="68"/>
       <c r="C28" s="64"/>
@@ -12897,7 +13126,7 @@
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="65"/>
       <c r="C31" s="64"/>
@@ -12957,7 +13186,7 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -13047,7 +13276,7 @@
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
       <c r="J4" s="98" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K4" s="38"/>
       <c r="L4" s="38"/>
@@ -13077,7 +13306,7 @@
       <c r="H5" s="38"/>
       <c r="I5" s="38"/>
       <c r="J5" s="98" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K5" s="38"/>
       <c r="L5" s="38"/>
@@ -13107,7 +13336,7 @@
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
       <c r="J6" s="98" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K6" s="38"/>
       <c r="L6" s="38"/>
@@ -13137,7 +13366,7 @@
       <c r="H7" s="38"/>
       <c r="I7" s="38"/>
       <c r="J7" s="98" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K7" s="38"/>
       <c r="L7" s="38"/>
@@ -13351,7 +13580,7 @@
     <row r="15" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A15" s="67"/>
       <c r="B15" s="63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C15" s="64"/>
       <c r="D15" s="64"/>
@@ -13433,7 +13662,7 @@
     <row r="18" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A18" s="67"/>
       <c r="B18" s="63" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="68"/>
       <c r="D18" s="64"/>
@@ -13516,7 +13745,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="65"/>
       <c r="C21" s="64"/>
@@ -13544,7 +13773,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B22" s="70"/>
       <c r="C22" s="100"/>
@@ -13572,7 +13801,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B23" s="65"/>
       <c r="C23" s="64"/>
@@ -13600,7 +13829,7 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24" s="65"/>
       <c r="C24" s="64"/>
@@ -13628,7 +13857,7 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" s="65"/>
       <c r="C25" s="64"/>
@@ -13656,7 +13885,7 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B26" s="65"/>
       <c r="C26" s="64"/>
@@ -13738,7 +13967,7 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" s="70"/>
       <c r="C29" s="100"/>
@@ -13766,7 +13995,7 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="67" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B30" s="70"/>
       <c r="C30" s="100"/>
@@ -13794,7 +14023,7 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" s="70"/>
       <c r="C31" s="100"/>
@@ -13822,7 +14051,7 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="67" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" s="70"/>
       <c r="C32" s="100"/>
@@ -13902,7 +14131,7 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="67" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="70"/>
       <c r="C35" s="100"/>
@@ -13930,7 +14159,7 @@
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B36" s="70"/>
       <c r="C36" s="100"/>
@@ -14010,7 +14239,7 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B39" s="65"/>
       <c r="C39" s="64"/>
@@ -14686,47 +14915,47 @@
   <sheetData>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J5" s="67" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N5" s="67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C6">
         <f>COUNTIF(Stats!D:D,'Player Count'!B6)</f>
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G6">
         <f>COUNTIF(Stats!D:D,'Player Count'!F6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K6">
         <f>COUNTIF(Stats!D:D,'Player Count'!J6)</f>
@@ -14734,7 +14963,7 @@
       </c>
       <c r="M6" s="109"/>
       <c r="N6" s="67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O6">
         <f>COUNTIF(Stats!D:D,'Player Count'!N6)</f>
@@ -14744,21 +14973,21 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C7">
         <f>COUNTIF(Stats!D:D,'Player Count'!B7)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G7">
         <f>COUNTIF(Stats!D:D,'Player Count'!F7)</f>
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K7">
         <f>COUNTIF(Stats!D:D,'Player Count'!J7)</f>
@@ -14766,7 +14995,7 @@
       </c>
       <c r="M7" s="109"/>
       <c r="N7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O7">
         <f>COUNTIF(Stats!D:D,'Player Count'!N7)</f>
@@ -14776,21 +15005,21 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C8">
         <f>COUNTIF(Stats!D:D,'Player Count'!B8)</f>
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G8">
         <f>COUNTIF(Stats!D:D,'Player Count'!F8)</f>
         <v>2</v>
       </c>
       <c r="J8" s="67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K8">
         <f>COUNTIF(Stats!D:D,'Player Count'!J8)</f>
@@ -14798,7 +15027,7 @@
       </c>
       <c r="M8" s="109"/>
       <c r="N8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O8">
         <f>COUNTIF(Stats!D:D,'Player Count'!N8)</f>
@@ -14808,21 +15037,21 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C9">
         <f>COUNTIF(Stats!D:D,'Player Count'!B9)</f>
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G9">
         <f>COUNTIF(Stats!D:D,'Player Count'!F9)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="67" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K9">
         <f>COUNTIF(Stats!D:D,'Player Count'!J9)</f>
@@ -14830,7 +15059,7 @@
       </c>
       <c r="M9" s="109"/>
       <c r="N9" s="67" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O9">
         <f>COUNTIF(Stats!D:D,'Player Count'!N9)</f>
@@ -14840,21 +15069,21 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10">
         <f>COUNTIF(Stats!D:D,'Player Count'!B10)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G10">
         <f>COUNTIF(Stats!D:D,'Player Count'!F10)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="67" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K10">
         <f>COUNTIF(Stats!D:D,'Player Count'!J10)</f>
@@ -14862,7 +15091,7 @@
       </c>
       <c r="M10" s="109"/>
       <c r="N10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O10">
         <f>COUNTIF(Stats!D:D,'Player Count'!N10)</f>
@@ -14872,21 +15101,21 @@
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="67" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C11">
         <f>COUNTIF(Stats!D:D,'Player Count'!B11)</f>
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G11">
         <f>COUNTIF(Stats!D:D,'Player Count'!F11)</f>
         <v>2</v>
       </c>
       <c r="J11" s="67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K11">
         <f>COUNTIF(Stats!D:D,'Player Count'!J11)</f>
@@ -14894,7 +15123,7 @@
       </c>
       <c r="M11" s="109"/>
       <c r="N11" s="67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O11">
         <f>COUNTIF(Stats!D:D,'Player Count'!N11)</f>
@@ -14904,21 +15133,21 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C12">
         <f>COUNTIF(Stats!D:D,'Player Count'!B12)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="67" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G12">
         <f>COUNTIF(Stats!D:D,'Player Count'!F12)</f>
         <v>1</v>
       </c>
       <c r="J12" s="67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K12">
         <f>COUNTIF(Stats!D:D,'Player Count'!J12)</f>
@@ -14926,7 +15155,7 @@
       </c>
       <c r="M12" s="109"/>
       <c r="N12" s="67" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O12">
         <f>COUNTIF(Stats!D:D,'Player Count'!N12)</f>
@@ -14936,29 +15165,29 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C13">
         <f>COUNTIF(Stats!D:D,'Player Count'!B13)</f>
         <v>3</v>
       </c>
       <c r="F13" s="67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G13">
         <f>COUNTIF(Stats!D:D,'Player Count'!F13)</f>
         <v>0</v>
       </c>
       <c r="J13" s="67" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K13">
         <f>COUNTIF(Stats!D:D,'Player Count'!J13)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="109"/>
       <c r="N13" s="67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O13">
         <f>COUNTIF(Stats!D:D,'Player Count'!N13)</f>
@@ -14968,21 +15197,21 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C14">
         <f>COUNTIF(Stats!D:D,'Player Count'!B14)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="67" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G14">
         <f>COUNTIF(Stats!D:D,'Player Count'!F14)</f>
         <v>0</v>
       </c>
       <c r="J14" s="67" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K14">
         <f>COUNTIF(Stats!D:D,'Player Count'!J14)</f>
@@ -14990,7 +15219,7 @@
       </c>
       <c r="M14" s="109"/>
       <c r="N14" s="67" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O14">
         <f>COUNTIF(Stats!D:D,'Player Count'!N14)</f>
@@ -15000,29 +15229,29 @@
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15">
         <f>COUNTIF(Stats!D:D,'Player Count'!B15)</f>
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G15">
         <f>COUNTIF(Stats!D:D,'Player Count'!F15)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K15">
         <f>COUNTIF(Stats!D:D,'Player Count'!J15)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" s="109"/>
       <c r="N15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O15">
         <f>COUNTIF(Stats!D:D,'Player Count'!N15)</f>
@@ -15032,53 +15261,53 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C16">
         <f>COUNTIF(Stats!D:D,'Player Count'!B16)</f>
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G16">
         <f>COUNTIF(Stats!D:D,'Player Count'!F16)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="67" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K16">
         <f>COUNTIF(Stats!D:D,'Player Count'!J16)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" s="109"/>
       <c r="N16" s="67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O16">
         <f>COUNTIF(Stats!D:D,'Player Count'!N16)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="109"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C17">
         <f>COUNTIF(Stats!D:D,'Player Count'!B17)</f>
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G17">
         <f>COUNTIF(Stats!D:D,'Player Count'!F17)</f>
         <v>2</v>
       </c>
       <c r="J17" s="67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K17">
         <f>COUNTIF(Stats!D:D,'Player Count'!J17)</f>
@@ -15086,7 +15315,7 @@
       </c>
       <c r="M17" s="109"/>
       <c r="N17" s="67" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O17">
         <f>COUNTIF(Stats!D:D,'Player Count'!N17)</f>
@@ -15096,21 +15325,21 @@
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18">
         <f>COUNTIF(Stats!D:D,'Player Count'!B18)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="67" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G18">
         <f>COUNTIF(Stats!D:D,'Player Count'!F18)</f>
         <v>4</v>
       </c>
       <c r="J18" s="67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K18">
         <f>COUNTIF(Stats!D:D,'Player Count'!J18)</f>
@@ -15118,31 +15347,31 @@
       </c>
       <c r="M18" s="109"/>
       <c r="N18" s="67" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O18">
         <f>COUNTIF(Stats!D:D,'Player Count'!N18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="109"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C19">
         <f>COUNTIF(Stats!D:D,'Player Count'!B19)</f>
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G19">
         <f>COUNTIF(Stats!D:D,'Player Count'!F19)</f>
         <v>1</v>
       </c>
       <c r="J19" s="67" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K19">
         <f>COUNTIF(Stats!D:D,'Player Count'!J19)</f>
@@ -15150,31 +15379,31 @@
       </c>
       <c r="M19" s="109"/>
       <c r="N19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O19">
         <f>COUNTIF(Stats!D:D,'Player Count'!N19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="109"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C20">
         <f>COUNTIF(Stats!D:D,'Player Count'!B20)</f>
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G20">
         <f>COUNTIF(Stats!D:D,'Player Count'!F20)</f>
         <v>0</v>
       </c>
       <c r="J20" s="67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K20">
         <f>COUNTIF(Stats!D:D,'Player Count'!J20)</f>
@@ -15182,31 +15411,31 @@
       </c>
       <c r="M20" s="109"/>
       <c r="N20" s="67" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O20">
         <f>COUNTIF(Stats!D:D,'Player Count'!N20)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="109"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C21">
         <f>COUNTIF(Stats!D:D,'Player Count'!B21)</f>
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G21">
         <f>COUNTIF(Stats!D:D,'Player Count'!F21)</f>
         <v>2</v>
       </c>
       <c r="J21" s="67" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K21">
         <f>COUNTIF(Stats!D:D,'Player Count'!J21)</f>
@@ -15214,7 +15443,7 @@
       </c>
       <c r="M21" s="109"/>
       <c r="N21" s="67" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O21">
         <f>COUNTIF(Stats!D:D,'Player Count'!N21)</f>
@@ -15224,21 +15453,21 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22">
         <f>COUNTIF(Stats!D:D,'Player Count'!B22)</f>
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G22">
         <f>COUNTIF(Stats!D:D,'Player Count'!F22)</f>
         <v>2</v>
       </c>
       <c r="J22" s="67" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K22">
         <f>COUNTIF(Stats!D:D,'Player Count'!J22)</f>
@@ -15246,7 +15475,7 @@
       </c>
       <c r="M22" s="109"/>
       <c r="N22" s="67" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O22">
         <f>COUNTIF(Stats!D:D,'Player Count'!N22)</f>
@@ -15256,21 +15485,21 @@
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23">
         <f>COUNTIF(Stats!D:D,'Player Count'!B23)</f>
         <v>5</v>
       </c>
       <c r="F23" s="67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G23">
         <f>COUNTIF(Stats!D:D,'Player Count'!F23)</f>
         <v>5</v>
       </c>
       <c r="J23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K23">
         <f>COUNTIF(Stats!D:D,'Player Count'!J23)</f>
@@ -15278,7 +15507,7 @@
       </c>
       <c r="M23" s="109"/>
       <c r="N23" s="67" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O23">
         <f>COUNTIF(Stats!D:D,'Player Count'!N23)</f>
@@ -15288,29 +15517,29 @@
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" s="67" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C24">
         <f>COUNTIF(Stats!D:D,'Player Count'!B24)</f>
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G24">
         <f>COUNTIF(Stats!D:D,'Player Count'!F24)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" s="67" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K24">
         <f>COUNTIF(Stats!D:D,'Player Count'!J24)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24" s="109"/>
       <c r="N24" s="67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O24">
         <f>COUNTIF(Stats!D:D,'Player Count'!N24)</f>
@@ -15320,21 +15549,21 @@
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="67" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25">
         <f>COUNTIF(Stats!D:D,'Player Count'!B25)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G25">
         <f>COUNTIF(Stats!D:D,'Player Count'!F25)</f>
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K25">
         <f>COUNTIF(Stats!D:D,'Player Count'!J25)</f>
@@ -15342,7 +15571,7 @@
       </c>
       <c r="M25" s="109"/>
       <c r="N25" s="67" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O25">
         <f>COUNTIF(Stats!D:D,'Player Count'!N25)</f>
@@ -15352,21 +15581,21 @@
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" s="78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G26">
         <f>COUNTIF(Stats!D:D,'Player Count'!F26)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" s="67" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K26">
         <f>COUNTIF(Stats!D:D,'Player Count'!J26)</f>
@@ -15374,7 +15603,7 @@
       </c>
       <c r="M26" s="109"/>
       <c r="N26" s="67" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O26">
         <f>COUNTIF(Stats!D:D,'Player Count'!N26)</f>
@@ -15384,14 +15613,14 @@
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G27">
         <f>COUNTIF(Stats!D:D,'Player Count'!F27)</f>
         <v>0</v>
       </c>
       <c r="J27" s="67" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K27">
         <f>COUNTIF(Stats!D:D,'Player Count'!J27)</f>
@@ -15399,7 +15628,7 @@
       </c>
       <c r="M27" s="109"/>
       <c r="N27" s="67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O27">
         <f>COUNTIF(Stats!D:D,'Player Count'!N27)</f>
@@ -15409,14 +15638,14 @@
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G28">
         <f>COUNTIF(Stats!D:D,'Player Count'!F28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K28">
         <f>COUNTIF(Stats!D:D,'Player Count'!J28)</f>
@@ -15424,31 +15653,31 @@
       </c>
       <c r="M28" s="109"/>
       <c r="N28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O28">
         <f>COUNTIF(Stats!D:D,'Player Count'!N28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="109"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G29">
         <f>COUNTIF(Stats!D:D,'Player Count'!F29)</f>
         <v>2</v>
       </c>
       <c r="J29" s="67" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K29">
         <f>COUNTIF(Stats!D:D,'Player Count'!J29)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="67" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O29">
         <f>COUNTIF(Stats!D:D,'Player Count'!N29)</f>
@@ -15458,25 +15687,25 @@
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" s="67"/>
       <c r="F30" s="78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G30" s="78">
         <f>SUM(G6:G29)</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J30" s="78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N30" s="78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
@@ -15496,32 +15725,32 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.44311377245508982</v>
+        <v>0.43820224719101125</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.23952095808383234</v>
+        <v>0.21348314606741572</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.17964071856287425</v>
+        <v>0.20224719101123595</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.1377245508982036</v>
+        <v>0.14606741573033707</v>
       </c>
     </row>
   </sheetData>
@@ -15544,60 +15773,60 @@
   <sheetData>
     <row r="5" spans="6:24" x14ac:dyDescent="0.3">
       <c r="G5" s="67" t="s">
+        <v>321</v>
+      </c>
+      <c r="H5" s="67" t="s">
         <v>324</v>
       </c>
-      <c r="H5" s="67" t="s">
+      <c r="I5" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="J5" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="K5" s="67" t="s">
         <v>327</v>
       </c>
-      <c r="I5" s="67" t="s">
+      <c r="L5" s="67" t="s">
         <v>328</v>
       </c>
-      <c r="J5" s="67" t="s">
+      <c r="M5" s="67" t="s">
         <v>329</v>
       </c>
-      <c r="K5" s="67" t="s">
+      <c r="N5" s="67" t="s">
         <v>330</v>
       </c>
-      <c r="L5" s="67" t="s">
+      <c r="O5" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="M5" s="67" t="s">
+      <c r="P5" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="N5" s="67" t="s">
+      <c r="Q5" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="O5" s="67" t="s">
+      <c r="R5" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="P5" s="67" t="s">
+      <c r="S5" s="67" t="s">
+        <v>334</v>
+      </c>
+      <c r="T5" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="Q5" s="67" t="s">
+      <c r="U5" s="67" t="s">
         <v>336</v>
       </c>
-      <c r="R5" s="67" t="s">
+      <c r="V5" s="67" t="s">
         <v>337</v>
       </c>
-      <c r="S5" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="T5" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="U5" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="V5" s="67" t="s">
-        <v>340</v>
-      </c>
       <c r="W5" s="67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="113">
         <v>-20</v>
@@ -15638,7 +15867,7 @@
         <v>280</v>
       </c>
       <c r="X6" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="6:24" x14ac:dyDescent="0.3">
@@ -15680,7 +15909,7 @@
         <v>210</v>
       </c>
       <c r="X7" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="6:24" x14ac:dyDescent="0.3">
@@ -15804,7 +16033,7 @@
         <v>-65</v>
       </c>
       <c r="X10" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="6:24" x14ac:dyDescent="0.3">
@@ -15844,7 +16073,7 @@
         <v>-45</v>
       </c>
       <c r="X11" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="6:24" x14ac:dyDescent="0.3">
@@ -15888,7 +16117,7 @@
         <v>5</v>
       </c>
       <c r="X12" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="6:24" x14ac:dyDescent="0.3">
@@ -15922,7 +16151,7 @@
         <v>-35</v>
       </c>
       <c r="X13" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="6:24" x14ac:dyDescent="0.3">
@@ -15964,12 +16193,12 @@
         <v>-45</v>
       </c>
       <c r="X14" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G15" s="113">
         <v>-20</v>
@@ -16049,12 +16278,12 @@
         <v>-60</v>
       </c>
       <c r="X16" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="113">
         <v>-20</v>
@@ -16089,7 +16318,7 @@
     </row>
     <row r="18" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F18" s="67" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G18" s="113">
         <v>-20</v>
@@ -16118,12 +16347,12 @@
         <v>-35</v>
       </c>
       <c r="X18" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F19" s="67" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G19" s="113">
         <v>-20</v>

--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1240" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA0DF0CC-B9A5-4491-BE58-A8EF076EE83D}"/>
+  <xr:revisionPtr revIDLastSave="1330" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1A2389-ED17-4E57-A138-F1DE0706B28B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="454">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1389,6 +1389,18 @@
   </si>
   <si>
     <t>DAVIS KEILLOR DUNN</t>
+  </si>
+  <si>
+    <t>CHARLIE MCCANN</t>
+  </si>
+  <si>
+    <t>CHELTENHAM</t>
+  </si>
+  <si>
+    <t>MARCUS RASHFORD</t>
+  </si>
+  <si>
+    <t>AARON COLLINS</t>
   </si>
 </sst>
 </file>
@@ -3444,15 +3456,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3471,7 +3483,7 @@
         <v>413</v>
       </c>
       <c r="F6" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="86">
         <v>46275</v>
@@ -3489,11 +3501,11 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
@@ -3524,15 +3536,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3568,11 +3580,11 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
@@ -3610,11 +3622,11 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
@@ -3642,15 +3654,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R10" s="118"/>
       <c r="S10" s="118"/>
@@ -3689,11 +3701,11 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
@@ -3738,15 +3750,15 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3782,11 +3794,11 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
@@ -3813,7 +3825,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="87"/>
       <c r="H14" s="84"/>
@@ -3829,15 +3841,15 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -3864,15 +3876,15 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3890,7 +3902,7 @@
         <v>17</v>
       </c>
       <c r="F16" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="84"/>
       <c r="H16" s="84"/>
@@ -3910,11 +3922,11 @@
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3932,7 +3944,7 @@
         <v>28</v>
       </c>
       <c r="F17" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="84"/>
       <c r="H17" s="84"/>
@@ -3948,15 +3960,15 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R17" s="118"/>
       <c r="S17" s="118"/>
@@ -3995,15 +4007,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4087,7 +4099,7 @@
         <v>413</v>
       </c>
       <c r="F21" s="30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G21" s="87">
         <v>46261</v>
@@ -4191,7 +4203,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4511,7 +4523,7 @@
         <v>43</v>
       </c>
       <c r="F40" s="30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G40" s="87"/>
       <c r="H40" s="91"/>
@@ -4657,7 +4669,7 @@
         <v>413</v>
       </c>
       <c r="F46" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="91">
         <v>46261</v>
@@ -4804,7 +4816,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -4957,7 +4969,7 @@
         <v>413</v>
       </c>
       <c r="F60" s="21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60" s="86">
         <v>46268</v>
@@ -5134,7 +5146,7 @@
         <v>17</v>
       </c>
       <c r="F67" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" s="83"/>
       <c r="H67" s="91"/>
@@ -5192,7 +5204,7 @@
         <v>413</v>
       </c>
       <c r="F69" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="91">
         <v>46261</v>
@@ -5221,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="F70" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" s="87"/>
       <c r="H70" s="91"/>
@@ -5302,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" s="87"/>
       <c r="H73" s="91"/>
@@ -5437,7 +5449,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -5707,23 +5719,27 @@
     </row>
     <row r="93" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="79"/>
-      <c r="B93" s="28" t="s">
+      <c r="B93" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C93" s="28" t="s">
+      <c r="C93" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="D93" s="28" t="s">
+      <c r="D93" s="106" t="s">
         <v>359</v>
       </c>
-      <c r="E93" s="29">
+      <c r="E93" s="107">
         <v>1</v>
       </c>
-      <c r="F93" s="30">
+      <c r="F93" s="108">
         <v>0</v>
       </c>
-      <c r="G93" s="91"/>
-      <c r="H93" s="91"/>
+      <c r="G93" s="91" t="s">
+        <v>414</v>
+      </c>
+      <c r="H93" s="91">
+        <v>46275</v>
+      </c>
       <c r="I93" s="91"/>
       <c r="J93" s="76"/>
       <c r="K93" s="1"/>
@@ -5738,18 +5754,20 @@
         <v>16</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>143</v>
+        <v>453</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E94" s="29">
-        <v>10</v>
+        <v>359</v>
+      </c>
+      <c r="E94" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F94" s="30">
-        <v>2</v>
-      </c>
-      <c r="G94" s="91"/>
+        <v>1</v>
+      </c>
+      <c r="G94" s="91">
+        <v>46275</v>
+      </c>
       <c r="H94" s="91"/>
       <c r="I94" s="90"/>
       <c r="J94" s="76"/>
@@ -5761,11 +5779,21 @@
     </row>
     <row r="95" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="79"/>
-      <c r="B95" s="28"/>
-      <c r="C95" s="28"/>
-      <c r="D95" s="28"/>
-      <c r="E95" s="29"/>
-      <c r="F95" s="30"/>
+      <c r="B95" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" s="29">
+        <v>10</v>
+      </c>
+      <c r="F95" s="30">
+        <v>3</v>
+      </c>
       <c r="G95" s="91"/>
       <c r="H95" s="91"/>
       <c r="I95" s="90"/>
@@ -5953,7 +5981,7 @@
         <v>413</v>
       </c>
       <c r="F102" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G102" s="87">
         <v>46254</v>
@@ -5982,7 +6010,7 @@
         <v>48</v>
       </c>
       <c r="F103" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="87"/>
       <c r="H103" s="91"/>
@@ -6056,7 +6084,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6501,7 +6529,7 @@
         <v>413</v>
       </c>
       <c r="F126" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="87">
         <v>46261</v>
@@ -6707,7 +6735,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -6831,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="F140" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G140" s="80"/>
       <c r="H140" s="94"/>
@@ -7010,23 +7038,27 @@
     </row>
     <row r="148" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="79"/>
-      <c r="B148" s="28" t="s">
+      <c r="B148" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C148" s="28" t="s">
+      <c r="C148" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="D148" s="28" t="s">
+      <c r="D148" s="106" t="s">
         <v>352</v>
       </c>
-      <c r="E148" s="29">
+      <c r="E148" s="107">
         <v>6</v>
       </c>
-      <c r="F148" s="30">
+      <c r="F148" s="108">
         <v>3</v>
       </c>
-      <c r="G148" s="87"/>
-      <c r="H148" s="91"/>
+      <c r="G148" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H148" s="91">
+        <v>46275</v>
+      </c>
       <c r="I148" s="90"/>
       <c r="J148" s="96"/>
       <c r="K148" s="1"/>
@@ -7041,18 +7073,20 @@
         <v>16</v>
       </c>
       <c r="C149" s="28" t="s">
-        <v>367</v>
+        <v>452</v>
       </c>
       <c r="D149" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E149" s="29">
-        <v>2</v>
+        <v>59</v>
+      </c>
+      <c r="E149" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F149" s="30">
-        <v>4</v>
-      </c>
-      <c r="G149" s="87"/>
+        <v>0</v>
+      </c>
+      <c r="G149" s="87">
+        <v>46275</v>
+      </c>
       <c r="H149" s="91"/>
       <c r="I149" s="90"/>
       <c r="J149" s="76"/>
@@ -7064,11 +7098,21 @@
     </row>
     <row r="150" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="79"/>
-      <c r="B150" s="28"/>
-      <c r="C150" s="28"/>
-      <c r="D150" s="28"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="30"/>
+      <c r="B150" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="D150" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E150" s="29">
+        <v>2</v>
+      </c>
+      <c r="F150" s="30">
+        <v>4</v>
+      </c>
       <c r="G150" s="87"/>
       <c r="H150" s="91"/>
       <c r="I150" s="90"/>
@@ -7121,7 +7165,7 @@
         <v>33</v>
       </c>
       <c r="F152" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G152" s="87"/>
       <c r="H152" s="91"/>
@@ -7148,7 +7192,7 @@
         <v>13</v>
       </c>
       <c r="F153" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G153" s="87"/>
       <c r="H153" s="91"/>
@@ -7175,7 +7219,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G154" s="87"/>
       <c r="H154" s="91"/>
@@ -7340,7 +7384,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -7623,7 +7667,7 @@
         <v>12</v>
       </c>
       <c r="F174" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G174" s="91"/>
       <c r="H174" s="91"/>
@@ -7711,7 +7755,7 @@
         <v>23</v>
       </c>
       <c r="F178" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G178" s="91"/>
       <c r="H178" s="91"/>
@@ -7738,7 +7782,7 @@
         <v>24</v>
       </c>
       <c r="F179" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G179" s="83"/>
       <c r="H179" s="91"/>
@@ -7765,7 +7809,7 @@
         <v>7</v>
       </c>
       <c r="F180" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G180" s="91"/>
       <c r="H180" s="91"/>
@@ -7927,7 +7971,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -8051,7 +8095,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -8358,7 +8402,7 @@
         <v>10</v>
       </c>
       <c r="F207" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G207" s="83"/>
       <c r="H207" s="90"/>
@@ -8385,7 +8429,7 @@
         <v>5</v>
       </c>
       <c r="F208" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G208" s="83"/>
       <c r="H208" s="91"/>
@@ -8530,7 +8574,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -8860,23 +8904,27 @@
     </row>
     <row r="230" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="79"/>
-      <c r="B230" s="28" t="s">
+      <c r="B230" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C230" s="28" t="s">
+      <c r="C230" s="106" t="s">
         <v>283</v>
       </c>
-      <c r="D230" s="28" t="s">
+      <c r="D230" s="106" t="s">
         <v>433</v>
       </c>
-      <c r="E230" s="29">
+      <c r="E230" s="107">
         <v>6</v>
       </c>
-      <c r="F230" s="30">
+      <c r="F230" s="108">
         <v>0</v>
       </c>
-      <c r="G230" s="87"/>
-      <c r="H230" s="91"/>
+      <c r="G230" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H230" s="91">
+        <v>46282</v>
+      </c>
       <c r="I230" s="89"/>
       <c r="J230" s="76"/>
       <c r="K230" s="1"/>
@@ -8887,12 +8935,24 @@
     </row>
     <row r="231" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="79"/>
-      <c r="B231" s="28"/>
-      <c r="C231" s="28"/>
-      <c r="D231" s="28"/>
-      <c r="E231" s="29"/>
-      <c r="F231" s="30"/>
-      <c r="G231" s="87"/>
+      <c r="B231" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C231" s="28" t="s">
+        <v>450</v>
+      </c>
+      <c r="D231" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="E231" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F231" s="30">
+        <v>0</v>
+      </c>
+      <c r="G231" s="87">
+        <v>46282</v>
+      </c>
       <c r="H231" s="91"/>
       <c r="I231" s="89"/>
       <c r="J231" s="76"/>
@@ -8944,7 +9004,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G233" s="87"/>
       <c r="H233" s="91"/>
@@ -9149,7 +9209,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -9273,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G248" s="80"/>
       <c r="H248" s="94"/>
@@ -9405,7 +9465,7 @@
         <v>16</v>
       </c>
       <c r="F254" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G254" s="91"/>
       <c r="H254" s="91"/>
@@ -9628,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="F263" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263" s="87"/>
       <c r="H263" s="91"/>
@@ -9736,7 +9796,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -9860,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="F275" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G275" s="80"/>
       <c r="H275" s="94"/>
@@ -10188,7 +10248,7 @@
         <v>1</v>
       </c>
       <c r="F289" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" s="87"/>
       <c r="H289" s="91"/>
@@ -10323,7 +10383,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -10476,7 +10536,7 @@
         <v>413</v>
       </c>
       <c r="F303" s="21">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G303" s="87">
         <v>46261</v>
@@ -10724,7 +10784,7 @@
         <v>78</v>
       </c>
       <c r="F313" s="30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -10782,7 +10842,7 @@
         <v>413</v>
       </c>
       <c r="F315" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G315" s="87">
         <v>46268</v>
@@ -10811,7 +10871,7 @@
         <v>1</v>
       </c>
       <c r="F316" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G316" s="87"/>
       <c r="H316" s="91"/>
@@ -11096,7 +11156,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -11244,7 +11304,7 @@
         <v>10</v>
       </c>
       <c r="F335" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G335" s="87"/>
       <c r="H335" s="91"/>
@@ -11372,7 +11432,7 @@
         <v>9</v>
       </c>
       <c r="F340" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G340" s="87"/>
       <c r="H340" s="90"/>
@@ -11558,7 +11618,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -11640,7 +11700,7 @@
         <v>3</v>
       </c>
       <c r="F356" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -11736,7 +11796,7 @@
         <v>15</v>
       </c>
       <c r="F362" s="30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G362" s="1"/>
       <c r="H362" s="103"/>
@@ -11803,7 +11863,7 @@
         <v>413</v>
       </c>
       <c r="F365" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G365" s="103">
         <v>46268</v>
@@ -11837,7 +11897,7 @@
         <v>25</v>
       </c>
       <c r="F367" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="103"/>
@@ -12041,7 +12101,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -12394,13 +12454,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="25">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F7" s="26">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G7" s="27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="111"/>
       <c r="I7" s="41"/>
@@ -12413,19 +12473,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="E8" s="25">
-        <v>11</v>
-      </c>
-      <c r="F8" s="56">
-        <v>18</v>
-      </c>
-      <c r="G8" s="57">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="F8" s="26">
+        <v>15</v>
+      </c>
+      <c r="G8" s="27">
+        <v>5</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -12438,19 +12498,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>134</v>
+        <v>30</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>29</v>
       </c>
       <c r="E9" s="25">
         <v>9</v>
       </c>
-      <c r="F9" s="26">
-        <v>15</v>
-      </c>
-      <c r="G9" s="27">
-        <v>6</v>
+      <c r="F9" s="56">
+        <v>21</v>
+      </c>
+      <c r="G9" s="57">
+        <v>12</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -12463,19 +12523,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>157</v>
+        <v>265</v>
       </c>
       <c r="E10" s="25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" s="26">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G10" s="27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="41"/>
@@ -12488,19 +12548,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>265</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="E11" s="25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" s="26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11" s="27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="41"/>
@@ -12513,19 +12573,19 @@
         <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="E12" s="25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" s="26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" s="27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -12538,19 +12598,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>125</v>
       </c>
       <c r="E13" s="25">
-        <v>5</v>
-      </c>
-      <c r="F13" s="26">
-        <v>8</v>
-      </c>
-      <c r="G13" s="27">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="F13" s="56">
+        <v>19</v>
+      </c>
+      <c r="G13" s="57">
+        <v>13</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="41"/>
@@ -12563,19 +12623,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>322</v>
+        <v>141</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
       <c r="E14" s="25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" s="26">
         <v>10</v>
       </c>
       <c r="G14" s="27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="41"/>
@@ -12588,19 +12648,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E15" s="25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="26">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15" s="27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="41"/>
@@ -12613,19 +12673,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>141</v>
+        <v>322</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>142</v>
+        <v>341</v>
       </c>
       <c r="E16" s="25">
-        <v>2</v>
-      </c>
-      <c r="F16" s="56">
         <v>5</v>
       </c>
-      <c r="G16" s="57">
-        <v>3</v>
+      <c r="F16" s="26">
+        <v>12</v>
+      </c>
+      <c r="G16" s="27">
+        <v>7</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -12640,17 +12700,17 @@
       <c r="C17" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="24" t="s">
         <v>399</v>
       </c>
       <c r="E17" s="25">
-        <v>1</v>
-      </c>
-      <c r="F17" s="56">
+        <v>2</v>
+      </c>
+      <c r="F17" s="26">
+        <v>13</v>
+      </c>
+      <c r="G17" s="27">
         <v>11</v>
-      </c>
-      <c r="G17" s="57">
-        <v>10</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -12671,11 +12731,11 @@
       <c r="E18" s="25">
         <v>-2</v>
       </c>
-      <c r="F18" s="26">
-        <v>6</v>
-      </c>
-      <c r="G18" s="27">
-        <v>8</v>
+      <c r="F18" s="56">
+        <v>12</v>
+      </c>
+      <c r="G18" s="57">
+        <v>14</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -12688,16 +12748,16 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E19" s="25">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F19" s="26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="27">
         <v>6</v>
@@ -12713,19 +12773,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>126</v>
+        <v>92</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>105</v>
       </c>
       <c r="E20" s="25">
         <v>-4</v>
       </c>
       <c r="F20" s="26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G20" s="27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="41"/>
@@ -15063,7 +15123,7 @@
       </c>
       <c r="O9">
         <f>COUNTIF(Stats!D:D,'Player Count'!N9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="109"/>
     </row>
@@ -15361,7 +15421,7 @@
       </c>
       <c r="C19">
         <f>COUNTIF(Stats!D:D,'Player Count'!B19)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
         <v>201</v>
@@ -15471,7 +15531,7 @@
       </c>
       <c r="K22">
         <f>COUNTIF(Stats!D:D,'Player Count'!J22)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M22" s="109"/>
       <c r="N22" s="67" t="s">
@@ -15585,7 +15645,7 @@
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s">
         <v>208</v>
@@ -15698,14 +15758,14 @@
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N30" s="78" t="s">
         <v>186</v>
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
@@ -15729,28 +15789,28 @@
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.43820224719101125</v>
+        <v>0.43646408839779005</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.21348314606741572</v>
+        <v>0.20994475138121546</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20224719101123595</v>
+        <v>0.20441988950276244</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.14606741573033707</v>
+        <v>0.14917127071823205</v>
       </c>
     </row>
   </sheetData>

--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1061" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2D71B1-8827-4AE0-8AB7-3C525667647C}"/>
+  <xr:revisionPtr revIDLastSave="1330" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1A2389-ED17-4E57-A138-F1DE0706B28B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="454">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -267,9 +266,6 @@
     <t>BRISTOL CITY</t>
   </si>
   <si>
-    <t>CHARLTON</t>
-  </si>
-  <si>
     <t>PHIL FODEN</t>
   </si>
   <si>
@@ -888,9 +884,6 @@
     <t>DOM BALLARD</t>
   </si>
   <si>
-    <t>BURNLEY</t>
-  </si>
-  <si>
     <t>IGOR THIAGO</t>
   </si>
   <si>
@@ -957,9 +950,6 @@
     <t>FEMI AZEEZ</t>
   </si>
   <si>
-    <t>EXETER</t>
-  </si>
-  <si>
     <t>JACK CLARKE</t>
   </si>
   <si>
@@ -1348,6 +1338,69 @@
   </si>
   <si>
     <t>YOANNE WISSA</t>
+  </si>
+  <si>
+    <t>COLORADO RAPIDS</t>
+  </si>
+  <si>
+    <t>SHAQUILLE GWENGE</t>
+  </si>
+  <si>
+    <t>NEWPORT</t>
+  </si>
+  <si>
+    <t>JAMAL LOWE</t>
+  </si>
+  <si>
+    <t>EMIL RIIS</t>
+  </si>
+  <si>
+    <t>YUSUF AKHAMRICH</t>
+  </si>
+  <si>
+    <t>LEYTON ORIENT</t>
+  </si>
+  <si>
+    <t>DANE SCARLETT</t>
+  </si>
+  <si>
+    <t>AARON PRESSLEY</t>
+  </si>
+  <si>
+    <t>WALSALL</t>
+  </si>
+  <si>
+    <t>WEST BROM</t>
+  </si>
+  <si>
+    <t>JIMMY-JAY MORGAN</t>
+  </si>
+  <si>
+    <t>CALUM KAVANAGH</t>
+  </si>
+  <si>
+    <t>NOTTS COUNTY</t>
+  </si>
+  <si>
+    <t>WYCOMBE</t>
+  </si>
+  <si>
+    <t>KIERNAN DEWSBURY-HALL</t>
+  </si>
+  <si>
+    <t>DAVIS KEILLOR DUNN</t>
+  </si>
+  <si>
+    <t>CHARLIE MCCANN</t>
+  </si>
+  <si>
+    <t>CHELTENHAM</t>
+  </si>
+  <si>
+    <t>MARCUS RASHFORD</t>
+  </si>
+  <si>
+    <t>AARON COLLINS</t>
   </si>
 </sst>
 </file>
@@ -3372,21 +3425,25 @@
     </row>
     <row r="5" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="C5" s="115"/>
+      <c r="D5" s="114" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="116">
         <v>1</v>
       </c>
-      <c r="F5" s="15">
-        <v>4</v>
-      </c>
-      <c r="G5" s="83"/>
-      <c r="H5" s="84"/>
+      <c r="F5" s="117">
+        <v>7</v>
+      </c>
+      <c r="G5" s="83" t="s">
+        <v>414</v>
+      </c>
+      <c r="H5" s="84">
+        <v>46275</v>
+      </c>
       <c r="I5" s="85"/>
       <c r="J5" s="82"/>
       <c r="K5" s="16" t="str">
@@ -3399,15 +3456,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3415,12 +3472,22 @@
     </row>
     <row r="6" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
-      <c r="B6" s="21"/>
+      <c r="B6" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="86"/>
+      <c r="D6" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="F6" s="21">
+        <v>1</v>
+      </c>
+      <c r="G6" s="86">
+        <v>46275</v>
+      </c>
       <c r="H6" s="84"/>
       <c r="I6" s="81"/>
       <c r="J6" s="79"/>
@@ -3434,15 +3501,15 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3469,15 +3536,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3489,10 +3556,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E8" s="29">
         <v>1</v>
@@ -3513,15 +3580,15 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3530,10 +3597,10 @@
         <v>14</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" s="29">
         <v>2</v>
@@ -3555,11 +3622,11 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
@@ -3587,15 +3654,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R10" s="118"/>
       <c r="S10" s="118"/>
@@ -3609,10 +3676,10 @@
         <v>16</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" s="29">
         <v>8</v>
@@ -3634,11 +3701,11 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
@@ -3654,10 +3721,10 @@
         <v>16</v>
       </c>
       <c r="C12" s="106" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D12" s="106" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" s="107">
         <v>3</v>
@@ -3666,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H12" s="84">
         <v>46261</v>
@@ -3683,15 +3750,15 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3700,13 +3767,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F13" s="30">
         <v>0</v>
@@ -3727,15 +3794,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="118"/>
       <c r="S13" s="118"/>
@@ -3749,7 +3816,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D14" s="28" t="s">
         <v>31</v>
@@ -3758,7 +3825,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="87"/>
       <c r="H14" s="84"/>
@@ -3778,11 +3845,11 @@
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -3809,15 +3876,15 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3826,16 +3893,16 @@
         <v>17</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E16" s="29">
         <v>17</v>
       </c>
       <c r="F16" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="84"/>
       <c r="H16" s="84"/>
@@ -3851,15 +3918,15 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3868,7 +3935,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>19</v>
@@ -3877,7 +3944,7 @@
         <v>28</v>
       </c>
       <c r="F17" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="84"/>
       <c r="H17" s="84"/>
@@ -3893,15 +3960,15 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R17" s="118"/>
       <c r="S17" s="118"/>
@@ -3915,16 +3982,16 @@
         <v>17</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18" s="29">
         <v>1</v>
       </c>
       <c r="F18" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="83"/>
       <c r="H18" s="84"/>
@@ -3940,15 +4007,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -3960,7 +4027,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>57</v>
@@ -3969,7 +4036,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" s="87"/>
       <c r="H19" s="84"/>
@@ -3987,10 +4054,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="106" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" s="106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="107">
         <v>8</v>
@@ -3999,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H20" s="84">
         <v>46261</v>
@@ -4023,16 +4090,16 @@
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F21" s="30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G21" s="87">
         <v>46261</v>
@@ -4136,7 +4203,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4191,7 +4258,7 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>21</v>
@@ -4265,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" s="80"/>
       <c r="H32" s="94"/>
@@ -4317,10 +4384,10 @@
         <v>14</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="E35" s="29">
         <v>1</v>
@@ -4344,7 +4411,7 @@
         <v>14</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>24</v>
@@ -4388,7 +4455,7 @@
         <v>16</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D38" s="28" t="s">
         <v>22</v>
@@ -4420,16 +4487,16 @@
         <v>16</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E39" s="29">
         <v>11</v>
       </c>
       <c r="F39" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -4456,7 +4523,7 @@
         <v>43</v>
       </c>
       <c r="F40" s="30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G40" s="87"/>
       <c r="H40" s="91"/>
@@ -4508,16 +4575,16 @@
         <v>17</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E43" s="29">
         <v>1</v>
       </c>
       <c r="F43" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="87"/>
       <c r="H43" s="91"/>
@@ -4535,16 +4602,16 @@
         <v>17</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E44" s="29">
         <v>7</v>
       </c>
       <c r="F44" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="87"/>
       <c r="H44" s="91"/>
@@ -4562,7 +4629,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="106" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D45" s="106" t="s">
         <v>70</v>
@@ -4574,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H45" s="91">
         <v>46261</v>
@@ -4593,16 +4660,16 @@
         <v>17</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D46" s="28" t="s">
         <v>26</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F46" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="91">
         <v>46261</v>
@@ -4622,10 +4689,10 @@
         <v>17</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E47" s="29">
         <v>13</v>
@@ -4649,10 +4716,10 @@
         <v>17</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E48" s="29">
         <v>2</v>
@@ -4749,7 +4816,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -4799,7 +4866,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4867,7 +4934,7 @@
       </c>
       <c r="C59" s="115"/>
       <c r="D59" s="114" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E59" s="116">
         <v>5</v>
@@ -4876,7 +4943,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="80" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H59" s="94">
         <v>46268</v>
@@ -4899,10 +4966,10 @@
         <v>23</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F60" s="21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G60" s="86">
         <v>46268</v>
@@ -4939,7 +5006,7 @@
         <v>14</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D62" s="28" t="s">
         <v>59</v>
@@ -4966,7 +5033,7 @@
         <v>14</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D63" s="28" t="s">
         <v>22</v>
@@ -5010,10 +5077,10 @@
         <v>16</v>
       </c>
       <c r="C65" s="106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D65" s="106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E65" s="107">
         <v>10</v>
@@ -5022,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="83" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H65" s="91">
         <v>46261</v>
@@ -5041,13 +5108,13 @@
         <v>16</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D66" s="28" t="s">
         <v>24</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F66" s="30">
         <v>0</v>
@@ -5079,7 +5146,7 @@
         <v>17</v>
       </c>
       <c r="F67" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" s="83"/>
       <c r="H67" s="91"/>
@@ -5097,7 +5164,7 @@
         <v>16</v>
       </c>
       <c r="C68" s="106" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D68" s="106" t="s">
         <v>58</v>
@@ -5109,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H68" s="91">
         <v>46261</v>
@@ -5128,16 +5195,16 @@
         <v>16</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F69" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="91">
         <v>46261</v>
@@ -5157,7 +5224,7 @@
         <v>17</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D70" s="28" t="s">
         <v>19</v>
@@ -5166,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="F70" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" s="87"/>
       <c r="H70" s="91"/>
@@ -5184,7 +5251,7 @@
         <v>17</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D71" s="28" t="s">
         <v>59</v>
@@ -5193,7 +5260,7 @@
         <v>23</v>
       </c>
       <c r="F71" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" s="83"/>
       <c r="H71" s="91"/>
@@ -5220,7 +5287,7 @@
         <v>4</v>
       </c>
       <c r="F72" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="87"/>
       <c r="H72" s="91"/>
@@ -5238,7 +5305,7 @@
         <v>17</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D73" s="28" t="s">
         <v>53</v>
@@ -5247,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" s="87"/>
       <c r="H73" s="91"/>
@@ -5265,7 +5332,7 @@
         <v>17</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>52</v>
@@ -5382,7 +5449,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -5500,13 +5567,13 @@
       </c>
       <c r="C86" s="13"/>
       <c r="D86" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E86" s="14">
         <v>4</v>
       </c>
       <c r="F86" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
@@ -5558,7 +5625,7 @@
         <v>14</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>22</v>
@@ -5585,7 +5652,7 @@
         <v>14</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D90" s="28" t="s">
         <v>34</v>
@@ -5629,7 +5696,7 @@
         <v>16</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D92" s="28" t="s">
         <v>69</v>
@@ -5652,23 +5719,27 @@
     </row>
     <row r="93" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="79"/>
-      <c r="B93" s="28" t="s">
+      <c r="B93" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C93" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D93" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="E93" s="29">
+      <c r="C93" s="106" t="s">
+        <v>98</v>
+      </c>
+      <c r="D93" s="106" t="s">
+        <v>359</v>
+      </c>
+      <c r="E93" s="107">
         <v>1</v>
       </c>
-      <c r="F93" s="30">
+      <c r="F93" s="108">
         <v>0</v>
       </c>
-      <c r="G93" s="91"/>
-      <c r="H93" s="91"/>
+      <c r="G93" s="91" t="s">
+        <v>414</v>
+      </c>
+      <c r="H93" s="91">
+        <v>46275</v>
+      </c>
       <c r="I93" s="91"/>
       <c r="J93" s="76"/>
       <c r="K93" s="1"/>
@@ -5683,18 +5754,20 @@
         <v>16</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>144</v>
+        <v>453</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E94" s="29">
-        <v>10</v>
+        <v>359</v>
+      </c>
+      <c r="E94" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F94" s="30">
-        <v>2</v>
-      </c>
-      <c r="G94" s="91"/>
+        <v>1</v>
+      </c>
+      <c r="G94" s="91">
+        <v>46275</v>
+      </c>
       <c r="H94" s="91"/>
       <c r="I94" s="90"/>
       <c r="J94" s="76"/>
@@ -5706,11 +5779,21 @@
     </row>
     <row r="95" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="79"/>
-      <c r="B95" s="28"/>
-      <c r="C95" s="28"/>
-      <c r="D95" s="28"/>
-      <c r="E95" s="29"/>
-      <c r="F95" s="30"/>
+      <c r="B95" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" s="29">
+        <v>10</v>
+      </c>
+      <c r="F95" s="30">
+        <v>3</v>
+      </c>
       <c r="G95" s="91"/>
       <c r="H95" s="91"/>
       <c r="I95" s="90"/>
@@ -5744,10 +5827,10 @@
         <v>17</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>75</v>
+        <v>446</v>
       </c>
       <c r="E97" s="29">
         <v>4</v>
@@ -5771,10 +5854,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E98" s="29">
         <v>7</v>
@@ -5798,7 +5881,7 @@
         <v>17</v>
       </c>
       <c r="C99" s="106" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D99" s="106" t="s">
         <v>31</v>
@@ -5810,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H99" s="91">
         <v>46247</v>
@@ -5829,13 +5912,13 @@
         <v>17</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E100" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F100" s="30">
         <v>0</v>
@@ -5858,10 +5941,10 @@
         <v>17</v>
       </c>
       <c r="C101" s="106" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D101" s="106" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E101" s="107">
         <v>1</v>
@@ -5870,7 +5953,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H101" s="91">
         <v>46254</v>
@@ -5889,16 +5972,16 @@
         <v>17</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D102" s="28" t="s">
         <v>53</v>
       </c>
       <c r="E102" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F102" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G102" s="87">
         <v>46254</v>
@@ -5918,16 +6001,16 @@
         <v>17</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D103" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E103" s="29">
         <v>48</v>
       </c>
       <c r="F103" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="87"/>
       <c r="H103" s="91"/>
@@ -6001,7 +6084,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6051,7 +6134,7 @@
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>49</v>
@@ -6177,10 +6260,10 @@
         <v>14</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D116" s="28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E116" s="29">
         <v>1</v>
@@ -6204,10 +6287,10 @@
         <v>14</v>
       </c>
       <c r="C117" s="28" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D117" s="28" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E117" s="29">
         <v>1</v>
@@ -6248,10 +6331,10 @@
         <v>16</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E119" s="29">
         <v>1</v>
@@ -6275,10 +6358,10 @@
         <v>16</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E120" s="29">
         <v>1</v>
@@ -6302,10 +6385,10 @@
         <v>16</v>
       </c>
       <c r="C121" s="106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D121" s="106" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E121" s="107">
         <v>1</v>
@@ -6314,7 +6397,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="86" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H121" s="94">
         <v>46261</v>
@@ -6333,13 +6416,13 @@
         <v>16</v>
       </c>
       <c r="C122" s="28" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D122" s="28" t="s">
         <v>31</v>
       </c>
       <c r="E122" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F122" s="30">
         <v>0</v>
@@ -6379,7 +6462,7 @@
         <v>17</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D124" s="28" t="s">
         <v>70</v>
@@ -6418,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H125" s="91">
         <v>46261</v>
@@ -6437,16 +6520,16 @@
         <v>17</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D126" s="28" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E126" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F126" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="87">
         <v>46261</v>
@@ -6462,23 +6545,27 @@
     </row>
     <row r="127" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="79"/>
-      <c r="B127" s="28" t="s">
+      <c r="B127" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="D127" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E127" s="29">
+      <c r="C127" s="106" t="s">
+        <v>269</v>
+      </c>
+      <c r="D127" s="106" t="s">
+        <v>97</v>
+      </c>
+      <c r="E127" s="107">
         <v>20</v>
       </c>
-      <c r="F127" s="30">
+      <c r="F127" s="108">
         <v>1</v>
       </c>
-      <c r="G127" s="87"/>
-      <c r="H127" s="91"/>
+      <c r="G127" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H127" s="91">
+        <v>46275</v>
+      </c>
       <c r="I127" s="90"/>
       <c r="J127" s="76"/>
       <c r="K127" s="1"/>
@@ -6493,18 +6580,20 @@
         <v>17</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>112</v>
+        <v>449</v>
       </c>
       <c r="D128" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="E128" s="29">
-        <v>1</v>
+        <v>352</v>
+      </c>
+      <c r="E128" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F128" s="30">
         <v>0</v>
       </c>
-      <c r="G128" s="87"/>
+      <c r="G128" s="87">
+        <v>46275</v>
+      </c>
       <c r="H128" s="91"/>
       <c r="I128" s="90"/>
       <c r="J128" s="76"/>
@@ -6520,10 +6609,10 @@
         <v>17</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>367</v>
+        <v>111</v>
       </c>
       <c r="D129" s="28" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="E129" s="29">
         <v>1</v>
@@ -6543,13 +6632,27 @@
     </row>
     <row r="130" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="79"/>
-      <c r="B130" s="28"/>
-      <c r="C130" s="28"/>
-      <c r="D130" s="28"/>
-      <c r="E130" s="29"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="87"/>
-      <c r="H130" s="91"/>
+      <c r="B130" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" s="106" t="s">
+        <v>364</v>
+      </c>
+      <c r="D130" s="106" t="s">
+        <v>267</v>
+      </c>
+      <c r="E130" s="107">
+        <v>1</v>
+      </c>
+      <c r="F130" s="108">
+        <v>0</v>
+      </c>
+      <c r="G130" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H130" s="91">
+        <v>46268</v>
+      </c>
       <c r="I130" s="90"/>
       <c r="J130" s="76"/>
       <c r="K130" s="1"/>
@@ -6560,12 +6663,24 @@
     </row>
     <row r="131" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="79"/>
-      <c r="B131" s="106"/>
-      <c r="C131" s="106"/>
-      <c r="D131" s="106"/>
-      <c r="E131" s="107"/>
-      <c r="F131" s="108"/>
-      <c r="G131" s="87"/>
+      <c r="B131" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="D131" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="E131" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F131" s="30">
+        <v>1</v>
+      </c>
+      <c r="G131" s="87">
+        <v>46268</v>
+      </c>
       <c r="H131" s="91"/>
       <c r="I131" s="90"/>
       <c r="J131" s="76"/>
@@ -6620,7 +6735,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -6744,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="F140" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G140" s="80"/>
       <c r="H140" s="94"/>
@@ -6796,10 +6911,10 @@
         <v>14</v>
       </c>
       <c r="C143" s="28" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D143" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E143" s="29">
         <v>2</v>
@@ -6823,7 +6938,7 @@
         <v>14</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D144" s="28" t="s">
         <v>59</v>
@@ -6863,23 +6978,27 @@
     </row>
     <row r="146" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="79"/>
-      <c r="B146" s="28" t="s">
+      <c r="B146" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C146" s="28" t="s">
-        <v>369</v>
-      </c>
-      <c r="D146" s="28" t="s">
+      <c r="C146" s="106" t="s">
+        <v>366</v>
+      </c>
+      <c r="D146" s="106" t="s">
+        <v>411</v>
+      </c>
+      <c r="E146" s="107">
+        <v>1</v>
+      </c>
+      <c r="F146" s="108">
+        <v>0</v>
+      </c>
+      <c r="G146" s="87" t="s">
         <v>414</v>
       </c>
-      <c r="E146" s="29">
-        <v>1</v>
-      </c>
-      <c r="F146" s="30">
-        <v>0</v>
-      </c>
-      <c r="G146" s="87"/>
-      <c r="H146" s="91"/>
+      <c r="H146" s="91">
+        <v>46268</v>
+      </c>
       <c r="I146" s="90"/>
       <c r="J146" s="76"/>
       <c r="K146" s="1"/>
@@ -6894,18 +7013,20 @@
         <v>16</v>
       </c>
       <c r="C147" s="28" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D147" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="E147" s="29">
-        <v>6</v>
+        <v>93</v>
+      </c>
+      <c r="E147" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F147" s="30">
-        <v>2</v>
-      </c>
-      <c r="G147" s="87"/>
+        <v>1</v>
+      </c>
+      <c r="G147" s="87">
+        <v>46268</v>
+      </c>
       <c r="H147" s="91"/>
       <c r="I147" s="90"/>
       <c r="J147" s="96"/>
@@ -6917,23 +7038,27 @@
     </row>
     <row r="148" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="79"/>
-      <c r="B148" s="28" t="s">
+      <c r="B148" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C148" s="28" t="s">
-        <v>370</v>
-      </c>
-      <c r="D148" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E148" s="29">
-        <v>2</v>
-      </c>
-      <c r="F148" s="30">
+      <c r="C148" s="106" t="s">
+        <v>104</v>
+      </c>
+      <c r="D148" s="106" t="s">
+        <v>352</v>
+      </c>
+      <c r="E148" s="107">
+        <v>6</v>
+      </c>
+      <c r="F148" s="108">
         <v>3</v>
       </c>
-      <c r="G148" s="87"/>
-      <c r="H148" s="91"/>
+      <c r="G148" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H148" s="91">
+        <v>46275</v>
+      </c>
       <c r="I148" s="90"/>
       <c r="J148" s="96"/>
       <c r="K148" s="1"/>
@@ -6944,12 +7069,24 @@
     </row>
     <row r="149" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="79"/>
-      <c r="B149" s="28"/>
-      <c r="C149" s="28"/>
-      <c r="D149" s="28"/>
-      <c r="E149" s="29"/>
-      <c r="F149" s="30"/>
-      <c r="G149" s="87"/>
+      <c r="B149" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="D149" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E149" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F149" s="30">
+        <v>0</v>
+      </c>
+      <c r="G149" s="87">
+        <v>46275</v>
+      </c>
       <c r="H149" s="91"/>
       <c r="I149" s="90"/>
       <c r="J149" s="76"/>
@@ -6961,11 +7098,21 @@
     </row>
     <row r="150" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="79"/>
-      <c r="B150" s="28"/>
-      <c r="C150" s="28"/>
-      <c r="D150" s="28"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="30"/>
+      <c r="B150" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="D150" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E150" s="29">
+        <v>2</v>
+      </c>
+      <c r="F150" s="30">
+        <v>4</v>
+      </c>
       <c r="G150" s="87"/>
       <c r="H150" s="91"/>
       <c r="I150" s="90"/>
@@ -6982,7 +7129,7 @@
         <v>17</v>
       </c>
       <c r="C151" s="28" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D151" s="28" t="s">
         <v>71</v>
@@ -6991,7 +7138,7 @@
         <v>1</v>
       </c>
       <c r="F151" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G151" s="83"/>
       <c r="H151" s="91"/>
@@ -7009,7 +7156,7 @@
         <v>17</v>
       </c>
       <c r="C152" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D152" s="28" t="s">
         <v>59</v>
@@ -7018,7 +7165,7 @@
         <v>33</v>
       </c>
       <c r="F152" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G152" s="87"/>
       <c r="H152" s="91"/>
@@ -7036,7 +7183,7 @@
         <v>17</v>
       </c>
       <c r="C153" s="28" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D153" s="28" t="s">
         <v>20</v>
@@ -7045,7 +7192,7 @@
         <v>13</v>
       </c>
       <c r="F153" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G153" s="87"/>
       <c r="H153" s="91"/>
@@ -7063,16 +7210,16 @@
         <v>17</v>
       </c>
       <c r="C154" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D154" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E154" s="29">
         <v>25</v>
       </c>
       <c r="F154" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G154" s="87"/>
       <c r="H154" s="91"/>
@@ -7090,10 +7237,10 @@
         <v>17</v>
       </c>
       <c r="C155" s="106" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D155" s="106" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E155" s="107">
         <v>10</v>
@@ -7102,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="G155" s="87" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H155" s="91">
         <v>46261</v>
@@ -7117,25 +7264,27 @@
     </row>
     <row r="156" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="79"/>
-      <c r="B156" s="28" t="s">
+      <c r="B156" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C156" s="28" t="s">
-        <v>426</v>
-      </c>
-      <c r="D156" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="E156" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="F156" s="30">
+      <c r="C156" s="106" t="s">
+        <v>423</v>
+      </c>
+      <c r="D156" s="106" t="s">
+        <v>424</v>
+      </c>
+      <c r="E156" s="107" t="s">
+        <v>413</v>
+      </c>
+      <c r="F156" s="108">
         <v>0</v>
       </c>
       <c r="G156" s="87">
         <v>46261</v>
       </c>
-      <c r="H156" s="91"/>
+      <c r="H156" s="91">
+        <v>46268</v>
+      </c>
       <c r="I156" s="90"/>
       <c r="J156" s="76"/>
       <c r="K156" s="1"/>
@@ -7146,12 +7295,24 @@
     </row>
     <row r="157" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="79"/>
-      <c r="B157" s="28"/>
-      <c r="C157" s="28"/>
-      <c r="D157" s="28"/>
-      <c r="E157" s="29"/>
-      <c r="F157" s="30"/>
-      <c r="G157" s="87"/>
+      <c r="B157" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="D157" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="E157" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F157" s="30">
+        <v>0</v>
+      </c>
+      <c r="G157" s="87">
+        <v>46268</v>
+      </c>
       <c r="H157" s="91"/>
       <c r="I157" s="90"/>
       <c r="J157" s="76"/>
@@ -7223,7 +7384,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -7399,10 +7560,10 @@
         <v>14</v>
       </c>
       <c r="C170" s="28" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D170" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E170" s="29">
         <v>3</v>
@@ -7426,10 +7587,10 @@
         <v>14</v>
       </c>
       <c r="C171" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D171" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E171" s="29">
         <v>4</v>
@@ -7470,10 +7631,10 @@
         <v>16</v>
       </c>
       <c r="C173" s="28" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D173" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E173" s="29">
         <v>6</v>
@@ -7497,7 +7658,7 @@
         <v>16</v>
       </c>
       <c r="C174" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D174" s="28" t="s">
         <v>19</v>
@@ -7506,7 +7667,7 @@
         <v>12</v>
       </c>
       <c r="F174" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G174" s="91"/>
       <c r="H174" s="91"/>
@@ -7524,7 +7685,7 @@
         <v>16</v>
       </c>
       <c r="C175" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D175" s="28" t="s">
         <v>22</v>
@@ -7585,16 +7746,16 @@
         <v>17</v>
       </c>
       <c r="C178" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D178" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E178" s="29">
         <v>23</v>
       </c>
       <c r="F178" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G178" s="91"/>
       <c r="H178" s="91"/>
@@ -7612,16 +7773,16 @@
         <v>17</v>
       </c>
       <c r="C179" s="28" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D179" s="28" t="s">
-        <v>305</v>
+        <v>447</v>
       </c>
       <c r="E179" s="29">
         <v>24</v>
       </c>
       <c r="F179" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G179" s="83"/>
       <c r="H179" s="91"/>
@@ -7639,16 +7800,16 @@
         <v>17</v>
       </c>
       <c r="C180" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D180" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E180" s="29">
         <v>7</v>
       </c>
       <c r="F180" s="30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G180" s="91"/>
       <c r="H180" s="91"/>
@@ -7666,10 +7827,10 @@
         <v>17</v>
       </c>
       <c r="C181" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D181" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E181" s="29">
         <v>3</v>
@@ -7693,10 +7854,10 @@
         <v>17</v>
       </c>
       <c r="C182" s="28" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D182" s="28" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E182" s="29">
         <v>1</v>
@@ -7810,7 +7971,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -7860,10 +8021,10 @@
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="1"/>
@@ -7928,13 +8089,13 @@
       </c>
       <c r="C194" s="13"/>
       <c r="D194" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E194" s="14">
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -7986,10 +8147,10 @@
         <v>14</v>
       </c>
       <c r="C197" s="28" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D197" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E197" s="29">
         <v>3</v>
@@ -8013,7 +8174,7 @@
         <v>14</v>
       </c>
       <c r="C198" s="28" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D198" s="28" t="s">
         <v>31</v>
@@ -8057,10 +8218,10 @@
         <v>16</v>
       </c>
       <c r="C200" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D200" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E200" s="29">
         <v>10</v>
@@ -8084,7 +8245,7 @@
         <v>16</v>
       </c>
       <c r="C201" s="28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D201" s="28" t="s">
         <v>34</v>
@@ -8093,7 +8254,7 @@
         <v>4</v>
       </c>
       <c r="F201" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G201" s="83"/>
       <c r="H201" s="90"/>
@@ -8111,7 +8272,7 @@
         <v>16</v>
       </c>
       <c r="C202" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D202" s="28" t="s">
         <v>31</v>
@@ -8172,10 +8333,10 @@
         <v>17</v>
       </c>
       <c r="C205" s="106" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D205" s="106" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E205" s="107">
         <v>3</v>
@@ -8184,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="83" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H205" s="91">
         <v>46254</v>
@@ -8203,16 +8364,16 @@
         <v>17</v>
       </c>
       <c r="C206" s="28" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D206" s="28" t="s">
         <v>62</v>
       </c>
       <c r="E206" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F206" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" s="87">
         <v>46254</v>
@@ -8232,7 +8393,7 @@
         <v>17</v>
       </c>
       <c r="C207" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D207" s="28" t="s">
         <v>74</v>
@@ -8241,7 +8402,7 @@
         <v>10</v>
       </c>
       <c r="F207" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G207" s="83"/>
       <c r="H207" s="90"/>
@@ -8259,7 +8420,7 @@
         <v>17</v>
       </c>
       <c r="C208" s="28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D208" s="28" t="s">
         <v>63</v>
@@ -8268,7 +8429,7 @@
         <v>5</v>
       </c>
       <c r="F208" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G208" s="83"/>
       <c r="H208" s="91"/>
@@ -8286,7 +8447,7 @@
         <v>17</v>
       </c>
       <c r="C209" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D209" s="28" t="s">
         <v>31</v>
@@ -8295,7 +8456,7 @@
         <v>49</v>
       </c>
       <c r="F209" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G209" s="87"/>
       <c r="H209" s="91"/>
@@ -8313,7 +8474,7 @@
         <v>17</v>
       </c>
       <c r="C210" s="28" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D210" s="28" t="s">
         <v>58</v>
@@ -8413,7 +8574,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -8463,7 +8624,7 @@
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>50</v>
@@ -8537,7 +8698,7 @@
         <v>8</v>
       </c>
       <c r="F221" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G221" s="80"/>
       <c r="H221" s="94"/>
@@ -8589,10 +8750,10 @@
         <v>14</v>
       </c>
       <c r="C224" s="28" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D224" s="28" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E224" s="29">
         <v>1</v>
@@ -8616,10 +8777,10 @@
         <v>14</v>
       </c>
       <c r="C225" s="28" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D225" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E225" s="29">
         <v>1</v>
@@ -8660,10 +8821,10 @@
         <v>16</v>
       </c>
       <c r="C227" s="28" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D227" s="28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E227" s="29">
         <v>1</v>
@@ -8683,23 +8844,27 @@
     </row>
     <row r="228" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="79"/>
-      <c r="B228" s="28" t="s">
+      <c r="B228" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C228" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="D228" s="28" t="s">
+      <c r="C228" s="106" t="s">
+        <v>129</v>
+      </c>
+      <c r="D228" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="E228" s="29">
+      <c r="E228" s="107">
         <v>1</v>
       </c>
-      <c r="F228" s="30">
+      <c r="F228" s="108">
         <v>0</v>
       </c>
-      <c r="G228" s="87"/>
-      <c r="H228" s="91"/>
+      <c r="G228" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H228" s="91">
+        <v>46268</v>
+      </c>
       <c r="I228" s="89"/>
       <c r="J228" s="1"/>
       <c r="K228" s="1"/>
@@ -8714,18 +8879,20 @@
         <v>16</v>
       </c>
       <c r="C229" s="28" t="s">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="D229" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E229" s="29">
-        <v>6</v>
+        <v>128</v>
+      </c>
+      <c r="E229" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F229" s="30">
         <v>0</v>
       </c>
-      <c r="G229" s="87"/>
+      <c r="G229" s="87">
+        <v>46268</v>
+      </c>
       <c r="H229" s="91"/>
       <c r="I229" s="89"/>
       <c r="J229" s="76"/>
@@ -8737,13 +8904,27 @@
     </row>
     <row r="230" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="79"/>
-      <c r="B230" s="28"/>
-      <c r="C230" s="28"/>
-      <c r="D230" s="28"/>
-      <c r="E230" s="29"/>
-      <c r="F230" s="30"/>
-      <c r="G230" s="87"/>
-      <c r="H230" s="91"/>
+      <c r="B230" s="106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C230" s="106" t="s">
+        <v>283</v>
+      </c>
+      <c r="D230" s="106" t="s">
+        <v>433</v>
+      </c>
+      <c r="E230" s="107">
+        <v>6</v>
+      </c>
+      <c r="F230" s="108">
+        <v>0</v>
+      </c>
+      <c r="G230" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H230" s="91">
+        <v>46282</v>
+      </c>
       <c r="I230" s="89"/>
       <c r="J230" s="76"/>
       <c r="K230" s="1"/>
@@ -8754,12 +8935,24 @@
     </row>
     <row r="231" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="79"/>
-      <c r="B231" s="28"/>
-      <c r="C231" s="28"/>
-      <c r="D231" s="28"/>
-      <c r="E231" s="29"/>
-      <c r="F231" s="30"/>
-      <c r="G231" s="87"/>
+      <c r="B231" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C231" s="28" t="s">
+        <v>450</v>
+      </c>
+      <c r="D231" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="E231" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F231" s="30">
+        <v>0</v>
+      </c>
+      <c r="G231" s="87">
+        <v>46282</v>
+      </c>
       <c r="H231" s="91"/>
       <c r="I231" s="89"/>
       <c r="J231" s="76"/>
@@ -8775,7 +8968,7 @@
         <v>17</v>
       </c>
       <c r="C232" s="28" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D232" s="28" t="s">
         <v>23</v>
@@ -8802,16 +8995,16 @@
         <v>17</v>
       </c>
       <c r="C233" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D233" s="28" t="s">
-        <v>162</v>
+        <v>439</v>
       </c>
       <c r="E233" s="29">
         <v>19</v>
       </c>
       <c r="F233" s="30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G233" s="87"/>
       <c r="H233" s="91"/>
@@ -8825,23 +9018,27 @@
     </row>
     <row r="234" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="79"/>
-      <c r="B234" s="28" t="s">
+      <c r="B234" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C234" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D234" s="28" t="s">
+      <c r="C234" s="106" t="s">
+        <v>132</v>
+      </c>
+      <c r="D234" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="E234" s="29">
+      <c r="E234" s="107">
         <v>34</v>
       </c>
-      <c r="F234" s="30">
+      <c r="F234" s="108">
         <v>0</v>
       </c>
-      <c r="G234" s="87"/>
-      <c r="H234" s="91"/>
+      <c r="G234" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H234" s="91">
+        <v>46268</v>
+      </c>
       <c r="I234" s="89"/>
       <c r="J234" s="1"/>
       <c r="K234" s="1"/>
@@ -8856,18 +9053,20 @@
         <v>17</v>
       </c>
       <c r="C235" s="28" t="s">
-        <v>276</v>
+        <v>441</v>
       </c>
       <c r="D235" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="E235" s="29">
-        <v>5</v>
+        <v>442</v>
+      </c>
+      <c r="E235" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F235" s="30">
         <v>0</v>
       </c>
-      <c r="G235" s="87"/>
+      <c r="G235" s="87">
+        <v>46268</v>
+      </c>
       <c r="H235" s="91"/>
       <c r="I235" s="89"/>
       <c r="J235" s="76"/>
@@ -8883,16 +9082,16 @@
         <v>17</v>
       </c>
       <c r="C236" s="28" t="s">
-        <v>378</v>
+        <v>275</v>
       </c>
       <c r="D236" s="28" t="s">
-        <v>124</v>
+        <v>276</v>
       </c>
       <c r="E236" s="29">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F236" s="30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G236" s="83"/>
       <c r="H236" s="91"/>
@@ -8906,11 +9105,21 @@
     </row>
     <row r="237" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="79"/>
-      <c r="B237" s="106"/>
-      <c r="C237" s="106"/>
-      <c r="D237" s="106"/>
-      <c r="E237" s="107"/>
-      <c r="F237" s="108"/>
+      <c r="B237" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237" s="28" t="s">
+        <v>375</v>
+      </c>
+      <c r="D237" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E237" s="29">
+        <v>13</v>
+      </c>
+      <c r="F237" s="30">
+        <v>2</v>
+      </c>
       <c r="G237" s="87"/>
       <c r="H237" s="91"/>
       <c r="I237" s="89"/>
@@ -9000,7 +9209,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -9050,7 +9259,7 @@
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>51</v>
@@ -9124,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G248" s="80"/>
       <c r="H248" s="94"/>
@@ -9176,7 +9385,7 @@
         <v>14</v>
       </c>
       <c r="C251" s="28" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D251" s="28" t="s">
         <v>22</v>
@@ -9247,16 +9456,16 @@
         <v>16</v>
       </c>
       <c r="C254" s="28" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D254" s="28" t="s">
-        <v>282</v>
+        <v>100</v>
       </c>
       <c r="E254" s="29">
         <v>16</v>
       </c>
       <c r="F254" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G254" s="91"/>
       <c r="H254" s="91"/>
@@ -9274,10 +9483,10 @@
         <v>16</v>
       </c>
       <c r="C255" s="28" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D255" s="28" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="E255" s="29">
         <v>2</v>
@@ -9301,10 +9510,10 @@
         <v>16</v>
       </c>
       <c r="C256" s="28" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D256" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E256" s="29">
         <v>1</v>
@@ -9362,16 +9571,16 @@
         <v>17</v>
       </c>
       <c r="C259" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D259" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E259" s="29">
         <v>14</v>
       </c>
       <c r="F259" s="30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G259" s="87"/>
       <c r="H259" s="91"/>
@@ -9389,7 +9598,7 @@
         <v>17</v>
       </c>
       <c r="C260" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D260" s="28" t="s">
         <v>74</v>
@@ -9398,7 +9607,7 @@
         <v>22</v>
       </c>
       <c r="F260" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
@@ -9416,10 +9625,10 @@
         <v>17</v>
       </c>
       <c r="C261" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D261" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E261" s="29">
         <v>33</v>
@@ -9443,7 +9652,7 @@
         <v>17</v>
       </c>
       <c r="C262" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D262" s="28" t="s">
         <v>62</v>
@@ -9470,7 +9679,7 @@
         <v>17</v>
       </c>
       <c r="C263" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D263" s="28" t="s">
         <v>59</v>
@@ -9479,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="F263" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263" s="87"/>
       <c r="H263" s="91"/>
@@ -9637,10 +9846,10 @@
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" s="1"/>
@@ -9705,13 +9914,13 @@
       </c>
       <c r="C275" s="13"/>
       <c r="D275" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E275" s="14">
         <v>1</v>
       </c>
       <c r="F275" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G275" s="80"/>
       <c r="H275" s="94"/>
@@ -9763,10 +9972,10 @@
         <v>14</v>
       </c>
       <c r="C278" s="28" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D278" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E278" s="29">
         <v>1</v>
@@ -9790,10 +9999,10 @@
         <v>14</v>
       </c>
       <c r="C279" s="28" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D279" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E279" s="29">
         <v>1</v>
@@ -9834,10 +10043,10 @@
         <v>16</v>
       </c>
       <c r="C281" s="28" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D281" s="28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E281" s="29">
         <v>1</v>
@@ -9861,10 +10070,10 @@
         <v>16</v>
       </c>
       <c r="C282" s="28" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D282" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E282" s="29">
         <v>1</v>
@@ -9888,7 +10097,7 @@
         <v>16</v>
       </c>
       <c r="C283" s="28" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D283" s="28" t="s">
         <v>52</v>
@@ -9949,7 +10158,7 @@
         <v>17</v>
       </c>
       <c r="C286" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D286" s="28" t="s">
         <v>31</v>
@@ -9976,10 +10185,10 @@
         <v>17</v>
       </c>
       <c r="C287" s="28" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D287" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E287" s="29">
         <v>1</v>
@@ -10003,7 +10212,7 @@
         <v>17</v>
       </c>
       <c r="C288" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D288" s="28" t="s">
         <v>72</v>
@@ -10012,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="F288" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G288" s="87"/>
       <c r="H288" s="91"/>
@@ -10030,16 +10239,16 @@
         <v>17</v>
       </c>
       <c r="C289" s="28" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D289" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E289" s="29">
         <v>1</v>
       </c>
       <c r="F289" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" s="87"/>
       <c r="H289" s="91"/>
@@ -10057,10 +10266,10 @@
         <v>17</v>
       </c>
       <c r="C290" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D290" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E290" s="29">
         <v>1</v>
@@ -10174,7 +10383,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -10224,10 +10433,10 @@
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E299" s="2"/>
       <c r="F299" s="1"/>
@@ -10301,7 +10510,7 @@
         <v>6</v>
       </c>
       <c r="G302" s="80" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H302" s="91">
         <v>46261</v>
@@ -10324,10 +10533,10 @@
         <v>63</v>
       </c>
       <c r="E303" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F303" s="21">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G303" s="87">
         <v>46261</v>
@@ -10364,7 +10573,7 @@
         <v>14</v>
       </c>
       <c r="C305" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D305" s="28" t="s">
         <v>71</v>
@@ -10391,10 +10600,10 @@
         <v>14</v>
       </c>
       <c r="C306" s="28" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D306" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E306" s="29">
         <v>1</v>
@@ -10435,10 +10644,10 @@
         <v>16</v>
       </c>
       <c r="C308" s="28" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D308" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E308" s="29">
         <v>1</v>
@@ -10458,23 +10667,27 @@
     </row>
     <row r="309" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="79"/>
-      <c r="B309" s="28" t="s">
+      <c r="B309" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C309" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="D309" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E309" s="29">
+      <c r="C309" s="106" t="s">
+        <v>379</v>
+      </c>
+      <c r="D309" s="106" t="s">
+        <v>131</v>
+      </c>
+      <c r="E309" s="107">
         <v>1</v>
       </c>
-      <c r="F309" s="30">
+      <c r="F309" s="108">
         <v>0</v>
       </c>
-      <c r="G309" s="87"/>
-      <c r="H309" s="91"/>
+      <c r="G309" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H309" s="91">
+        <v>46268</v>
+      </c>
       <c r="I309" s="90"/>
       <c r="J309" s="1"/>
       <c r="K309" s="1"/>
@@ -10489,18 +10702,20 @@
         <v>16</v>
       </c>
       <c r="C310" s="28" t="s">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="D310" s="77" t="s">
-        <v>268</v>
-      </c>
-      <c r="E310" s="29">
-        <v>1</v>
+        <v>352</v>
+      </c>
+      <c r="E310" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F310" s="30">
         <v>0</v>
       </c>
-      <c r="G310" s="87"/>
+      <c r="G310" s="87">
+        <v>46268</v>
+      </c>
       <c r="H310" s="91"/>
       <c r="I310" s="90"/>
       <c r="J310" s="1"/>
@@ -10512,11 +10727,21 @@
     </row>
     <row r="311" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="79"/>
-      <c r="B311" s="28"/>
-      <c r="C311" s="28"/>
-      <c r="D311" s="28"/>
-      <c r="E311" s="29"/>
-      <c r="F311" s="30"/>
+      <c r="B311" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C311" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="D311" s="77" t="s">
+        <v>267</v>
+      </c>
+      <c r="E311" s="29">
+        <v>1</v>
+      </c>
+      <c r="F311" s="30">
+        <v>1</v>
+      </c>
       <c r="G311" s="83"/>
       <c r="H311" s="91"/>
       <c r="I311" s="90"/>
@@ -10559,7 +10784,7 @@
         <v>78</v>
       </c>
       <c r="F313" s="30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -10573,23 +10798,27 @@
     </row>
     <row r="314" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="79"/>
-      <c r="B314" s="28" t="s">
+      <c r="B314" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C314" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="D314" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="E314" s="29">
+      <c r="C314" s="106" t="s">
+        <v>381</v>
+      </c>
+      <c r="D314" s="106" t="s">
+        <v>292</v>
+      </c>
+      <c r="E314" s="107">
         <v>1</v>
       </c>
-      <c r="F314" s="30">
+      <c r="F314" s="108">
         <v>0</v>
       </c>
-      <c r="G314" s="87"/>
-      <c r="H314" s="91"/>
+      <c r="G314" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H314" s="91">
+        <v>46268</v>
+      </c>
       <c r="I314" s="90"/>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
@@ -10604,18 +10833,20 @@
         <v>17</v>
       </c>
       <c r="C315" s="28" t="s">
-        <v>291</v>
+        <v>437</v>
       </c>
       <c r="D315" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E315" s="29">
-        <v>1</v>
+        <v>292</v>
+      </c>
+      <c r="E315" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F315" s="30">
-        <v>0</v>
-      </c>
-      <c r="G315" s="87"/>
+        <v>2</v>
+      </c>
+      <c r="G315" s="87">
+        <v>46268</v>
+      </c>
       <c r="H315" s="91"/>
       <c r="I315" s="90"/>
       <c r="J315" s="1"/>
@@ -10631,16 +10862,16 @@
         <v>17</v>
       </c>
       <c r="C316" s="28" t="s">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="D316" s="28" t="s">
-        <v>162</v>
+        <v>20</v>
       </c>
       <c r="E316" s="29">
         <v>1</v>
       </c>
       <c r="F316" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G316" s="87"/>
       <c r="H316" s="91"/>
@@ -10658,10 +10889,10 @@
         <v>17</v>
       </c>
       <c r="C317" s="28" t="s">
-        <v>385</v>
+        <v>320</v>
       </c>
       <c r="D317" s="28" t="s">
-        <v>280</v>
+        <v>161</v>
       </c>
       <c r="E317" s="29">
         <v>1</v>
@@ -10681,13 +10912,27 @@
     </row>
     <row r="318" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="79"/>
-      <c r="B318" s="106"/>
-      <c r="C318" s="106"/>
-      <c r="D318" s="106"/>
-      <c r="E318" s="107"/>
-      <c r="F318" s="108"/>
-      <c r="G318" s="83"/>
-      <c r="H318" s="91"/>
+      <c r="B318" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C318" s="106" t="s">
+        <v>382</v>
+      </c>
+      <c r="D318" s="106" t="s">
+        <v>279</v>
+      </c>
+      <c r="E318" s="107">
+        <v>1</v>
+      </c>
+      <c r="F318" s="108">
+        <v>0</v>
+      </c>
+      <c r="G318" s="83" t="s">
+        <v>414</v>
+      </c>
+      <c r="H318" s="91">
+        <v>46268</v>
+      </c>
       <c r="I318" s="90"/>
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
@@ -10698,12 +10943,24 @@
     </row>
     <row r="319" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="79"/>
-      <c r="B319" s="28"/>
-      <c r="C319" s="28"/>
-      <c r="D319" s="28"/>
-      <c r="E319" s="29"/>
-      <c r="F319" s="30"/>
-      <c r="G319" s="87"/>
+      <c r="B319" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C319" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="D319" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="E319" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F319" s="30">
+        <v>0</v>
+      </c>
+      <c r="G319" s="87">
+        <v>46268</v>
+      </c>
       <c r="H319" s="91"/>
       <c r="I319" s="90"/>
       <c r="J319" s="1"/>
@@ -10775,7 +11032,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -10825,10 +11082,10 @@
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E326" s="2"/>
       <c r="F326" s="1"/>
@@ -10899,7 +11156,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -10951,10 +11208,10 @@
         <v>14</v>
       </c>
       <c r="C332" s="106" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D332" s="106" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E332" s="107">
         <v>2</v>
@@ -10963,7 +11220,7 @@
         <v>0</v>
       </c>
       <c r="G332" s="83" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H332" s="91">
         <v>46261</v>
@@ -10982,13 +11239,13 @@
         <v>14</v>
       </c>
       <c r="C333" s="28" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D333" s="28" t="s">
         <v>23</v>
       </c>
       <c r="E333" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F333" s="30">
         <v>0</v>
@@ -11011,7 +11268,7 @@
         <v>14</v>
       </c>
       <c r="C334" s="28" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D334" s="28" t="s">
         <v>18</v>
@@ -11038,16 +11295,16 @@
         <v>16</v>
       </c>
       <c r="C335" s="28" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D335" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E335" s="29">
         <v>10</v>
       </c>
       <c r="F335" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G335" s="87"/>
       <c r="H335" s="91"/>
@@ -11065,10 +11322,10 @@
         <v>16</v>
       </c>
       <c r="C336" s="28" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D336" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E336" s="29">
         <v>1</v>
@@ -11088,23 +11345,27 @@
     </row>
     <row r="337" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="79"/>
-      <c r="B337" s="28" t="s">
+      <c r="B337" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C337" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="D337" s="28" t="s">
-        <v>390</v>
-      </c>
-      <c r="E337" s="29">
+      <c r="C337" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="D337" s="106" t="s">
+        <v>387</v>
+      </c>
+      <c r="E337" s="107">
         <v>1</v>
       </c>
-      <c r="F337" s="30">
+      <c r="F337" s="108">
         <v>0</v>
       </c>
-      <c r="G337" s="87"/>
-      <c r="H337" s="91"/>
+      <c r="G337" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H337" s="91">
+        <v>46268</v>
+      </c>
       <c r="I337" s="90"/>
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
@@ -11115,12 +11376,24 @@
     </row>
     <row r="338" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="79"/>
-      <c r="B338" s="28"/>
-      <c r="C338" s="28"/>
-      <c r="D338" s="28"/>
-      <c r="E338" s="29"/>
-      <c r="F338" s="30"/>
-      <c r="G338" s="87"/>
+      <c r="B338" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C338" s="28" t="s">
+        <v>448</v>
+      </c>
+      <c r="D338" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E338" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F338" s="30">
+        <v>0</v>
+      </c>
+      <c r="G338" s="87">
+        <v>46268</v>
+      </c>
       <c r="H338" s="91"/>
       <c r="I338" s="90"/>
       <c r="J338" s="1"/>
@@ -11150,7 +11423,7 @@
         <v>17</v>
       </c>
       <c r="C340" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D340" s="28" t="s">
         <v>58</v>
@@ -11159,7 +11432,7 @@
         <v>9</v>
       </c>
       <c r="F340" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G340" s="87"/>
       <c r="H340" s="90"/>
@@ -11174,10 +11447,10 @@
         <v>17</v>
       </c>
       <c r="C341" s="28" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D341" s="28" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E341" s="29">
         <v>5</v>
@@ -11198,16 +11471,16 @@
         <v>17</v>
       </c>
       <c r="C342" s="28" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D342" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E342" s="29">
         <v>12</v>
       </c>
       <c r="F342" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G342" s="87"/>
       <c r="H342" s="91"/>
@@ -11222,7 +11495,7 @@
         <v>17</v>
       </c>
       <c r="C343" s="28" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D343" s="28" t="s">
         <v>23</v>
@@ -11246,10 +11519,10 @@
         <v>17</v>
       </c>
       <c r="C344" s="28" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D344" s="28" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E344" s="29">
         <v>40</v>
@@ -11345,7 +11618,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -11371,10 +11644,10 @@
     <row r="353" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="1"/>
       <c r="C353" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E353" s="2"/>
       <c r="F353" s="1"/>
@@ -11421,13 +11694,13 @@
       </c>
       <c r="C356" s="13"/>
       <c r="D356" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E356" s="14">
         <v>3</v>
       </c>
       <c r="F356" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -11461,7 +11734,7 @@
         <v>14</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D359" s="28" t="s">
         <v>24</v>
@@ -11482,7 +11755,7 @@
         <v>14</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D360" s="28" t="s">
         <v>18</v>
@@ -11514,7 +11787,7 @@
         <v>16</v>
       </c>
       <c r="C362" s="28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D362" s="28" t="s">
         <v>19</v>
@@ -11523,7 +11796,7 @@
         <v>15</v>
       </c>
       <c r="F362" s="30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G362" s="1"/>
       <c r="H362" s="103"/>
@@ -11535,7 +11808,7 @@
         <v>16</v>
       </c>
       <c r="C363" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D363" s="28" t="s">
         <v>22</v>
@@ -11556,7 +11829,7 @@
         <v>16</v>
       </c>
       <c r="C364" s="106" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D364" s="106" t="s">
         <v>22</v>
@@ -11568,7 +11841,7 @@
         <v>0</v>
       </c>
       <c r="G364" s="103" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H364" s="103">
         <v>46268</v>
@@ -11581,16 +11854,16 @@
         <v>16</v>
       </c>
       <c r="C365" s="28" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D365" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E365" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F365" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G365" s="103">
         <v>46268</v>
@@ -11615,16 +11888,16 @@
         <v>17</v>
       </c>
       <c r="C367" s="28" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D367" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E367" s="29">
         <v>25</v>
       </c>
       <c r="F367" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="103"/>
@@ -11636,7 +11909,7 @@
         <v>17</v>
       </c>
       <c r="C368" s="106" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D368" s="106" t="s">
         <v>70</v>
@@ -11648,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="G368" s="103" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H368" s="103">
         <v>46268</v>
@@ -11661,13 +11934,13 @@
         <v>17</v>
       </c>
       <c r="C369" s="28" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D369" s="28" t="s">
         <v>34</v>
       </c>
       <c r="E369" s="29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F369" s="30">
         <v>0</v>
@@ -11680,71 +11953,75 @@
       <c r="J369" s="1"/>
     </row>
     <row r="370" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B370" s="28" t="s">
+      <c r="B370" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C370" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="D370" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="E370" s="29">
+      <c r="C370" s="106" t="s">
+        <v>277</v>
+      </c>
+      <c r="D370" s="106" t="s">
+        <v>352</v>
+      </c>
+      <c r="E370" s="107">
         <v>1</v>
       </c>
-      <c r="F370" s="30">
+      <c r="F370" s="108">
         <v>1</v>
       </c>
-      <c r="G370" s="103"/>
-      <c r="H370" s="103"/>
+      <c r="G370" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="H370" s="103">
+        <v>46268</v>
+      </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
     </row>
     <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B371" s="106" t="s">
+      <c r="B371" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C371" s="106" t="s">
-        <v>399</v>
-      </c>
-      <c r="D371" s="106" t="s">
-        <v>400</v>
-      </c>
-      <c r="E371" s="107">
-        <v>1</v>
-      </c>
-      <c r="F371" s="108">
+      <c r="C371" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="D371" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="E371" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F371" s="30">
         <v>0</v>
       </c>
-      <c r="G371" s="103" t="s">
-        <v>417</v>
-      </c>
-      <c r="H371" s="103">
-        <v>46254</v>
-      </c>
+      <c r="G371" s="103">
+        <v>46268</v>
+      </c>
+      <c r="H371" s="103"/>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
     </row>
     <row r="372" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B372" s="28" t="s">
+      <c r="B372" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C372" s="28" t="s">
-        <v>420</v>
-      </c>
-      <c r="D372" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E372" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="F372" s="30">
+      <c r="C372" s="106" t="s">
+        <v>396</v>
+      </c>
+      <c r="D372" s="106" t="s">
+        <v>397</v>
+      </c>
+      <c r="E372" s="107">
+        <v>1</v>
+      </c>
+      <c r="F372" s="108">
         <v>0</v>
       </c>
-      <c r="G372" s="103">
+      <c r="G372" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="H372" s="103">
         <v>46254</v>
       </c>
-      <c r="H372" s="103"/>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
     </row>
@@ -11753,28 +12030,40 @@
         <v>17</v>
       </c>
       <c r="C373" s="28" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="D373" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="E373" s="29">
-        <v>20</v>
+        <v>73</v>
+      </c>
+      <c r="E373" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F373" s="30">
         <v>0</v>
       </c>
-      <c r="G373" s="103"/>
+      <c r="G373" s="103">
+        <v>46254</v>
+      </c>
       <c r="H373" s="103"/>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
     </row>
     <row r="374" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B374" s="106"/>
-      <c r="C374" s="106"/>
-      <c r="D374" s="106"/>
-      <c r="E374" s="107"/>
-      <c r="F374" s="108"/>
+      <c r="B374" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C374" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="D374" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="E374" s="29">
+        <v>20</v>
+      </c>
+      <c r="F374" s="30">
+        <v>0</v>
+      </c>
       <c r="G374" s="103"/>
       <c r="H374" s="103"/>
       <c r="I374" s="1"/>
@@ -11812,7 +12101,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -11822,10 +12111,10 @@
     <row r="380" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="1"/>
       <c r="C380" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D380" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="D380" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="E380" s="2"/>
       <c r="F380" s="1"/>
@@ -12105,7 +12394,7 @@
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
       <c r="D4" s="43" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="41"/>
@@ -12165,13 +12454,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="25">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F7" s="26">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G7" s="27">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" s="111"/>
       <c r="I7" s="41"/>
@@ -12184,16 +12473,16 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="E8" s="25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" s="26">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8" s="27">
         <v>5</v>
@@ -12209,19 +12498,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>29</v>
       </c>
       <c r="E9" s="25">
-        <v>6</v>
-      </c>
-      <c r="F9" s="26">
-        <v>7</v>
-      </c>
-      <c r="G9" s="27">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F9" s="56">
+        <v>21</v>
+      </c>
+      <c r="G9" s="57">
+        <v>12</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -12234,18 +12523,18 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>135</v>
+        <v>21</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>265</v>
       </c>
       <c r="E10" s="25">
-        <v>5</v>
-      </c>
-      <c r="F10" s="56">
-        <v>10</v>
-      </c>
-      <c r="G10" s="57">
+        <v>9</v>
+      </c>
+      <c r="F10" s="26">
+        <v>14</v>
+      </c>
+      <c r="G10" s="27">
         <v>5</v>
       </c>
       <c r="H10" s="111"/>
@@ -12259,19 +12548,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="E11" s="25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" s="26">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G11" s="27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="41"/>
@@ -12281,22 +12570,22 @@
     <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47"/>
       <c r="B12" s="54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>344</v>
+        <v>50</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>157</v>
       </c>
       <c r="E12" s="25">
-        <v>3</v>
-      </c>
-      <c r="F12" s="56">
-        <v>7</v>
-      </c>
-      <c r="G12" s="57">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="F12" s="26">
+        <v>9</v>
+      </c>
+      <c r="G12" s="27">
+        <v>1</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -12311,17 +12600,17 @@
       <c r="C13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>126</v>
+      <c r="D13" s="55" t="s">
+        <v>125</v>
       </c>
       <c r="E13" s="25">
-        <v>2</v>
-      </c>
-      <c r="F13" s="26">
-        <v>12</v>
-      </c>
-      <c r="G13" s="27">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="F13" s="56">
+        <v>19</v>
+      </c>
+      <c r="G13" s="57">
+        <v>13</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="41"/>
@@ -12334,16 +12623,16 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>266</v>
+        <v>141</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>142</v>
       </c>
       <c r="E14" s="25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" s="26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G14" s="27">
         <v>4</v>
@@ -12359,19 +12648,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>343</v>
+        <v>51</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>402</v>
+        <v>134</v>
       </c>
       <c r="E15" s="25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F15" s="26">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G15" s="27">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="41"/>
@@ -12384,19 +12673,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>32</v>
+        <v>322</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>341</v>
       </c>
       <c r="E16" s="25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F16" s="26">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G16" s="27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -12409,19 +12698,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="55" t="s">
-        <v>143</v>
+        <v>340</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>399</v>
       </c>
       <c r="E17" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="26">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G17" s="27">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -12434,19 +12723,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E18" s="25">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F18" s="56">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G18" s="57">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -12459,10 +12748,10 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="E19" s="25">
         <v>-3</v>
@@ -12484,19 +12773,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D20" s="55" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E20" s="25">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="F20" s="26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20" s="27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="41"/>
@@ -12562,7 +12851,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -12599,10 +12888,10 @@
       <c r="F4" s="100"/>
       <c r="G4" s="100"/>
       <c r="I4" s="38" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12616,10 +12905,10 @@
       <c r="F5" s="64"/>
       <c r="G5" s="64"/>
       <c r="I5" s="38" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12633,10 +12922,10 @@
       <c r="F6" s="64"/>
       <c r="G6" s="64"/>
       <c r="I6" s="38" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12653,7 +12942,7 @@
         <v>38</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12678,7 +12967,7 @@
       <c r="F9" s="100"/>
       <c r="G9" s="100"/>
       <c r="I9" s="38" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12693,7 +12982,7 @@
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="67"/>
       <c r="B11" s="63" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C11" s="68"/>
       <c r="D11" s="64"/>
@@ -12787,7 +13076,7 @@
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="67"/>
       <c r="B20" s="63" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C20" s="68"/>
       <c r="D20" s="64"/>
@@ -12837,7 +13126,7 @@
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" s="65"/>
       <c r="C25" s="64"/>
@@ -12858,7 +13147,7 @@
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="67"/>
       <c r="B27" s="63" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C27" s="68"/>
       <c r="D27" s="64"/>
@@ -12868,7 +13157,7 @@
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B28" s="68"/>
       <c r="C28" s="64"/>
@@ -12897,7 +13186,7 @@
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="65"/>
       <c r="C31" s="64"/>
@@ -12957,7 +13246,7 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -13047,7 +13336,7 @@
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
       <c r="J4" s="98" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K4" s="38"/>
       <c r="L4" s="38"/>
@@ -13077,7 +13366,7 @@
       <c r="H5" s="38"/>
       <c r="I5" s="38"/>
       <c r="J5" s="98" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K5" s="38"/>
       <c r="L5" s="38"/>
@@ -13107,7 +13396,7 @@
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
       <c r="J6" s="98" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K6" s="38"/>
       <c r="L6" s="38"/>
@@ -13137,7 +13426,7 @@
       <c r="H7" s="38"/>
       <c r="I7" s="38"/>
       <c r="J7" s="98" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K7" s="38"/>
       <c r="L7" s="38"/>
@@ -13351,7 +13640,7 @@
     <row r="15" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A15" s="67"/>
       <c r="B15" s="63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C15" s="64"/>
       <c r="D15" s="64"/>
@@ -13433,7 +13722,7 @@
     <row r="18" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A18" s="67"/>
       <c r="B18" s="63" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="68"/>
       <c r="D18" s="64"/>
@@ -13516,7 +13805,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="65"/>
       <c r="C21" s="64"/>
@@ -13544,7 +13833,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B22" s="70"/>
       <c r="C22" s="100"/>
@@ -13572,7 +13861,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B23" s="65"/>
       <c r="C23" s="64"/>
@@ -13600,7 +13889,7 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24" s="65"/>
       <c r="C24" s="64"/>
@@ -13628,7 +13917,7 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" s="65"/>
       <c r="C25" s="64"/>
@@ -13656,7 +13945,7 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B26" s="65"/>
       <c r="C26" s="64"/>
@@ -13738,7 +14027,7 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" s="70"/>
       <c r="C29" s="100"/>
@@ -13766,7 +14055,7 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="67" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B30" s="70"/>
       <c r="C30" s="100"/>
@@ -13794,7 +14083,7 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" s="70"/>
       <c r="C31" s="100"/>
@@ -13822,7 +14111,7 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="67" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" s="70"/>
       <c r="C32" s="100"/>
@@ -13902,7 +14191,7 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="67" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="70"/>
       <c r="C35" s="100"/>
@@ -13930,7 +14219,7 @@
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B36" s="70"/>
       <c r="C36" s="100"/>
@@ -14010,7 +14299,7 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B39" s="65"/>
       <c r="C39" s="64"/>
@@ -14686,47 +14975,47 @@
   <sheetData>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J5" s="67" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N5" s="67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C6">
         <f>COUNTIF(Stats!D:D,'Player Count'!B6)</f>
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G6">
         <f>COUNTIF(Stats!D:D,'Player Count'!F6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K6">
         <f>COUNTIF(Stats!D:D,'Player Count'!J6)</f>
@@ -14734,7 +15023,7 @@
       </c>
       <c r="M6" s="109"/>
       <c r="N6" s="67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O6">
         <f>COUNTIF(Stats!D:D,'Player Count'!N6)</f>
@@ -14744,21 +15033,21 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C7">
         <f>COUNTIF(Stats!D:D,'Player Count'!B7)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G7">
         <f>COUNTIF(Stats!D:D,'Player Count'!F7)</f>
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K7">
         <f>COUNTIF(Stats!D:D,'Player Count'!J7)</f>
@@ -14766,7 +15055,7 @@
       </c>
       <c r="M7" s="109"/>
       <c r="N7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O7">
         <f>COUNTIF(Stats!D:D,'Player Count'!N7)</f>
@@ -14776,21 +15065,21 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C8">
         <f>COUNTIF(Stats!D:D,'Player Count'!B8)</f>
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G8">
         <f>COUNTIF(Stats!D:D,'Player Count'!F8)</f>
         <v>2</v>
       </c>
       <c r="J8" s="67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K8">
         <f>COUNTIF(Stats!D:D,'Player Count'!J8)</f>
@@ -14798,7 +15087,7 @@
       </c>
       <c r="M8" s="109"/>
       <c r="N8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O8">
         <f>COUNTIF(Stats!D:D,'Player Count'!N8)</f>
@@ -14808,21 +15097,21 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C9">
         <f>COUNTIF(Stats!D:D,'Player Count'!B9)</f>
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G9">
         <f>COUNTIF(Stats!D:D,'Player Count'!F9)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="67" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K9">
         <f>COUNTIF(Stats!D:D,'Player Count'!J9)</f>
@@ -14830,31 +15119,31 @@
       </c>
       <c r="M9" s="109"/>
       <c r="N9" s="67" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O9">
         <f>COUNTIF(Stats!D:D,'Player Count'!N9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="109"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10">
         <f>COUNTIF(Stats!D:D,'Player Count'!B10)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G10">
         <f>COUNTIF(Stats!D:D,'Player Count'!F10)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="67" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K10">
         <f>COUNTIF(Stats!D:D,'Player Count'!J10)</f>
@@ -14862,7 +15151,7 @@
       </c>
       <c r="M10" s="109"/>
       <c r="N10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O10">
         <f>COUNTIF(Stats!D:D,'Player Count'!N10)</f>
@@ -14872,21 +15161,21 @@
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="67" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C11">
         <f>COUNTIF(Stats!D:D,'Player Count'!B11)</f>
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G11">
         <f>COUNTIF(Stats!D:D,'Player Count'!F11)</f>
         <v>2</v>
       </c>
       <c r="J11" s="67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K11">
         <f>COUNTIF(Stats!D:D,'Player Count'!J11)</f>
@@ -14894,7 +15183,7 @@
       </c>
       <c r="M11" s="109"/>
       <c r="N11" s="67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O11">
         <f>COUNTIF(Stats!D:D,'Player Count'!N11)</f>
@@ -14904,21 +15193,21 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C12">
         <f>COUNTIF(Stats!D:D,'Player Count'!B12)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="67" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G12">
         <f>COUNTIF(Stats!D:D,'Player Count'!F12)</f>
         <v>1</v>
       </c>
       <c r="J12" s="67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K12">
         <f>COUNTIF(Stats!D:D,'Player Count'!J12)</f>
@@ -14926,7 +15215,7 @@
       </c>
       <c r="M12" s="109"/>
       <c r="N12" s="67" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O12">
         <f>COUNTIF(Stats!D:D,'Player Count'!N12)</f>
@@ -14936,29 +15225,29 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C13">
         <f>COUNTIF(Stats!D:D,'Player Count'!B13)</f>
         <v>3</v>
       </c>
       <c r="F13" s="67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G13">
         <f>COUNTIF(Stats!D:D,'Player Count'!F13)</f>
         <v>0</v>
       </c>
       <c r="J13" s="67" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K13">
         <f>COUNTIF(Stats!D:D,'Player Count'!J13)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="109"/>
       <c r="N13" s="67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O13">
         <f>COUNTIF(Stats!D:D,'Player Count'!N13)</f>
@@ -14968,21 +15257,21 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C14">
         <f>COUNTIF(Stats!D:D,'Player Count'!B14)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="67" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G14">
         <f>COUNTIF(Stats!D:D,'Player Count'!F14)</f>
         <v>0</v>
       </c>
       <c r="J14" s="67" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K14">
         <f>COUNTIF(Stats!D:D,'Player Count'!J14)</f>
@@ -14990,7 +15279,7 @@
       </c>
       <c r="M14" s="109"/>
       <c r="N14" s="67" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O14">
         <f>COUNTIF(Stats!D:D,'Player Count'!N14)</f>
@@ -15000,29 +15289,29 @@
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15">
         <f>COUNTIF(Stats!D:D,'Player Count'!B15)</f>
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G15">
         <f>COUNTIF(Stats!D:D,'Player Count'!F15)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K15">
         <f>COUNTIF(Stats!D:D,'Player Count'!J15)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" s="109"/>
       <c r="N15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O15">
         <f>COUNTIF(Stats!D:D,'Player Count'!N15)</f>
@@ -15032,53 +15321,53 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C16">
         <f>COUNTIF(Stats!D:D,'Player Count'!B16)</f>
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G16">
         <f>COUNTIF(Stats!D:D,'Player Count'!F16)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="67" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K16">
         <f>COUNTIF(Stats!D:D,'Player Count'!J16)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" s="109"/>
       <c r="N16" s="67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O16">
         <f>COUNTIF(Stats!D:D,'Player Count'!N16)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="109"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C17">
         <f>COUNTIF(Stats!D:D,'Player Count'!B17)</f>
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G17">
         <f>COUNTIF(Stats!D:D,'Player Count'!F17)</f>
         <v>2</v>
       </c>
       <c r="J17" s="67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K17">
         <f>COUNTIF(Stats!D:D,'Player Count'!J17)</f>
@@ -15086,7 +15375,7 @@
       </c>
       <c r="M17" s="109"/>
       <c r="N17" s="67" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O17">
         <f>COUNTIF(Stats!D:D,'Player Count'!N17)</f>
@@ -15096,21 +15385,21 @@
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18">
         <f>COUNTIF(Stats!D:D,'Player Count'!B18)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="67" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G18">
         <f>COUNTIF(Stats!D:D,'Player Count'!F18)</f>
         <v>4</v>
       </c>
       <c r="J18" s="67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K18">
         <f>COUNTIF(Stats!D:D,'Player Count'!J18)</f>
@@ -15118,31 +15407,31 @@
       </c>
       <c r="M18" s="109"/>
       <c r="N18" s="67" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O18">
         <f>COUNTIF(Stats!D:D,'Player Count'!N18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="109"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C19">
         <f>COUNTIF(Stats!D:D,'Player Count'!B19)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G19">
         <f>COUNTIF(Stats!D:D,'Player Count'!F19)</f>
         <v>1</v>
       </c>
       <c r="J19" s="67" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K19">
         <f>COUNTIF(Stats!D:D,'Player Count'!J19)</f>
@@ -15150,31 +15439,31 @@
       </c>
       <c r="M19" s="109"/>
       <c r="N19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O19">
         <f>COUNTIF(Stats!D:D,'Player Count'!N19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="109"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C20">
         <f>COUNTIF(Stats!D:D,'Player Count'!B20)</f>
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G20">
         <f>COUNTIF(Stats!D:D,'Player Count'!F20)</f>
         <v>0</v>
       </c>
       <c r="J20" s="67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K20">
         <f>COUNTIF(Stats!D:D,'Player Count'!J20)</f>
@@ -15182,31 +15471,31 @@
       </c>
       <c r="M20" s="109"/>
       <c r="N20" s="67" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O20">
         <f>COUNTIF(Stats!D:D,'Player Count'!N20)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="109"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C21">
         <f>COUNTIF(Stats!D:D,'Player Count'!B21)</f>
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G21">
         <f>COUNTIF(Stats!D:D,'Player Count'!F21)</f>
         <v>2</v>
       </c>
       <c r="J21" s="67" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K21">
         <f>COUNTIF(Stats!D:D,'Player Count'!J21)</f>
@@ -15214,7 +15503,7 @@
       </c>
       <c r="M21" s="109"/>
       <c r="N21" s="67" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O21">
         <f>COUNTIF(Stats!D:D,'Player Count'!N21)</f>
@@ -15224,29 +15513,29 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22">
         <f>COUNTIF(Stats!D:D,'Player Count'!B22)</f>
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G22">
         <f>COUNTIF(Stats!D:D,'Player Count'!F22)</f>
         <v>2</v>
       </c>
       <c r="J22" s="67" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K22">
         <f>COUNTIF(Stats!D:D,'Player Count'!J22)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M22" s="109"/>
       <c r="N22" s="67" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O22">
         <f>COUNTIF(Stats!D:D,'Player Count'!N22)</f>
@@ -15256,21 +15545,21 @@
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23">
         <f>COUNTIF(Stats!D:D,'Player Count'!B23)</f>
         <v>5</v>
       </c>
       <c r="F23" s="67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G23">
         <f>COUNTIF(Stats!D:D,'Player Count'!F23)</f>
         <v>5</v>
       </c>
       <c r="J23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K23">
         <f>COUNTIF(Stats!D:D,'Player Count'!J23)</f>
@@ -15278,7 +15567,7 @@
       </c>
       <c r="M23" s="109"/>
       <c r="N23" s="67" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O23">
         <f>COUNTIF(Stats!D:D,'Player Count'!N23)</f>
@@ -15288,29 +15577,29 @@
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" s="67" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C24">
         <f>COUNTIF(Stats!D:D,'Player Count'!B24)</f>
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G24">
         <f>COUNTIF(Stats!D:D,'Player Count'!F24)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" s="67" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K24">
         <f>COUNTIF(Stats!D:D,'Player Count'!J24)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24" s="109"/>
       <c r="N24" s="67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O24">
         <f>COUNTIF(Stats!D:D,'Player Count'!N24)</f>
@@ -15320,21 +15609,21 @@
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="67" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25">
         <f>COUNTIF(Stats!D:D,'Player Count'!B25)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G25">
         <f>COUNTIF(Stats!D:D,'Player Count'!F25)</f>
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K25">
         <f>COUNTIF(Stats!D:D,'Player Count'!J25)</f>
@@ -15342,7 +15631,7 @@
       </c>
       <c r="M25" s="109"/>
       <c r="N25" s="67" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O25">
         <f>COUNTIF(Stats!D:D,'Player Count'!N25)</f>
@@ -15352,21 +15641,21 @@
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" s="78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G26">
         <f>COUNTIF(Stats!D:D,'Player Count'!F26)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" s="67" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K26">
         <f>COUNTIF(Stats!D:D,'Player Count'!J26)</f>
@@ -15374,7 +15663,7 @@
       </c>
       <c r="M26" s="109"/>
       <c r="N26" s="67" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O26">
         <f>COUNTIF(Stats!D:D,'Player Count'!N26)</f>
@@ -15384,14 +15673,14 @@
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G27">
         <f>COUNTIF(Stats!D:D,'Player Count'!F27)</f>
         <v>0</v>
       </c>
       <c r="J27" s="67" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K27">
         <f>COUNTIF(Stats!D:D,'Player Count'!J27)</f>
@@ -15399,7 +15688,7 @@
       </c>
       <c r="M27" s="109"/>
       <c r="N27" s="67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O27">
         <f>COUNTIF(Stats!D:D,'Player Count'!N27)</f>
@@ -15409,14 +15698,14 @@
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G28">
         <f>COUNTIF(Stats!D:D,'Player Count'!F28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K28">
         <f>COUNTIF(Stats!D:D,'Player Count'!J28)</f>
@@ -15424,31 +15713,31 @@
       </c>
       <c r="M28" s="109"/>
       <c r="N28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O28">
         <f>COUNTIF(Stats!D:D,'Player Count'!N28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="109"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G29">
         <f>COUNTIF(Stats!D:D,'Player Count'!F29)</f>
         <v>2</v>
       </c>
       <c r="J29" s="67" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K29">
         <f>COUNTIF(Stats!D:D,'Player Count'!J29)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="67" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O29">
         <f>COUNTIF(Stats!D:D,'Player Count'!N29)</f>
@@ -15458,25 +15747,25 @@
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" s="67"/>
       <c r="F30" s="78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G30" s="78">
         <f>SUM(G6:G29)</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J30" s="78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="N30" s="78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
@@ -15496,32 +15785,32 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.44311377245508982</v>
+        <v>0.43646408839779005</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.23952095808383234</v>
+        <v>0.20994475138121546</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.17964071856287425</v>
+        <v>0.20441988950276244</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.1377245508982036</v>
+        <v>0.14917127071823205</v>
       </c>
     </row>
   </sheetData>
@@ -15544,60 +15833,60 @@
   <sheetData>
     <row r="5" spans="6:24" x14ac:dyDescent="0.3">
       <c r="G5" s="67" t="s">
+        <v>321</v>
+      </c>
+      <c r="H5" s="67" t="s">
         <v>324</v>
       </c>
-      <c r="H5" s="67" t="s">
+      <c r="I5" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="J5" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="K5" s="67" t="s">
         <v>327</v>
       </c>
-      <c r="I5" s="67" t="s">
+      <c r="L5" s="67" t="s">
         <v>328</v>
       </c>
-      <c r="J5" s="67" t="s">
+      <c r="M5" s="67" t="s">
         <v>329</v>
       </c>
-      <c r="K5" s="67" t="s">
+      <c r="N5" s="67" t="s">
         <v>330</v>
       </c>
-      <c r="L5" s="67" t="s">
+      <c r="O5" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="M5" s="67" t="s">
+      <c r="P5" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="N5" s="67" t="s">
+      <c r="Q5" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="O5" s="67" t="s">
+      <c r="R5" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="P5" s="67" t="s">
+      <c r="S5" s="67" t="s">
+        <v>334</v>
+      </c>
+      <c r="T5" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="Q5" s="67" t="s">
+      <c r="U5" s="67" t="s">
         <v>336</v>
       </c>
-      <c r="R5" s="67" t="s">
+      <c r="V5" s="67" t="s">
         <v>337</v>
       </c>
-      <c r="S5" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="T5" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="U5" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="V5" s="67" t="s">
-        <v>340</v>
-      </c>
       <c r="W5" s="67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="113">
         <v>-20</v>
@@ -15638,7 +15927,7 @@
         <v>280</v>
       </c>
       <c r="X6" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="6:24" x14ac:dyDescent="0.3">
@@ -15680,7 +15969,7 @@
         <v>210</v>
       </c>
       <c r="X7" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="6:24" x14ac:dyDescent="0.3">
@@ -15804,7 +16093,7 @@
         <v>-65</v>
       </c>
       <c r="X10" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="6:24" x14ac:dyDescent="0.3">
@@ -15844,7 +16133,7 @@
         <v>-45</v>
       </c>
       <c r="X11" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="6:24" x14ac:dyDescent="0.3">
@@ -15888,7 +16177,7 @@
         <v>5</v>
       </c>
       <c r="X12" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="6:24" x14ac:dyDescent="0.3">
@@ -15922,7 +16211,7 @@
         <v>-35</v>
       </c>
       <c r="X13" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="6:24" x14ac:dyDescent="0.3">
@@ -15964,12 +16253,12 @@
         <v>-45</v>
       </c>
       <c r="X14" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G15" s="113">
         <v>-20</v>
@@ -16049,12 +16338,12 @@
         <v>-60</v>
       </c>
       <c r="X16" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="113">
         <v>-20</v>
@@ -16089,7 +16378,7 @@
     </row>
     <row r="18" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F18" s="67" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G18" s="113">
         <v>-20</v>
@@ -16118,12 +16407,12 @@
         <v>-35</v>
       </c>
       <c r="X18" s="67" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F19" s="67" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G19" s="113">
         <v>-20</v>

--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1330" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1A2389-ED17-4E57-A138-F1DE0706B28B}"/>
+  <xr:revisionPtr revIDLastSave="1392" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16F01DB7-1CEF-4279-A5ED-179DC90924DF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="469">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1401,6 +1401,51 @@
   </si>
   <si>
     <t>AARON COLLINS</t>
+  </si>
+  <si>
+    <t>Glens</t>
+  </si>
+  <si>
+    <t>Wooden Spoon Army</t>
+  </si>
+  <si>
+    <t>Crème D'Advocat</t>
+  </si>
+  <si>
+    <t>#holyf**K</t>
+  </si>
+  <si>
+    <t>NEWQUAY HORNETS</t>
+  </si>
+  <si>
+    <t>PHOENIX FLYERS</t>
+  </si>
+  <si>
+    <t>KINGS XI</t>
+  </si>
+  <si>
+    <t>ALTERNATIVE ULSTERMEN</t>
+  </si>
+  <si>
+    <t>SURREAL MADRID</t>
+  </si>
+  <si>
+    <t>WOODHALL SPA WHITES</t>
+  </si>
+  <si>
+    <t>MUNTERS UNITED</t>
+  </si>
+  <si>
+    <t>BETTER TOGETHER</t>
+  </si>
+  <si>
+    <t>DYNAMO DURHAM</t>
+  </si>
+  <si>
+    <t>AMERICA</t>
+  </si>
+  <si>
+    <t>KONSTANTINOS MAVROPANOS</t>
   </si>
 </sst>
 </file>
@@ -3456,11 +3501,11 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
@@ -3501,7 +3546,7 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
@@ -3509,7 +3554,7 @@
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3536,7 +3581,7 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
@@ -3544,7 +3589,7 @@
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3580,11 +3625,11 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
@@ -3593,23 +3638,27 @@
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79"/>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="106" t="s">
         <v>343</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="29">
+      <c r="D9" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="E9" s="107">
         <v>2</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="108">
         <v>0</v>
       </c>
-      <c r="G9" s="83"/>
-      <c r="H9" s="75"/>
+      <c r="G9" s="83" t="s">
+        <v>414</v>
+      </c>
+      <c r="H9" s="84">
+        <v>46282</v>
+      </c>
       <c r="I9" s="99"/>
       <c r="J9" s="82"/>
       <c r="K9" s="71" t="str">
@@ -3622,7 +3671,7 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
@@ -3630,17 +3679,29 @@
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="79"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="87"/>
+      <c r="B10" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>468</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F10" s="30">
+        <v>0</v>
+      </c>
+      <c r="G10" s="87">
+        <v>46282</v>
+      </c>
       <c r="H10" s="84"/>
       <c r="I10" s="85"/>
       <c r="J10" s="82"/>
@@ -3701,11 +3762,11 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
@@ -3750,11 +3811,11 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
@@ -3794,7 +3855,7 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
@@ -3802,7 +3863,7 @@
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R13" s="118"/>
       <c r="S13" s="118"/>
@@ -3825,7 +3886,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="87"/>
       <c r="H14" s="84"/>
@@ -3841,7 +3902,7 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
@@ -3849,7 +3910,7 @@
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -3876,11 +3937,11 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
@@ -3918,7 +3979,7 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
@@ -3926,7 +3987,7 @@
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3960,15 +4021,15 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R17" s="118"/>
       <c r="S17" s="118"/>
@@ -4036,7 +4097,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19" s="87"/>
       <c r="H19" s="84"/>
@@ -4203,7 +4264,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4332,7 +4393,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G32" s="80"/>
       <c r="H32" s="94"/>
@@ -4414,7 +4475,7 @@
         <v>351</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>24</v>
+        <v>424</v>
       </c>
       <c r="E36" s="29">
         <v>1</v>
@@ -4816,7 +4877,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -4969,7 +5030,7 @@
         <v>413</v>
       </c>
       <c r="F60" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" s="86">
         <v>46268</v>
@@ -5449,7 +5510,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -5863,7 +5924,7 @@
         <v>7</v>
       </c>
       <c r="F98" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G98" s="87"/>
       <c r="H98" s="91"/>
@@ -6084,7 +6145,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6208,7 +6269,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -6735,7 +6796,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7694,7 +7755,7 @@
         <v>8</v>
       </c>
       <c r="F175" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G175" s="87"/>
       <c r="H175" s="91"/>
@@ -7971,7 +8032,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -8429,7 +8490,7 @@
         <v>5</v>
       </c>
       <c r="F208" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G208" s="83"/>
       <c r="H208" s="91"/>
@@ -8574,7 +8635,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -8698,7 +8759,7 @@
         <v>8</v>
       </c>
       <c r="F221" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G221" s="80"/>
       <c r="H221" s="94"/>
@@ -9209,7 +9270,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -9333,7 +9394,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G248" s="80"/>
       <c r="H248" s="94"/>
@@ -9796,7 +9857,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -10167,7 +10228,7 @@
         <v>1</v>
       </c>
       <c r="F286" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G286" s="83"/>
       <c r="H286" s="91"/>
@@ -10383,7 +10444,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -10536,7 +10597,7 @@
         <v>413</v>
       </c>
       <c r="F303" s="21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G303" s="87">
         <v>46261</v>
@@ -11032,7 +11093,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -11156,7 +11217,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -11504,7 +11565,7 @@
         <v>1</v>
       </c>
       <c r="F343" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G343" s="87"/>
       <c r="H343" s="91"/>
@@ -11618,7 +11679,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -13327,10 +13388,14 @@
       <c r="A4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="68"/>
+      <c r="B4" s="68" t="s">
+        <v>32</v>
+      </c>
       <c r="C4" s="64"/>
       <c r="D4" s="64"/>
-      <c r="E4" s="69"/>
+      <c r="E4" s="68" t="s">
+        <v>466</v>
+      </c>
       <c r="F4" s="100"/>
       <c r="G4" s="100"/>
       <c r="H4" s="38"/>
@@ -13357,10 +13422,14 @@
       <c r="A5" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="68"/>
+      <c r="B5" s="68" t="s">
+        <v>399</v>
+      </c>
       <c r="C5" s="64"/>
       <c r="D5" s="64"/>
-      <c r="E5" s="69"/>
+      <c r="E5" s="68" t="s">
+        <v>465</v>
+      </c>
       <c r="F5" s="100"/>
       <c r="G5" s="100"/>
       <c r="H5" s="38"/>
@@ -13387,10 +13456,14 @@
       <c r="A6" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="68"/>
+      <c r="B6" s="68" t="s">
+        <v>157</v>
+      </c>
       <c r="C6" s="64"/>
       <c r="D6" s="64"/>
-      <c r="E6" s="69"/>
+      <c r="E6" s="68" t="s">
+        <v>464</v>
+      </c>
       <c r="F6" s="100"/>
       <c r="G6" s="100"/>
       <c r="H6" s="38"/>
@@ -13417,10 +13490,14 @@
       <c r="A7" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="68"/>
+      <c r="B7" s="68" t="s">
+        <v>15</v>
+      </c>
       <c r="C7" s="64"/>
       <c r="D7" s="64"/>
-      <c r="E7" s="69"/>
+      <c r="E7" s="68" t="s">
+        <v>463</v>
+      </c>
       <c r="F7" s="100"/>
       <c r="G7" s="100"/>
       <c r="H7" s="38"/>
@@ -13447,15 +13524,21 @@
       <c r="A8" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="68"/>
+      <c r="B8" s="68" t="s">
+        <v>341</v>
+      </c>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="68" t="s">
+        <v>457</v>
+      </c>
       <c r="F8" s="64"/>
       <c r="G8" s="64"/>
       <c r="H8" s="38"/>
       <c r="I8" s="38"/>
-      <c r="J8" s="98"/>
+      <c r="J8" s="98" t="s">
+        <v>454</v>
+      </c>
       <c r="K8" s="38"/>
       <c r="L8" s="38"/>
       <c r="M8" s="38"/>
@@ -13475,15 +13558,21 @@
       <c r="A9" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="68"/>
+      <c r="B9" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="68" t="s">
+        <v>458</v>
+      </c>
       <c r="F9" s="64"/>
       <c r="G9" s="64"/>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
-      <c r="J9" s="98"/>
+      <c r="J9" s="98" t="s">
+        <v>455</v>
+      </c>
       <c r="K9" s="38"/>
       <c r="L9" s="38"/>
       <c r="M9" s="38"/>
@@ -13503,15 +13592,21 @@
       <c r="A10" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="68"/>
+      <c r="B10" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="68" t="s">
+        <v>459</v>
+      </c>
       <c r="F10" s="64"/>
       <c r="G10" s="64"/>
       <c r="H10" s="38"/>
       <c r="I10" s="38"/>
-      <c r="J10" s="98"/>
+      <c r="J10" s="98" t="s">
+        <v>456</v>
+      </c>
       <c r="K10" s="38"/>
       <c r="L10" s="38"/>
       <c r="M10" s="38"/>
@@ -13531,10 +13626,14 @@
       <c r="A11" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="68"/>
+      <c r="B11" s="68" t="s">
+        <v>125</v>
+      </c>
       <c r="C11" s="64"/>
       <c r="D11" s="64"/>
-      <c r="E11" s="68"/>
+      <c r="E11" s="68" t="s">
+        <v>460</v>
+      </c>
       <c r="F11" s="64"/>
       <c r="G11" s="64"/>
       <c r="H11" s="38"/>
@@ -13559,10 +13658,14 @@
       <c r="A12" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="68"/>
+      <c r="B12" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="68" t="s">
+        <v>461</v>
+      </c>
       <c r="F12" s="64"/>
       <c r="G12" s="64"/>
       <c r="H12" s="38"/>
@@ -13587,10 +13690,14 @@
       <c r="A13" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="68"/>
+      <c r="B13" s="68" t="s">
+        <v>29</v>
+      </c>
       <c r="C13" s="64"/>
       <c r="D13" s="64"/>
-      <c r="E13" s="69"/>
+      <c r="E13" s="68" t="s">
+        <v>462</v>
+      </c>
       <c r="F13" s="100"/>
       <c r="G13" s="100"/>
       <c r="H13" s="38"/>
@@ -15396,7 +15503,7 @@
       </c>
       <c r="G18">
         <f>COUNTIF(Stats!D:D,'Player Count'!F18)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="67" t="s">
         <v>223</v>
@@ -15549,14 +15656,14 @@
       </c>
       <c r="C23">
         <f>COUNTIF(Stats!D:D,'Player Count'!B23)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" s="67" t="s">
         <v>184</v>
       </c>
       <c r="G23">
         <f>COUNTIF(Stats!D:D,'Player Count'!F23)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23" t="s">
         <v>227</v>
@@ -15645,7 +15752,7 @@
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F26" t="s">
         <v>208</v>
@@ -15789,28 +15896,28 @@
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.43646408839779005</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20994475138121546</v>
+        <v>0.21111111111111111</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20441988950276244</v>
+        <v>0.20555555555555555</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.14917127071823205</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1392" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16F01DB7-1CEF-4279-A5ED-179DC90924DF}"/>
+  <xr:revisionPtr revIDLastSave="1605" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B68D3B-A854-496E-8406-D60DAA26BD45}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="483">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1436,9 +1436,6 @@
     <t>MUNTERS UNITED</t>
   </si>
   <si>
-    <t>BETTER TOGETHER</t>
-  </si>
-  <si>
     <t>DYNAMO DURHAM</t>
   </si>
   <si>
@@ -1446,6 +1443,51 @@
   </si>
   <si>
     <t>KONSTANTINOS MAVROPANOS</t>
+  </si>
+  <si>
+    <t>(1 - 0)</t>
+  </si>
+  <si>
+    <t>(0 - 0)</t>
+  </si>
+  <si>
+    <t>(1 - 2)</t>
+  </si>
+  <si>
+    <t>(3 - 2)</t>
+  </si>
+  <si>
+    <t>(1 - 1)</t>
+  </si>
+  <si>
+    <t>EDINBURGH STEALERS</t>
+  </si>
+  <si>
+    <t>(0 - 3)</t>
+  </si>
+  <si>
+    <t>(1 - 3)</t>
+  </si>
+  <si>
+    <t>(2 - 1)</t>
+  </si>
+  <si>
+    <t>(7 - 0)</t>
+  </si>
+  <si>
+    <t>(2 - 3)</t>
+  </si>
+  <si>
+    <t>(3 - 3)</t>
+  </si>
+  <si>
+    <t>(5 - 1)</t>
+  </si>
+  <si>
+    <t>(2 - 2)</t>
+  </si>
+  <si>
+    <t>(4 - 2)</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1908,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2168,6 +2210,54 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3462,11 +3552,11 @@
       <c r="O4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
+      <c r="R4" s="134"/>
+      <c r="S4" s="134"/>
+      <c r="T4" s="134"/>
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
     </row>
     <row r="5" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
@@ -3505,11 +3595,11 @@
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3528,7 +3618,7 @@
         <v>413</v>
       </c>
       <c r="F6" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="86">
         <v>46275</v>
@@ -3546,11 +3636,11 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
@@ -3645,7 +3735,7 @@
         <v>343</v>
       </c>
       <c r="D9" s="106" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E9" s="107">
         <v>2</v>
@@ -3671,15 +3761,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3688,7 +3778,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>53</v>
@@ -3697,7 +3787,7 @@
         <v>413</v>
       </c>
       <c r="F10" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="87">
         <v>46282</v>
@@ -3715,21 +3805,21 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>12</v>
-      </c>
-      <c r="R10" s="118"/>
-      <c r="S10" s="118"/>
-      <c r="T10" s="118"/>
-      <c r="U10" s="118"/>
-      <c r="V10" s="118"/>
+        <v>15</v>
+      </c>
+      <c r="R10" s="134"/>
+      <c r="S10" s="134"/>
+      <c r="T10" s="134"/>
+      <c r="U10" s="134"/>
+      <c r="V10" s="134"/>
     </row>
     <row r="11" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="79"/>
@@ -3762,15 +3852,15 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -3815,11 +3905,11 @@
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3855,21 +3945,21 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>3</v>
-      </c>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="118"/>
-      <c r="U13" s="118"/>
-      <c r="V13" s="118"/>
+        <v>6</v>
+      </c>
+      <c r="R13" s="134"/>
+      <c r="S13" s="134"/>
+      <c r="T13" s="134"/>
+      <c r="U13" s="134"/>
+      <c r="V13" s="134"/>
     </row>
     <row r="14" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="79"/>
@@ -3902,11 +3992,11 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
@@ -3937,15 +4027,15 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3979,11 +4069,11 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
@@ -4021,21 +4111,21 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>10</v>
-      </c>
-      <c r="R17" s="118"/>
-      <c r="S17" s="118"/>
-      <c r="T17" s="118"/>
-      <c r="U17" s="118"/>
-      <c r="V17" s="118"/>
+        <v>11</v>
+      </c>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="134"/>
     </row>
     <row r="18" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="79"/>
@@ -4068,15 +4158,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4139,11 +4229,11 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="R20" s="118"/>
-      <c r="S20" s="118"/>
-      <c r="T20" s="118"/>
-      <c r="U20" s="118"/>
-      <c r="V20" s="118"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="134"/>
+      <c r="U20" s="134"/>
+      <c r="V20" s="134"/>
     </row>
     <row r="21" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79"/>
@@ -4227,11 +4317,11 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-      <c r="R24" s="118"/>
-      <c r="S24" s="118"/>
-      <c r="T24" s="118"/>
-      <c r="U24" s="118"/>
-      <c r="V24" s="118"/>
+      <c r="R24" s="134"/>
+      <c r="S24" s="134"/>
+      <c r="T24" s="134"/>
+      <c r="U24" s="134"/>
+      <c r="V24" s="134"/>
     </row>
     <row r="25" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="79"/>
@@ -4309,11 +4399,11 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-      <c r="R28" s="118"/>
-      <c r="S28" s="118"/>
-      <c r="T28" s="118"/>
-      <c r="U28" s="118"/>
-      <c r="V28" s="118"/>
+      <c r="R28" s="134"/>
+      <c r="S28" s="134"/>
+      <c r="T28" s="134"/>
+      <c r="U28" s="134"/>
+      <c r="V28" s="134"/>
     </row>
     <row r="29" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -4515,32 +4605,34 @@
       <c r="B38" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="118" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="119">
         <v>19</v>
       </c>
-      <c r="F38" s="30">
-        <v>0</v>
+      <c r="F38" s="120">
+        <v>2</v>
       </c>
       <c r="G38" s="87"/>
       <c r="H38" s="91"/>
-      <c r="I38" s="93"/>
+      <c r="I38" s="93">
+        <v>2</v>
+      </c>
       <c r="J38" s="76"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
-      <c r="R38" s="118"/>
-      <c r="S38" s="118"/>
-      <c r="T38" s="118"/>
-      <c r="U38" s="118"/>
-      <c r="V38" s="118"/>
+      <c r="R38" s="134"/>
+      <c r="S38" s="134"/>
+      <c r="T38" s="134"/>
+      <c r="U38" s="134"/>
+      <c r="V38" s="134"/>
     </row>
     <row r="39" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="79"/>
@@ -4557,11 +4649,13 @@
         <v>11</v>
       </c>
       <c r="F39" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
-      <c r="I39" s="89"/>
+      <c r="I39" s="89">
+        <v>1</v>
+      </c>
       <c r="J39" s="76"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -4645,11 +4739,13 @@
         <v>1</v>
       </c>
       <c r="F43" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="87"/>
       <c r="H43" s="91"/>
-      <c r="I43" s="89"/>
+      <c r="I43" s="89">
+        <v>1</v>
+      </c>
       <c r="J43" s="76"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -4730,13 +4826,15 @@
         <v>413</v>
       </c>
       <c r="F46" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="91">
         <v>46261</v>
       </c>
       <c r="H46" s="91"/>
-      <c r="I46" s="89"/>
+      <c r="I46" s="89">
+        <v>1</v>
+      </c>
       <c r="J46" s="76"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -4759,11 +4857,13 @@
         <v>13</v>
       </c>
       <c r="F47" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="91"/>
       <c r="H47" s="91"/>
-      <c r="I47" s="89"/>
+      <c r="I47" s="89">
+        <v>1</v>
+      </c>
       <c r="J47" s="76"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -4786,11 +4886,13 @@
         <v>2</v>
       </c>
       <c r="F48" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="91"/>
       <c r="H48" s="91"/>
-      <c r="I48" s="89"/>
+      <c r="I48" s="89">
+        <v>1</v>
+      </c>
       <c r="J48" s="76"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -4877,7 +4979,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -4993,14 +5095,14 @@
       <c r="B59" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="C59" s="115"/>
-      <c r="D59" s="114" t="s">
+      <c r="C59" s="128"/>
+      <c r="D59" s="129" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="116">
+      <c r="E59" s="130">
         <v>5</v>
       </c>
-      <c r="F59" s="117">
+      <c r="F59" s="131">
         <v>10</v>
       </c>
       <c r="G59" s="80" t="s">
@@ -5022,14 +5124,14 @@
       <c r="B60" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21" t="s">
+      <c r="C60" s="132"/>
+      <c r="D60" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="22" t="s">
+      <c r="E60" s="133" t="s">
         <v>413</v>
       </c>
-      <c r="F60" s="21">
+      <c r="F60" s="132">
         <v>4</v>
       </c>
       <c r="G60" s="86">
@@ -5047,10 +5149,10 @@
     <row r="61" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="79"/>
       <c r="B61" s="21"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="21"/>
+      <c r="C61" s="132"/>
+      <c r="D61" s="132"/>
+      <c r="E61" s="133"/>
+      <c r="F61" s="132"/>
       <c r="G61" s="80"/>
       <c r="H61" s="92"/>
       <c r="I61" s="92"/>
@@ -5066,16 +5168,16 @@
       <c r="B62" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="118" t="s">
         <v>136</v>
       </c>
-      <c r="D62" s="28" t="s">
+      <c r="D62" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="E62" s="29">
+      <c r="E62" s="119">
         <v>4</v>
       </c>
-      <c r="F62" s="30">
+      <c r="F62" s="120">
         <v>0</v>
       </c>
       <c r="G62" s="83"/>
@@ -5093,16 +5195,16 @@
       <c r="B63" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="28" t="s">
+      <c r="C63" s="118" t="s">
         <v>96</v>
       </c>
-      <c r="D63" s="28" t="s">
+      <c r="D63" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E63" s="29">
+      <c r="E63" s="119">
         <v>1</v>
       </c>
-      <c r="F63" s="30">
+      <c r="F63" s="120">
         <v>1</v>
       </c>
       <c r="G63" s="87"/>
@@ -5118,10 +5220,10 @@
     <row r="64" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="79"/>
       <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="30"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="118"/>
+      <c r="E64" s="119"/>
+      <c r="F64" s="120"/>
       <c r="G64" s="87"/>
       <c r="H64" s="90"/>
       <c r="I64" s="90"/>
@@ -5137,16 +5239,16 @@
       <c r="B65" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C65" s="106" t="s">
+      <c r="C65" s="125" t="s">
         <v>113</v>
       </c>
-      <c r="D65" s="106" t="s">
+      <c r="D65" s="125" t="s">
         <v>131</v>
       </c>
-      <c r="E65" s="107">
+      <c r="E65" s="126">
         <v>10</v>
       </c>
-      <c r="F65" s="108">
+      <c r="F65" s="127">
         <v>0</v>
       </c>
       <c r="G65" s="83" t="s">
@@ -5168,16 +5270,16 @@
       <c r="B66" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C66" s="28" t="s">
+      <c r="C66" s="118" t="s">
         <v>429</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="D66" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="E66" s="29" t="s">
+      <c r="E66" s="119" t="s">
         <v>413</v>
       </c>
-      <c r="F66" s="30">
+      <c r="F66" s="120">
         <v>0</v>
       </c>
       <c r="G66" s="87">
@@ -5197,16 +5299,16 @@
       <c r="B67" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="28" t="s">
+      <c r="C67" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="D67" s="28" t="s">
+      <c r="D67" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="E67" s="29">
+      <c r="E67" s="119">
         <v>17</v>
       </c>
-      <c r="F67" s="30">
+      <c r="F67" s="120">
         <v>4</v>
       </c>
       <c r="G67" s="83"/>
@@ -5224,16 +5326,16 @@
       <c r="B68" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C68" s="106" t="s">
+      <c r="C68" s="125" t="s">
         <v>353</v>
       </c>
-      <c r="D68" s="106" t="s">
+      <c r="D68" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="E68" s="107">
+      <c r="E68" s="126">
         <v>1</v>
       </c>
-      <c r="F68" s="108">
+      <c r="F68" s="127">
         <v>0</v>
       </c>
       <c r="G68" s="87" t="s">
@@ -5255,16 +5357,16 @@
       <c r="B69" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C69" s="28" t="s">
+      <c r="C69" s="118" t="s">
         <v>428</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="D69" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="E69" s="29" t="s">
+      <c r="E69" s="119" t="s">
         <v>413</v>
       </c>
-      <c r="F69" s="30">
+      <c r="F69" s="120">
         <v>2</v>
       </c>
       <c r="G69" s="91">
@@ -5284,16 +5386,16 @@
       <c r="B70" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="28" t="s">
+      <c r="C70" s="118" t="s">
         <v>110</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D70" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="29">
+      <c r="E70" s="119">
         <v>1</v>
       </c>
-      <c r="F70" s="30">
+      <c r="F70" s="120">
         <v>3</v>
       </c>
       <c r="G70" s="87"/>
@@ -5311,16 +5413,16 @@
       <c r="B71" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C71" s="28" t="s">
+      <c r="C71" s="118" t="s">
         <v>137</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D71" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="E71" s="29">
+      <c r="E71" s="119">
         <v>23</v>
       </c>
-      <c r="F71" s="30">
+      <c r="F71" s="120">
         <v>2</v>
       </c>
       <c r="G71" s="83"/>
@@ -5338,16 +5440,16 @@
       <c r="B72" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C72" s="28" t="s">
+      <c r="C72" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="D72" s="28" t="s">
+      <c r="D72" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="E72" s="29">
+      <c r="E72" s="119">
         <v>4</v>
       </c>
-      <c r="F72" s="30">
+      <c r="F72" s="120">
         <v>3</v>
       </c>
       <c r="G72" s="87"/>
@@ -5365,16 +5467,16 @@
       <c r="B73" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="118" t="s">
         <v>354</v>
       </c>
-      <c r="D73" s="28" t="s">
+      <c r="D73" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E73" s="29">
+      <c r="E73" s="119">
         <v>1</v>
       </c>
-      <c r="F73" s="30">
+      <c r="F73" s="120">
         <v>4</v>
       </c>
       <c r="G73" s="87"/>
@@ -5392,16 +5494,16 @@
       <c r="B74" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C74" s="28" t="s">
+      <c r="C74" s="118" t="s">
         <v>355</v>
       </c>
-      <c r="D74" s="28" t="s">
+      <c r="D74" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="E74" s="29">
+      <c r="E74" s="119">
         <v>1</v>
       </c>
-      <c r="F74" s="30">
+      <c r="F74" s="120">
         <v>0</v>
       </c>
       <c r="G74" s="87"/>
@@ -5682,19 +5784,19 @@
     </row>
     <row r="89" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="79"/>
-      <c r="B89" s="28" t="s">
+      <c r="B89" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="28" t="s">
+      <c r="C89" s="118" t="s">
         <v>315</v>
       </c>
-      <c r="D89" s="28" t="s">
+      <c r="D89" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E89" s="29">
+      <c r="E89" s="119">
         <v>7</v>
       </c>
-      <c r="F89" s="30">
+      <c r="F89" s="120">
         <v>0</v>
       </c>
       <c r="G89" s="83"/>
@@ -6269,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -6590,7 +6692,7 @@
         <v>413</v>
       </c>
       <c r="F126" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G126" s="87">
         <v>46261</v>
@@ -6796,7 +6898,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -6920,11 +7022,13 @@
         <v>1</v>
       </c>
       <c r="F140" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G140" s="80"/>
       <c r="H140" s="94"/>
-      <c r="I140" s="94"/>
+      <c r="I140" s="93">
+        <v>3</v>
+      </c>
       <c r="J140" s="76"/>
       <c r="K140" s="1"/>
       <c r="L140" s="1"/>
@@ -6998,16 +7102,16 @@
       <c r="B144" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C144" s="28" t="s">
+      <c r="C144" s="118" t="s">
         <v>365</v>
       </c>
-      <c r="D144" s="28" t="s">
+      <c r="D144" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="E144" s="29">
+      <c r="E144" s="119">
         <v>6</v>
       </c>
-      <c r="F144" s="30">
+      <c r="F144" s="120">
         <v>0</v>
       </c>
       <c r="G144" s="83"/>
@@ -7023,10 +7127,10 @@
     <row r="145" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="79"/>
       <c r="B145" s="28"/>
-      <c r="C145" s="28"/>
-      <c r="D145" s="28"/>
-      <c r="E145" s="29"/>
-      <c r="F145" s="30"/>
+      <c r="C145" s="118"/>
+      <c r="D145" s="118"/>
+      <c r="E145" s="119"/>
+      <c r="F145" s="120"/>
       <c r="G145" s="87"/>
       <c r="H145" s="91"/>
       <c r="I145" s="90"/>
@@ -7042,16 +7146,16 @@
       <c r="B146" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C146" s="106" t="s">
+      <c r="C146" s="125" t="s">
         <v>366</v>
       </c>
-      <c r="D146" s="106" t="s">
+      <c r="D146" s="125" t="s">
         <v>411</v>
       </c>
-      <c r="E146" s="107">
+      <c r="E146" s="126">
         <v>1</v>
       </c>
-      <c r="F146" s="108">
+      <c r="F146" s="127">
         <v>0</v>
       </c>
       <c r="G146" s="87" t="s">
@@ -7073,16 +7177,16 @@
       <c r="B147" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C147" s="28" t="s">
+      <c r="C147" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="D147" s="28" t="s">
+      <c r="D147" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="E147" s="29" t="s">
+      <c r="E147" s="119" t="s">
         <v>413</v>
       </c>
-      <c r="F147" s="30">
+      <c r="F147" s="120">
         <v>1</v>
       </c>
       <c r="G147" s="87">
@@ -7102,16 +7206,16 @@
       <c r="B148" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C148" s="106" t="s">
+      <c r="C148" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="D148" s="106" t="s">
+      <c r="D148" s="125" t="s">
         <v>352</v>
       </c>
-      <c r="E148" s="107">
+      <c r="E148" s="126">
         <v>6</v>
       </c>
-      <c r="F148" s="108">
+      <c r="F148" s="127">
         <v>3</v>
       </c>
       <c r="G148" s="87" t="s">
@@ -7133,16 +7237,16 @@
       <c r="B149" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C149" s="28" t="s">
+      <c r="C149" s="118" t="s">
         <v>452</v>
       </c>
-      <c r="D149" s="28" t="s">
+      <c r="D149" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="E149" s="29" t="s">
+      <c r="E149" s="119" t="s">
         <v>413</v>
       </c>
-      <c r="F149" s="30">
+      <c r="F149" s="120">
         <v>0</v>
       </c>
       <c r="G149" s="87">
@@ -7162,21 +7266,23 @@
       <c r="B150" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C150" s="28" t="s">
+      <c r="C150" s="118" t="s">
         <v>367</v>
       </c>
-      <c r="D150" s="28" t="s">
+      <c r="D150" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="E150" s="29">
+      <c r="E150" s="119">
         <v>2</v>
       </c>
-      <c r="F150" s="30">
-        <v>4</v>
+      <c r="F150" s="120">
+        <v>5</v>
       </c>
       <c r="G150" s="87"/>
       <c r="H150" s="91"/>
-      <c r="I150" s="90"/>
+      <c r="I150" s="90">
+        <v>1</v>
+      </c>
       <c r="J150" s="76"/>
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
@@ -7189,16 +7295,16 @@
       <c r="B151" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C151" s="28" t="s">
+      <c r="C151" s="118" t="s">
         <v>293</v>
       </c>
-      <c r="D151" s="28" t="s">
+      <c r="D151" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="E151" s="29">
+      <c r="E151" s="119">
         <v>1</v>
       </c>
-      <c r="F151" s="30">
+      <c r="F151" s="120">
         <v>2</v>
       </c>
       <c r="G151" s="83"/>
@@ -7216,16 +7322,16 @@
       <c r="B152" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C152" s="28" t="s">
+      <c r="C152" s="118" t="s">
         <v>162</v>
       </c>
-      <c r="D152" s="28" t="s">
+      <c r="D152" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="E152" s="29">
+      <c r="E152" s="119">
         <v>33</v>
       </c>
-      <c r="F152" s="30">
+      <c r="F152" s="120">
         <v>2</v>
       </c>
       <c r="G152" s="87"/>
@@ -7243,21 +7349,23 @@
       <c r="B153" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C153" s="28" t="s">
+      <c r="C153" s="118" t="s">
         <v>306</v>
       </c>
-      <c r="D153" s="28" t="s">
+      <c r="D153" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="E153" s="29">
+      <c r="E153" s="119">
         <v>13</v>
       </c>
-      <c r="F153" s="30">
-        <v>5</v>
+      <c r="F153" s="120">
+        <v>6</v>
       </c>
       <c r="G153" s="87"/>
       <c r="H153" s="91"/>
-      <c r="I153" s="90"/>
+      <c r="I153" s="90">
+        <v>1</v>
+      </c>
       <c r="J153" s="96"/>
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
@@ -7270,16 +7378,16 @@
       <c r="B154" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C154" s="28" t="s">
+      <c r="C154" s="118" t="s">
         <v>160</v>
       </c>
-      <c r="D154" s="28" t="s">
+      <c r="D154" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="E154" s="29">
+      <c r="E154" s="119">
         <v>25</v>
       </c>
-      <c r="F154" s="30">
+      <c r="F154" s="120">
         <v>3</v>
       </c>
       <c r="G154" s="87"/>
@@ -7445,7 +7553,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -7561,19 +7669,21 @@
       <c r="B167" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C167" s="13"/>
-      <c r="D167" s="12" t="s">
+      <c r="C167" s="121"/>
+      <c r="D167" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="E167" s="14">
+      <c r="E167" s="123">
         <v>4</v>
       </c>
-      <c r="F167" s="15">
-        <v>5</v>
+      <c r="F167" s="124">
+        <v>8</v>
       </c>
       <c r="G167" s="80"/>
       <c r="H167" s="94"/>
-      <c r="I167" s="92"/>
+      <c r="I167" s="92">
+        <v>3</v>
+      </c>
       <c r="J167" s="76"/>
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
@@ -7745,21 +7855,23 @@
       <c r="B175" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C175" s="28" t="s">
+      <c r="C175" s="118" t="s">
         <v>135</v>
       </c>
-      <c r="D175" s="28" t="s">
+      <c r="D175" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E175" s="29">
+      <c r="E175" s="119">
         <v>8</v>
       </c>
-      <c r="F175" s="30">
-        <v>3</v>
+      <c r="F175" s="120">
+        <v>4</v>
       </c>
       <c r="G175" s="87"/>
       <c r="H175" s="91"/>
-      <c r="I175" s="90"/>
+      <c r="I175" s="90">
+        <v>1</v>
+      </c>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
@@ -7870,11 +7982,13 @@
         <v>7</v>
       </c>
       <c r="F180" s="30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G180" s="91"/>
       <c r="H180" s="91"/>
-      <c r="I180" s="90"/>
+      <c r="I180" s="90">
+        <v>2</v>
+      </c>
       <c r="J180" s="76"/>
       <c r="K180" s="1"/>
       <c r="L180" s="1"/>
@@ -7887,16 +8001,16 @@
       <c r="B181" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C181" s="28" t="s">
+      <c r="C181" s="118" t="s">
         <v>124</v>
       </c>
-      <c r="D181" s="28" t="s">
+      <c r="D181" s="118" t="s">
         <v>115</v>
       </c>
-      <c r="E181" s="29">
+      <c r="E181" s="119">
         <v>3</v>
       </c>
-      <c r="F181" s="30">
+      <c r="F181" s="120">
         <v>0</v>
       </c>
       <c r="G181" s="91"/>
@@ -7914,17 +8028,17 @@
       <c r="B182" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C182" s="28" t="s">
+      <c r="C182" s="118" t="s">
         <v>371</v>
       </c>
-      <c r="D182" s="28" t="s">
+      <c r="D182" s="118" t="s">
         <v>363</v>
       </c>
-      <c r="E182" s="29">
+      <c r="E182" s="119">
         <v>1</v>
       </c>
-      <c r="F182" s="30">
-        <v>0</v>
+      <c r="F182" s="120">
+        <v>1</v>
       </c>
       <c r="G182" s="87"/>
       <c r="H182" s="91"/>
@@ -8032,7 +8146,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -8156,11 +8270,13 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
-      <c r="I194" s="90"/>
+      <c r="I194" s="90">
+        <v>1</v>
+      </c>
       <c r="J194" s="76"/>
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
@@ -8234,16 +8350,16 @@
       <c r="B198" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C198" s="28" t="s">
+      <c r="C198" s="118" t="s">
         <v>372</v>
       </c>
-      <c r="D198" s="28" t="s">
+      <c r="D198" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="E198" s="29">
+      <c r="E198" s="119">
         <v>3</v>
       </c>
-      <c r="F198" s="30">
+      <c r="F198" s="120">
         <v>0</v>
       </c>
       <c r="G198" s="87"/>
@@ -8332,16 +8448,16 @@
       <c r="B202" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C202" s="28" t="s">
+      <c r="C202" s="118" t="s">
         <v>138</v>
       </c>
-      <c r="D202" s="28" t="s">
+      <c r="D202" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="E202" s="29">
+      <c r="E202" s="119">
         <v>1</v>
       </c>
-      <c r="F202" s="30">
+      <c r="F202" s="120">
         <v>0</v>
       </c>
       <c r="G202" s="83"/>
@@ -8480,16 +8596,16 @@
       <c r="B208" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C208" s="28" t="s">
+      <c r="C208" s="118" t="s">
         <v>286</v>
       </c>
-      <c r="D208" s="28" t="s">
+      <c r="D208" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="E208" s="29">
+      <c r="E208" s="119">
         <v>5</v>
       </c>
-      <c r="F208" s="30">
+      <c r="F208" s="120">
         <v>3</v>
       </c>
       <c r="G208" s="83"/>
@@ -8507,21 +8623,23 @@
       <c r="B209" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C209" s="28" t="s">
+      <c r="C209" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="D209" s="28" t="s">
+      <c r="D209" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="E209" s="29">
+      <c r="E209" s="119">
         <v>49</v>
       </c>
-      <c r="F209" s="30">
-        <v>3</v>
+      <c r="F209" s="120">
+        <v>4</v>
       </c>
       <c r="G209" s="87"/>
       <c r="H209" s="91"/>
-      <c r="I209" s="90"/>
+      <c r="I209" s="90">
+        <v>1</v>
+      </c>
       <c r="J209" s="76"/>
       <c r="K209" s="1"/>
       <c r="L209" s="1"/>
@@ -8759,11 +8877,13 @@
         <v>8</v>
       </c>
       <c r="F221" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G221" s="80"/>
       <c r="H221" s="94"/>
-      <c r="I221" s="93"/>
+      <c r="I221" s="93">
+        <v>3</v>
+      </c>
       <c r="J221" s="76"/>
       <c r="K221" s="1"/>
       <c r="L221" s="1"/>
@@ -9038,11 +9158,13 @@
         <v>11</v>
       </c>
       <c r="F232" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G232" s="87"/>
       <c r="H232" s="91"/>
-      <c r="I232" s="89"/>
+      <c r="I232" s="89">
+        <v>1</v>
+      </c>
       <c r="J232" s="1"/>
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
@@ -9169,16 +9291,16 @@
       <c r="B237" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C237" s="28" t="s">
+      <c r="C237" s="118" t="s">
         <v>375</v>
       </c>
-      <c r="D237" s="28" t="s">
+      <c r="D237" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="E237" s="29">
+      <c r="E237" s="119">
         <v>13</v>
       </c>
-      <c r="F237" s="30">
+      <c r="F237" s="120">
         <v>2</v>
       </c>
       <c r="G237" s="87"/>
@@ -9270,7 +9392,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -9383,21 +9505,25 @@
     </row>
     <row r="248" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="79"/>
-      <c r="B248" s="12" t="s">
+      <c r="B248" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="C248" s="13"/>
-      <c r="D248" s="12" t="s">
+      <c r="C248" s="115"/>
+      <c r="D248" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="E248" s="14">
+      <c r="E248" s="116">
         <v>1</v>
       </c>
-      <c r="F248" s="15">
+      <c r="F248" s="117">
         <v>14</v>
       </c>
-      <c r="G248" s="80"/>
-      <c r="H248" s="94"/>
+      <c r="G248" s="80" t="s">
+        <v>414</v>
+      </c>
+      <c r="H248" s="94">
+        <v>46282</v>
+      </c>
       <c r="I248" s="90"/>
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
@@ -9408,12 +9534,22 @@
     </row>
     <row r="249" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="79"/>
-      <c r="B249" s="21"/>
+      <c r="B249" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="C249" s="21"/>
-      <c r="D249" s="21"/>
-      <c r="E249" s="22"/>
-      <c r="F249" s="21"/>
-      <c r="G249" s="86"/>
+      <c r="D249" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="E249" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="F249" s="21">
+        <v>0</v>
+      </c>
+      <c r="G249" s="86">
+        <v>46282</v>
+      </c>
       <c r="H249" s="94"/>
       <c r="I249" s="92"/>
       <c r="J249" s="1"/>
@@ -9668,11 +9804,13 @@
         <v>22</v>
       </c>
       <c r="F260" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
-      <c r="I260" s="90"/>
+      <c r="I260" s="90">
+        <v>1</v>
+      </c>
       <c r="J260" s="1"/>
       <c r="K260" s="1"/>
       <c r="L260" s="1"/>
@@ -9749,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="F263" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G263" s="87"/>
       <c r="H263" s="91"/>
@@ -9857,7 +9995,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -9981,11 +10119,13 @@
         <v>1</v>
       </c>
       <c r="F275" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G275" s="80"/>
       <c r="H275" s="94"/>
-      <c r="I275" s="92"/>
+      <c r="I275" s="92">
+        <v>1</v>
+      </c>
       <c r="J275" s="1"/>
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
@@ -10103,21 +10243,23 @@
       <c r="B281" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C281" s="28" t="s">
+      <c r="C281" s="118" t="s">
         <v>401</v>
       </c>
-      <c r="D281" s="28" t="s">
+      <c r="D281" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E281" s="29">
+      <c r="E281" s="119">
         <v>1</v>
       </c>
-      <c r="F281" s="30">
-        <v>0</v>
+      <c r="F281" s="120">
+        <v>1</v>
       </c>
       <c r="G281" s="83"/>
       <c r="H281" s="91"/>
-      <c r="I281" s="90"/>
+      <c r="I281" s="90">
+        <v>1</v>
+      </c>
       <c r="J281" s="1"/>
       <c r="K281" s="1"/>
       <c r="L281" s="1"/>
@@ -10218,16 +10360,16 @@
       <c r="B286" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C286" s="28" t="s">
+      <c r="C286" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="D286" s="28" t="s">
+      <c r="D286" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="E286" s="29">
+      <c r="E286" s="119">
         <v>1</v>
       </c>
-      <c r="F286" s="30">
+      <c r="F286" s="120">
         <v>2</v>
       </c>
       <c r="G286" s="83"/>
@@ -10272,21 +10414,23 @@
       <c r="B288" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C288" s="28" t="s">
+      <c r="C288" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="D288" s="28" t="s">
+      <c r="D288" s="118" t="s">
         <v>72</v>
       </c>
-      <c r="E288" s="29">
+      <c r="E288" s="119">
         <v>1</v>
       </c>
-      <c r="F288" s="30">
-        <v>2</v>
+      <c r="F288" s="120">
+        <v>3</v>
       </c>
       <c r="G288" s="87"/>
       <c r="H288" s="91"/>
-      <c r="I288" s="90"/>
+      <c r="I288" s="90">
+        <v>1</v>
+      </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
@@ -10444,7 +10588,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -10845,7 +10989,7 @@
         <v>78</v>
       </c>
       <c r="F313" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -11093,7 +11237,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -11209,19 +11353,21 @@
       <c r="B329" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C329" s="13"/>
-      <c r="D329" s="12" t="s">
+      <c r="C329" s="121"/>
+      <c r="D329" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E329" s="14">
+      <c r="E329" s="123">
         <v>1</v>
       </c>
-      <c r="F329" s="15">
-        <v>10</v>
+      <c r="F329" s="124">
+        <v>11</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
-      <c r="I329" s="90"/>
+      <c r="I329" s="90">
+        <v>1</v>
+      </c>
       <c r="J329" s="1"/>
       <c r="K329" s="1"/>
       <c r="L329" s="1"/>
@@ -11365,11 +11511,13 @@
         <v>10</v>
       </c>
       <c r="F335" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G335" s="87"/>
       <c r="H335" s="91"/>
-      <c r="I335" s="90"/>
+      <c r="I335" s="90">
+        <v>1</v>
+      </c>
       <c r="J335" s="1"/>
       <c r="K335" s="1"/>
       <c r="L335" s="1"/>
@@ -11541,11 +11689,13 @@
         <v>12</v>
       </c>
       <c r="F342" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G342" s="87"/>
       <c r="H342" s="91"/>
-      <c r="I342" s="90"/>
+      <c r="I342" s="90">
+        <v>1</v>
+      </c>
       <c r="J342" s="1"/>
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
@@ -11679,7 +11829,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -11761,11 +11911,13 @@
         <v>3</v>
       </c>
       <c r="F356" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
-      <c r="I356" s="1"/>
+      <c r="I356" s="1">
+        <v>1</v>
+      </c>
       <c r="J356" s="1"/>
     </row>
     <row r="357" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -11868,16 +12020,16 @@
       <c r="B363" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C363" s="28" t="s">
+      <c r="C363" s="118" t="s">
         <v>75</v>
       </c>
-      <c r="D363" s="28" t="s">
+      <c r="D363" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E363" s="29">
+      <c r="E363" s="119">
         <v>5</v>
       </c>
-      <c r="F363" s="30">
+      <c r="F363" s="120">
         <v>0</v>
       </c>
       <c r="G363" s="103"/>
@@ -11924,13 +12076,15 @@
         <v>413</v>
       </c>
       <c r="F365" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G365" s="103">
         <v>46268</v>
       </c>
       <c r="H365" s="103"/>
-      <c r="I365" s="1"/>
+      <c r="I365" s="1">
+        <v>1</v>
+      </c>
       <c r="J365" s="1"/>
     </row>
     <row r="366" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -11958,11 +12112,13 @@
         <v>25</v>
       </c>
       <c r="F367" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="103"/>
-      <c r="I367" s="1"/>
+      <c r="I367" s="1">
+        <v>1</v>
+      </c>
       <c r="J367" s="1"/>
     </row>
     <row r="368" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -12113,21 +12269,23 @@
       <c r="B374" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C374" s="28" t="s">
+      <c r="C374" s="118" t="s">
         <v>398</v>
       </c>
-      <c r="D374" s="28" t="s">
+      <c r="D374" s="118" t="s">
         <v>363</v>
       </c>
-      <c r="E374" s="29">
+      <c r="E374" s="119">
         <v>20</v>
       </c>
-      <c r="F374" s="30">
-        <v>0</v>
+      <c r="F374" s="120">
+        <v>3</v>
       </c>
       <c r="G374" s="103"/>
       <c r="H374" s="103"/>
-      <c r="I374" s="1"/>
+      <c r="I374" s="1">
+        <v>3</v>
+      </c>
       <c r="J374" s="1"/>
     </row>
     <row r="375" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -12162,7 +12320,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -12515,13 +12673,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="25">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" s="26">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7" s="27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="111"/>
       <c r="I7" s="41"/>
@@ -12534,19 +12692,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>32</v>
+        <v>21</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>265</v>
       </c>
       <c r="E8" s="25">
-        <v>10</v>
-      </c>
-      <c r="F8" s="26">
-        <v>15</v>
-      </c>
-      <c r="G8" s="27">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="F8" s="56">
+        <v>21</v>
+      </c>
+      <c r="G8" s="57">
+        <v>7</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -12559,19 +12717,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="E9" s="25">
-        <v>9</v>
-      </c>
-      <c r="F9" s="56">
-        <v>21</v>
-      </c>
-      <c r="G9" s="57">
         <v>12</v>
+      </c>
+      <c r="F9" s="26">
+        <v>20</v>
+      </c>
+      <c r="G9" s="27">
+        <v>8</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -12584,16 +12742,16 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>265</v>
+        <v>142</v>
       </c>
       <c r="E10" s="25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" s="27">
         <v>5</v>
@@ -12615,10 +12773,10 @@
         <v>15</v>
       </c>
       <c r="E11" s="25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" s="27">
         <v>3</v>
@@ -12634,19 +12792,19 @@
         <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>157</v>
+        <v>30</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>29</v>
       </c>
       <c r="E12" s="25">
         <v>8</v>
       </c>
       <c r="F12" s="26">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G12" s="27">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -12661,17 +12819,17 @@
       <c r="C13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="24" t="s">
         <v>125</v>
       </c>
       <c r="E13" s="25">
-        <v>6</v>
-      </c>
-      <c r="F13" s="56">
+        <v>5</v>
+      </c>
+      <c r="F13" s="26">
         <v>19</v>
       </c>
-      <c r="G13" s="57">
-        <v>13</v>
+      <c r="G13" s="27">
+        <v>14</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="41"/>
@@ -12681,22 +12839,22 @@
     <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47"/>
       <c r="B14" s="54">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E14" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="26">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G14" s="27">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="41"/>
@@ -12709,19 +12867,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>322</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="E15" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="26">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G15" s="27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="41"/>
@@ -12734,19 +12892,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>322</v>
+        <v>50</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
       <c r="E16" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="26">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16" s="27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -12761,17 +12919,17 @@
       <c r="C17" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="55" t="s">
         <v>399</v>
       </c>
       <c r="E17" s="25">
-        <v>2</v>
-      </c>
-      <c r="F17" s="26">
-        <v>13</v>
-      </c>
-      <c r="G17" s="27">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="F17" s="56">
+        <v>15</v>
+      </c>
+      <c r="G17" s="57">
+        <v>12</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -12793,10 +12951,10 @@
         <v>-2</v>
       </c>
       <c r="F18" s="56">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="57">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -12809,19 +12967,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="E19" s="25">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F19" s="26">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G19" s="27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -12834,19 +12992,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="55" t="s">
-        <v>105</v>
+        <v>49</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>126</v>
       </c>
       <c r="E20" s="25">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="F20" s="26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="27">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="41"/>
@@ -13388,16 +13546,24 @@
       <c r="A4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
+      <c r="C4" s="100">
+        <v>0</v>
+      </c>
+      <c r="D4" s="100" t="s">
+        <v>479</v>
+      </c>
       <c r="E4" s="68" t="s">
-        <v>466</v>
-      </c>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
+        <v>465</v>
+      </c>
+      <c r="F4" s="64">
+        <v>2</v>
+      </c>
+      <c r="G4" s="64" t="s">
+        <v>482</v>
+      </c>
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
       <c r="J4" s="98" t="s">
@@ -13425,13 +13591,21 @@
       <c r="B5" s="68" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="68" t="s">
-        <v>465</v>
-      </c>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
+      <c r="C5" s="64">
+        <v>0</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>472</v>
+      </c>
+      <c r="E5" s="69" t="s">
+        <v>473</v>
+      </c>
+      <c r="F5" s="100">
+        <v>-3</v>
+      </c>
+      <c r="G5" s="100" t="s">
+        <v>474</v>
+      </c>
       <c r="H5" s="38"/>
       <c r="I5" s="38"/>
       <c r="J5" s="98" t="s">
@@ -13459,13 +13633,21 @@
       <c r="B6" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
+      <c r="C6" s="64">
+        <v>-2</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>475</v>
+      </c>
       <c r="E6" s="68" t="s">
         <v>464</v>
       </c>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
+      <c r="F6" s="64">
+        <v>-2</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>475</v>
+      </c>
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
       <c r="J6" s="98" t="s">
@@ -13490,16 +13672,24 @@
       <c r="A7" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
+      <c r="C7" s="100">
+        <v>0</v>
+      </c>
+      <c r="D7" s="100" t="s">
+        <v>469</v>
+      </c>
       <c r="E7" s="68" t="s">
         <v>463</v>
       </c>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
+      <c r="F7" s="64">
+        <v>1</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>468</v>
+      </c>
       <c r="H7" s="38"/>
       <c r="I7" s="38"/>
       <c r="J7" s="98" t="s">
@@ -13527,13 +13717,21 @@
       <c r="B8" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="68" t="s">
+      <c r="C8" s="64">
+        <v>1</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="E8" s="69" t="s">
         <v>457</v>
       </c>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
+      <c r="F8" s="100">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="100" t="s">
+        <v>470</v>
+      </c>
       <c r="H8" s="38"/>
       <c r="I8" s="38"/>
       <c r="J8" s="98" t="s">
@@ -13561,13 +13759,21 @@
       <c r="B9" s="68" t="s">
         <v>265</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="68" t="s">
+      <c r="C9" s="64">
+        <v>7</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>477</v>
+      </c>
+      <c r="E9" s="69" t="s">
         <v>458</v>
       </c>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
+      <c r="F9" s="100">
+        <v>0</v>
+      </c>
+      <c r="G9" s="100" t="s">
+        <v>472</v>
+      </c>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
       <c r="J9" s="98" t="s">
@@ -13595,13 +13801,21 @@
       <c r="B10" s="68" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="68" t="s">
+      <c r="C10" s="64">
+        <v>4</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>480</v>
+      </c>
+      <c r="E10" s="69" t="s">
         <v>459</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
+      <c r="F10" s="100">
+        <v>1</v>
+      </c>
+      <c r="G10" s="100" t="s">
+        <v>476</v>
+      </c>
       <c r="H10" s="38"/>
       <c r="I10" s="38"/>
       <c r="J10" s="98" t="s">
@@ -13626,16 +13840,24 @@
       <c r="A11" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="69" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
+      <c r="C11" s="100">
+        <v>0</v>
+      </c>
+      <c r="D11" s="100" t="s">
+        <v>469</v>
+      </c>
       <c r="E11" s="68" t="s">
         <v>460</v>
       </c>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
+      <c r="F11" s="64">
+        <v>0</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>481</v>
+      </c>
       <c r="H11" s="38"/>
       <c r="I11" s="38"/>
       <c r="J11" s="38"/>
@@ -13661,13 +13883,21 @@
       <c r="B12" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="68" t="s">
+      <c r="C12" s="64">
+        <v>1</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="E12" s="69" t="s">
         <v>461</v>
       </c>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
+      <c r="F12" s="100">
+        <v>0</v>
+      </c>
+      <c r="G12" s="100" t="s">
+        <v>481</v>
+      </c>
       <c r="H12" s="38"/>
       <c r="I12" s="38"/>
       <c r="J12" s="38"/>
@@ -13690,16 +13920,24 @@
       <c r="A13" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
+      <c r="C13" s="100">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="100" t="s">
+        <v>478</v>
+      </c>
       <c r="E13" s="68" t="s">
         <v>462</v>
       </c>
-      <c r="F13" s="100"/>
-      <c r="G13" s="100"/>
+      <c r="F13" s="64">
+        <v>1</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>471</v>
+      </c>
       <c r="H13" s="38"/>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
@@ -13776,10 +14014,14 @@
       <c r="A16" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="68"/>
+      <c r="B16" s="68" t="s">
+        <v>464</v>
+      </c>
       <c r="C16" s="64"/>
       <c r="D16" s="64"/>
-      <c r="E16" s="69"/>
+      <c r="E16" s="68" t="s">
+        <v>157</v>
+      </c>
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
       <c r="H16" s="38"/>
@@ -15222,7 +15464,7 @@
       </c>
       <c r="K9">
         <f>COUNTIF(Stats!D:D,'Player Count'!J9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="109"/>
       <c r="N9" s="67" t="s">
@@ -15865,7 +16107,7 @@
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N30" s="78" t="s">
         <v>186</v>
@@ -15896,28 +16138,28 @@
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.43333333333333335</v>
+        <v>0.43093922651933703</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.21111111111111111</v>
+        <v>0.20994475138121546</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20555555555555555</v>
+        <v>0.20994475138121546</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.15</v>
+        <v>0.14917127071823205</v>
       </c>
     </row>
   </sheetData>

--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1605" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B68D3B-A854-496E-8406-D60DAA26BD45}"/>
+  <xr:revisionPtr revIDLastSave="1698" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE3D8B39-3598-42D2-8623-C57CC08BEA14}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="486">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1488,6 +1488,15 @@
   </si>
   <si>
     <t>(4 - 2)</t>
+  </si>
+  <si>
+    <t>OLIVER IROW</t>
+  </si>
+  <si>
+    <t>CREWE</t>
+  </si>
+  <si>
+    <t>(1-0)</t>
   </si>
 </sst>
 </file>
@@ -3591,15 +3600,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3618,7 +3627,7 @@
         <v>413</v>
       </c>
       <c r="F6" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="86">
         <v>46275</v>
@@ -3636,11 +3645,11 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
@@ -3671,15 +3680,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3700,7 +3709,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="83"/>
       <c r="H8" s="75"/>
@@ -3715,15 +3724,15 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3761,15 +3770,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3805,11 +3814,11 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
@@ -3852,11 +3861,11 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
@@ -3905,11 +3914,11 @@
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3945,15 +3954,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R13" s="134"/>
       <c r="S13" s="134"/>
@@ -4027,7 +4036,7 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
@@ -4035,7 +4044,7 @@
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4053,7 +4062,7 @@
         <v>17</v>
       </c>
       <c r="F16" s="30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="84"/>
       <c r="H16" s="84"/>
@@ -4069,15 +4078,15 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4095,7 +4104,7 @@
         <v>28</v>
       </c>
       <c r="F17" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G17" s="84"/>
       <c r="H17" s="84"/>
@@ -4111,15 +4120,15 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R17" s="134"/>
       <c r="S17" s="134"/>
@@ -4142,7 +4151,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="83"/>
       <c r="H18" s="84"/>
@@ -4158,15 +4167,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4187,7 +4196,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G19" s="87"/>
       <c r="H19" s="84"/>
@@ -4354,7 +4363,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4619,9 +4628,7 @@
       </c>
       <c r="G38" s="87"/>
       <c r="H38" s="91"/>
-      <c r="I38" s="93">
-        <v>2</v>
-      </c>
+      <c r="I38" s="93"/>
       <c r="J38" s="76"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -4653,9 +4660,7 @@
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
-      <c r="I39" s="89">
-        <v>1</v>
-      </c>
+      <c r="I39" s="89"/>
       <c r="J39" s="76"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -4678,7 +4683,7 @@
         <v>43</v>
       </c>
       <c r="F40" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G40" s="87"/>
       <c r="H40" s="91"/>
@@ -4743,9 +4748,7 @@
       </c>
       <c r="G43" s="87"/>
       <c r="H43" s="91"/>
-      <c r="I43" s="89">
-        <v>1</v>
-      </c>
+      <c r="I43" s="89"/>
       <c r="J43" s="76"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -4826,15 +4829,13 @@
         <v>413</v>
       </c>
       <c r="F46" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="91">
         <v>46261</v>
       </c>
       <c r="H46" s="91"/>
-      <c r="I46" s="89">
-        <v>1</v>
-      </c>
+      <c r="I46" s="89"/>
       <c r="J46" s="76"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -4857,13 +4858,11 @@
         <v>13</v>
       </c>
       <c r="F47" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="91"/>
       <c r="H47" s="91"/>
-      <c r="I47" s="89">
-        <v>1</v>
-      </c>
+      <c r="I47" s="89"/>
       <c r="J47" s="76"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -4890,9 +4889,7 @@
       </c>
       <c r="G48" s="91"/>
       <c r="H48" s="91"/>
-      <c r="I48" s="89">
-        <v>1</v>
-      </c>
+      <c r="I48" s="89"/>
       <c r="J48" s="76"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -4979,7 +4976,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -5132,7 +5129,7 @@
         <v>413</v>
       </c>
       <c r="F60" s="132">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G60" s="86">
         <v>46268</v>
@@ -5423,7 +5420,7 @@
         <v>23</v>
       </c>
       <c r="F71" s="120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" s="83"/>
       <c r="H71" s="91"/>
@@ -5612,7 +5609,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -5736,7 +5733,7 @@
         <v>4</v>
       </c>
       <c r="F86" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
@@ -5926,7 +5923,7 @@
         <v>413</v>
       </c>
       <c r="F94" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94" s="91">
         <v>46275</v>
@@ -6026,7 +6023,7 @@
         <v>7</v>
       </c>
       <c r="F98" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G98" s="87"/>
       <c r="H98" s="91"/>
@@ -6173,7 +6170,7 @@
         <v>48</v>
       </c>
       <c r="F103" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" s="87"/>
       <c r="H103" s="91"/>
@@ -6247,7 +6244,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6371,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -6503,7 +6500,7 @@
         <v>1</v>
       </c>
       <c r="F119" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" s="87"/>
       <c r="H119" s="91"/>
@@ -6692,7 +6689,7 @@
         <v>413</v>
       </c>
       <c r="F126" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G126" s="87">
         <v>46261</v>
@@ -6898,7 +6895,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7009,26 +7006,28 @@
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
     </row>
-    <row r="140" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="79"/>
-      <c r="B140" s="12" t="s">
+      <c r="B140" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="C140" s="13"/>
-      <c r="D140" s="12" t="s">
+      <c r="C140" s="115"/>
+      <c r="D140" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="E140" s="14">
+      <c r="E140" s="116">
         <v>1</v>
       </c>
-      <c r="F140" s="15">
+      <c r="F140" s="117">
         <v>15</v>
       </c>
-      <c r="G140" s="80"/>
-      <c r="H140" s="94"/>
-      <c r="I140" s="93">
-        <v>3</v>
-      </c>
+      <c r="G140" s="80" t="s">
+        <v>414</v>
+      </c>
+      <c r="H140" s="94">
+        <v>46303</v>
+      </c>
+      <c r="I140" s="93"/>
       <c r="J140" s="76"/>
       <c r="K140" s="1"/>
       <c r="L140" s="1"/>
@@ -7038,12 +7037,22 @@
     </row>
     <row r="141" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="79"/>
-      <c r="B141" s="21"/>
+      <c r="B141" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="C141" s="21"/>
-      <c r="D141" s="21"/>
-      <c r="E141" s="22"/>
-      <c r="F141" s="21"/>
-      <c r="G141" s="86"/>
+      <c r="D141" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="E141" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="F141" s="21">
+        <v>0</v>
+      </c>
+      <c r="G141" s="86">
+        <v>46303</v>
+      </c>
       <c r="H141" s="94"/>
       <c r="I141" s="92"/>
       <c r="J141" s="76"/>
@@ -7085,7 +7094,7 @@
         <v>2</v>
       </c>
       <c r="F143" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G143" s="83"/>
       <c r="H143" s="91"/>
@@ -7280,9 +7289,7 @@
       </c>
       <c r="G150" s="87"/>
       <c r="H150" s="91"/>
-      <c r="I150" s="90">
-        <v>1</v>
-      </c>
+      <c r="I150" s="90"/>
       <c r="J150" s="76"/>
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
@@ -7305,7 +7312,7 @@
         <v>1</v>
       </c>
       <c r="F151" s="120">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G151" s="83"/>
       <c r="H151" s="91"/>
@@ -7363,9 +7370,7 @@
       </c>
       <c r="G153" s="87"/>
       <c r="H153" s="91"/>
-      <c r="I153" s="90">
-        <v>1</v>
-      </c>
+      <c r="I153" s="90"/>
       <c r="J153" s="96"/>
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
@@ -7477,7 +7482,7 @@
         <v>413</v>
       </c>
       <c r="F157" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" s="87">
         <v>46268</v>
@@ -7553,7 +7558,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -7681,9 +7686,7 @@
       </c>
       <c r="G167" s="80"/>
       <c r="H167" s="94"/>
-      <c r="I167" s="92">
-        <v>3</v>
-      </c>
+      <c r="I167" s="92"/>
       <c r="J167" s="76"/>
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
@@ -7838,7 +7841,7 @@
         <v>12</v>
       </c>
       <c r="F174" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G174" s="91"/>
       <c r="H174" s="91"/>
@@ -7865,13 +7868,11 @@
         <v>8</v>
       </c>
       <c r="F175" s="120">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G175" s="87"/>
       <c r="H175" s="91"/>
-      <c r="I175" s="90">
-        <v>1</v>
-      </c>
+      <c r="I175" s="90"/>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
@@ -7955,7 +7956,7 @@
         <v>24</v>
       </c>
       <c r="F179" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G179" s="83"/>
       <c r="H179" s="91"/>
@@ -7986,9 +7987,7 @@
       </c>
       <c r="G180" s="91"/>
       <c r="H180" s="91"/>
-      <c r="I180" s="90">
-        <v>2</v>
-      </c>
+      <c r="I180" s="90"/>
       <c r="J180" s="76"/>
       <c r="K180" s="1"/>
       <c r="L180" s="1"/>
@@ -8011,7 +8010,7 @@
         <v>3</v>
       </c>
       <c r="F181" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" s="91"/>
       <c r="H181" s="91"/>
@@ -8146,7 +8145,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -8270,13 +8269,11 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
-      <c r="I194" s="90">
-        <v>1</v>
-      </c>
+      <c r="I194" s="90"/>
       <c r="J194" s="76"/>
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
@@ -8550,7 +8547,7 @@
         <v>413</v>
       </c>
       <c r="F206" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G206" s="87">
         <v>46254</v>
@@ -8637,9 +8634,7 @@
       </c>
       <c r="G209" s="87"/>
       <c r="H209" s="91"/>
-      <c r="I209" s="90">
-        <v>1</v>
-      </c>
+      <c r="I209" s="90"/>
       <c r="J209" s="76"/>
       <c r="K209" s="1"/>
       <c r="L209" s="1"/>
@@ -8877,12 +8872,12 @@
         <v>8</v>
       </c>
       <c r="F221" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G221" s="80"/>
       <c r="H221" s="94"/>
       <c r="I221" s="93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J221" s="76"/>
       <c r="K221" s="1"/>
@@ -8961,13 +8956,13 @@
         <v>374</v>
       </c>
       <c r="D225" s="28" t="s">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="E225" s="29">
         <v>1</v>
       </c>
       <c r="F225" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G225" s="87"/>
       <c r="H225" s="91"/>
@@ -9069,7 +9064,7 @@
         <v>413</v>
       </c>
       <c r="F229" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G229" s="87">
         <v>46268</v>
@@ -9129,7 +9124,7 @@
         <v>413</v>
       </c>
       <c r="F231" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" s="87">
         <v>46282</v>
@@ -9162,9 +9157,7 @@
       </c>
       <c r="G232" s="87"/>
       <c r="H232" s="91"/>
-      <c r="I232" s="89">
-        <v>1</v>
-      </c>
+      <c r="I232" s="89"/>
       <c r="J232" s="1"/>
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
@@ -9245,13 +9238,15 @@
         <v>413</v>
       </c>
       <c r="F235" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G235" s="87">
         <v>46268</v>
       </c>
       <c r="H235" s="91"/>
-      <c r="I235" s="89"/>
+      <c r="I235" s="89">
+        <v>1</v>
+      </c>
       <c r="J235" s="76"/>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
@@ -9392,7 +9387,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -9676,23 +9671,27 @@
     </row>
     <row r="255" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="79"/>
-      <c r="B255" s="28" t="s">
+      <c r="B255" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C255" s="28" t="s">
+      <c r="C255" s="106" t="s">
         <v>302</v>
       </c>
-      <c r="D255" s="28" t="s">
+      <c r="D255" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="E255" s="29">
+      <c r="E255" s="107">
         <v>2</v>
       </c>
-      <c r="F255" s="30">
+      <c r="F255" s="108">
         <v>0</v>
       </c>
-      <c r="G255" s="87"/>
-      <c r="H255" s="91"/>
+      <c r="G255" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="H255" s="91">
+        <v>46289</v>
+      </c>
       <c r="I255" s="90"/>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
@@ -9707,18 +9706,20 @@
         <v>16</v>
       </c>
       <c r="C256" s="28" t="s">
-        <v>291</v>
+        <v>483</v>
       </c>
       <c r="D256" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E256" s="29">
-        <v>1</v>
+        <v>267</v>
+      </c>
+      <c r="E256" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="F256" s="30">
-        <v>1</v>
-      </c>
-      <c r="G256" s="87"/>
+        <v>0</v>
+      </c>
+      <c r="G256" s="87">
+        <v>46289</v>
+      </c>
       <c r="H256" s="91"/>
       <c r="I256" s="90"/>
       <c r="J256" s="1"/>
@@ -9730,11 +9731,21 @@
     </row>
     <row r="257" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="79"/>
-      <c r="B257" s="28"/>
-      <c r="C257" s="28"/>
-      <c r="D257" s="28"/>
-      <c r="E257" s="29"/>
-      <c r="F257" s="30"/>
+      <c r="B257" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C257" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="D257" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E257" s="29">
+        <v>1</v>
+      </c>
+      <c r="F257" s="30">
+        <v>1</v>
+      </c>
       <c r="G257" s="87"/>
       <c r="H257" s="91"/>
       <c r="I257" s="90"/>
@@ -9808,9 +9819,7 @@
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
-      <c r="I260" s="90">
-        <v>1</v>
-      </c>
+      <c r="I260" s="90"/>
       <c r="J260" s="1"/>
       <c r="K260" s="1"/>
       <c r="L260" s="1"/>
@@ -10119,13 +10128,11 @@
         <v>1</v>
       </c>
       <c r="F275" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G275" s="80"/>
       <c r="H275" s="94"/>
-      <c r="I275" s="92">
-        <v>1</v>
-      </c>
+      <c r="I275" s="92"/>
       <c r="J275" s="1"/>
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
@@ -10257,9 +10264,7 @@
       </c>
       <c r="G281" s="83"/>
       <c r="H281" s="91"/>
-      <c r="I281" s="90">
-        <v>1</v>
-      </c>
+      <c r="I281" s="90"/>
       <c r="J281" s="1"/>
       <c r="K281" s="1"/>
       <c r="L281" s="1"/>
@@ -10428,9 +10433,7 @@
       </c>
       <c r="G288" s="87"/>
       <c r="H288" s="91"/>
-      <c r="I288" s="90">
-        <v>1</v>
-      </c>
+      <c r="I288" s="90"/>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
@@ -10588,7 +10591,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -10741,7 +10744,7 @@
         <v>413</v>
       </c>
       <c r="F303" s="21">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G303" s="87">
         <v>46261</v>
@@ -10858,7 +10861,7 @@
         <v>1</v>
       </c>
       <c r="F308" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G308" s="87"/>
       <c r="H308" s="91"/>
@@ -10916,7 +10919,7 @@
         <v>413</v>
       </c>
       <c r="F310" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G310" s="87">
         <v>46268</v>
@@ -10989,7 +10992,7 @@
         <v>78</v>
       </c>
       <c r="F313" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -11047,7 +11050,7 @@
         <v>413</v>
       </c>
       <c r="F315" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G315" s="87">
         <v>46268</v>
@@ -11237,7 +11240,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -11361,13 +11364,11 @@
         <v>1</v>
       </c>
       <c r="F329" s="124">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
-      <c r="I329" s="90">
-        <v>1</v>
-      </c>
+      <c r="I329" s="90"/>
       <c r="J329" s="1"/>
       <c r="K329" s="1"/>
       <c r="L329" s="1"/>
@@ -11515,9 +11516,7 @@
       </c>
       <c r="G335" s="87"/>
       <c r="H335" s="91"/>
-      <c r="I335" s="90">
-        <v>1</v>
-      </c>
+      <c r="I335" s="90"/>
       <c r="J335" s="1"/>
       <c r="K335" s="1"/>
       <c r="L335" s="1"/>
@@ -11598,7 +11597,7 @@
         <v>413</v>
       </c>
       <c r="F338" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G338" s="87">
         <v>46268</v>
@@ -11641,7 +11640,7 @@
         <v>9</v>
       </c>
       <c r="F340" s="30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G340" s="87"/>
       <c r="H340" s="90"/>
@@ -11689,13 +11688,11 @@
         <v>12</v>
       </c>
       <c r="F342" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G342" s="87"/>
       <c r="H342" s="91"/>
-      <c r="I342" s="90">
-        <v>1</v>
-      </c>
+      <c r="I342" s="90"/>
       <c r="J342" s="1"/>
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
@@ -11829,7 +11826,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -11911,13 +11908,11 @@
         <v>3</v>
       </c>
       <c r="F356" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
-      <c r="I356" s="1">
-        <v>1</v>
-      </c>
+      <c r="I356" s="1"/>
       <c r="J356" s="1"/>
     </row>
     <row r="357" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -12082,9 +12077,7 @@
         <v>46268</v>
       </c>
       <c r="H365" s="103"/>
-      <c r="I365" s="1">
-        <v>1</v>
-      </c>
+      <c r="I365" s="1"/>
       <c r="J365" s="1"/>
     </row>
     <row r="366" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -12112,13 +12105,11 @@
         <v>25</v>
       </c>
       <c r="F367" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="103"/>
-      <c r="I367" s="1">
-        <v>1</v>
-      </c>
+      <c r="I367" s="1"/>
       <c r="J367" s="1"/>
     </row>
     <row r="368" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -12195,73 +12186,75 @@
       <c r="J370" s="1"/>
     </row>
     <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B371" s="28" t="s">
+      <c r="B371" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C371" s="28" t="s">
+      <c r="C371" s="106" t="s">
         <v>440</v>
       </c>
-      <c r="D371" s="28" t="s">
+      <c r="D371" s="106" t="s">
         <v>439</v>
       </c>
-      <c r="E371" s="29" t="s">
+      <c r="E371" s="107" t="s">
         <v>413</v>
       </c>
-      <c r="F371" s="30">
+      <c r="F371" s="108">
         <v>0</v>
       </c>
       <c r="G371" s="103">
         <v>46268</v>
       </c>
-      <c r="H371" s="103"/>
+      <c r="H371" s="103">
+        <v>46303</v>
+      </c>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
     </row>
     <row r="372" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B372" s="106" t="s">
+      <c r="B372" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C372" s="106" t="s">
-        <v>396</v>
-      </c>
-      <c r="D372" s="106" t="s">
-        <v>397</v>
-      </c>
-      <c r="E372" s="107">
-        <v>1</v>
-      </c>
-      <c r="F372" s="108">
+      <c r="C372" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D372" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E372" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F372" s="30">
         <v>0</v>
       </c>
-      <c r="G372" s="103" t="s">
-        <v>414</v>
-      </c>
-      <c r="H372" s="103">
-        <v>46254</v>
-      </c>
+      <c r="G372" s="103">
+        <v>46303</v>
+      </c>
+      <c r="H372" s="103"/>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
     </row>
     <row r="373" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B373" s="28" t="s">
+      <c r="B373" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C373" s="28" t="s">
-        <v>417</v>
-      </c>
-      <c r="D373" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E373" s="29" t="s">
-        <v>413</v>
-      </c>
-      <c r="F373" s="30">
+      <c r="C373" s="106" t="s">
+        <v>396</v>
+      </c>
+      <c r="D373" s="106" t="s">
+        <v>397</v>
+      </c>
+      <c r="E373" s="107">
+        <v>1</v>
+      </c>
+      <c r="F373" s="108">
         <v>0</v>
       </c>
-      <c r="G373" s="103">
+      <c r="G373" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="H373" s="103">
         <v>46254</v>
       </c>
-      <c r="H373" s="103"/>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
     </row>
@@ -12269,31 +12262,41 @@
       <c r="B374" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C374" s="118" t="s">
+      <c r="C374" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="D374" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E374" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F374" s="30">
+        <v>0</v>
+      </c>
+      <c r="G374" s="103">
+        <v>46254</v>
+      </c>
+      <c r="H374" s="103"/>
+      <c r="I374" s="1"/>
+      <c r="J374" s="1"/>
+    </row>
+    <row r="375" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B375" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C375" s="118" t="s">
         <v>398</v>
       </c>
-      <c r="D374" s="118" t="s">
+      <c r="D375" s="118" t="s">
         <v>363</v>
       </c>
-      <c r="E374" s="119">
+      <c r="E375" s="119">
         <v>20</v>
       </c>
-      <c r="F374" s="120">
+      <c r="F375" s="120">
         <v>3</v>
       </c>
-      <c r="G374" s="103"/>
-      <c r="H374" s="103"/>
-      <c r="I374" s="1">
-        <v>3</v>
-      </c>
-      <c r="J374" s="1"/>
-    </row>
-    <row r="375" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B375" s="106"/>
-      <c r="C375" s="106"/>
-      <c r="D375" s="106"/>
-      <c r="E375" s="107"/>
-      <c r="F375" s="108"/>
       <c r="G375" s="103"/>
       <c r="H375" s="103"/>
       <c r="I375" s="1"/>
@@ -12320,7 +12323,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -12673,13 +12676,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="25">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F7" s="26">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G7" s="27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" s="111"/>
       <c r="I7" s="41"/>
@@ -12698,10 +12701,10 @@
         <v>265</v>
       </c>
       <c r="E8" s="25">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F8" s="56">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G8" s="57">
         <v>7</v>
@@ -12723,10 +12726,10 @@
         <v>32</v>
       </c>
       <c r="E9" s="25">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F9" s="26">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G9" s="27">
         <v>8</v>
@@ -12742,19 +12745,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="E10" s="25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10" s="26">
+        <v>27</v>
+      </c>
+      <c r="G10" s="27">
         <v>15</v>
-      </c>
-      <c r="G10" s="27">
-        <v>5</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="41"/>
@@ -12769,17 +12772,17 @@
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="55" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="26">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G11" s="27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="41"/>
@@ -12789,22 +12792,22 @@
     <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47"/>
       <c r="B12" s="54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>29</v>
+        <v>341</v>
       </c>
       <c r="E12" s="25">
         <v>8</v>
       </c>
-      <c r="F12" s="26">
-        <v>23</v>
-      </c>
-      <c r="G12" s="27">
-        <v>15</v>
+      <c r="F12" s="56">
+        <v>20</v>
+      </c>
+      <c r="G12" s="57">
+        <v>12</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -12817,19 +12820,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="E13" s="25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" s="26">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G13" s="27">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="41"/>
@@ -12839,22 +12842,22 @@
     <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47"/>
       <c r="B14" s="54">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="25">
         <v>7</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" s="25">
-        <v>5</v>
-      </c>
       <c r="F14" s="26">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G14" s="27">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="41"/>
@@ -12867,19 +12870,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>322</v>
+        <v>51</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>341</v>
+        <v>134</v>
       </c>
       <c r="E15" s="25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" s="26">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G15" s="27">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="41"/>
@@ -12892,19 +12895,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="55" t="s">
-        <v>157</v>
+        <v>25</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>125</v>
       </c>
       <c r="E16" s="25">
         <v>4</v>
       </c>
       <c r="F16" s="26">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G16" s="27">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -12919,17 +12922,17 @@
       <c r="C17" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="24" t="s">
         <v>399</v>
       </c>
       <c r="E17" s="25">
         <v>3</v>
       </c>
-      <c r="F17" s="56">
-        <v>15</v>
-      </c>
-      <c r="G17" s="57">
-        <v>12</v>
+      <c r="F17" s="26">
+        <v>16</v>
+      </c>
+      <c r="G17" s="27">
+        <v>13</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -12948,13 +12951,13 @@
         <v>139</v>
       </c>
       <c r="E18" s="25">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="56">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G18" s="57">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -12969,17 +12972,17 @@
       <c r="C19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="55" t="s">
         <v>105</v>
       </c>
       <c r="E19" s="25">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="F19" s="26">
         <v>8</v>
       </c>
       <c r="G19" s="27">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -12998,13 +13001,13 @@
         <v>126</v>
       </c>
       <c r="E20" s="25">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="F20" s="26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="41"/>
@@ -14017,13 +14020,21 @@
       <c r="B16" s="68" t="s">
         <v>464</v>
       </c>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="68" t="s">
+      <c r="C16" s="64">
+        <v>1</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>485</v>
+      </c>
+      <c r="E16" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="100"/>
-      <c r="G16" s="100"/>
+      <c r="F16" s="100">
+        <v>0</v>
+      </c>
+      <c r="G16" s="100" t="s">
+        <v>472</v>
+      </c>
       <c r="H16" s="38"/>
       <c r="I16" s="38"/>
       <c r="J16" s="38"/>
@@ -15354,7 +15365,7 @@
       </c>
       <c r="C6">
         <f>COUNTIF(Stats!D:D,'Player Count'!B6)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>188</v>
@@ -15600,7 +15611,7 @@
       </c>
       <c r="O13">
         <f>COUNTIF(Stats!D:D,'Player Count'!N13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="109"/>
     </row>
@@ -15952,7 +15963,7 @@
       </c>
       <c r="O24">
         <f>COUNTIF(Stats!D:D,'Player Count'!N24)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="109"/>
     </row>
@@ -15994,7 +16005,7 @@
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s">
         <v>208</v>
@@ -16114,7 +16125,7 @@
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
@@ -16138,28 +16149,28 @@
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.43093922651933703</v>
+        <v>0.42934782608695654</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20994475138121546</v>
+        <v>0.20652173913043478</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20994475138121546</v>
+        <v>0.20652173913043478</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.14917127071823205</v>
+        <v>0.15760869565217392</v>
       </c>
     </row>
   </sheetData>
